--- a/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
+++ b/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario Stress-Testing" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monte Carlo Risk" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Risk &amp; Copula" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -103,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,6 +122,7 @@
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2122,4 +2124,405 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MULTIVARIATE COPULA TAIL RISK &amp; CREDIT COMMITTEE UNDERWRITING</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>1. MULTIVARIATE COPULA RISK COMPARISON (50,000 SIMULATIONS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Model Specification</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Tail Dep. (Lower / Upper)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Mean DSCR</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Median DSCR</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>VaR 95% (5th pct)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>VaR 99% (1st pct)</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>CVaR 99% (Worst 1%)</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>P(DSCR &lt; 1.25x)</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>P(DSCR &lt; 1.00x)</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>CVaR 99% Deficit (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Gaussian Copula (Benchmark)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>0.00 / 0.00 (Independent)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1.36x</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>1.34x</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>0.64x</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>0.37x</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>0.26x</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>42.31%</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>21.61%</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>33,906 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Student-t Copula (nu=4)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>0.18 / 0.18 (Symmetric)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1.36x</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1.34x</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>0.64x</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>0.35x</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>0.21x</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>42.11%</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>21.23%</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>36,735 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Clayton Copula (theta=1.8)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>0.68 / 0.00 (Asymmetric Lower)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>1.36x</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1.38x</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>0.49x</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>0.17x</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>0.04x</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>40.35%</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>23.23%</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>47,597 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>2. UNDERWRITING SCORECARD &amp; DSRA SIZING</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Underwriting Parameter</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Credit Committee Benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Facility Requested (Senior Mortgage)</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>507,500.00 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Total Project CapEx</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>729,000.00 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Senior Loan-to-Value (Total CapEx)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>69.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Baseline Year 1 DSCR</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>1.34x</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Mature Year 3 DSCR</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>1.73x</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Operating Break-Even Occupancy</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>18.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Debt Service Break-Even Occupancy</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Standard Covenant DSRA (6 Months)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>21,774.91 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Copula Tail DSRA (CVaR 99%)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>47,596.85 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Unhedged Deficit under 6-Month DSRA</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>25,821.94 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Credit Committee Recommendation</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>CONDITIONAL APPROVAL (Escrow DSRA + LEADER Grant Pledge)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
+++ b/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario Stress-Testing" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monte Carlo Risk" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Risk &amp; Copula" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Economics &amp; Runway" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,7 +59,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +76,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F1F5F9"/>
         <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,6 +130,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2525,4 +2533,1633 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="87" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UNIT ECONOMICS, CONTRIBUTION MARGIN &amp; 24-MONTH MONTHLY CASH RUNWAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>1. UNIT ECONOMICS &amp; CONTRIBUTION MARGIN (USALI STANDARDS)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>2. RevPAR &amp; TRevPAR PERFORMANCE SCHEDULE (YEARS 1 TO 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Metric / Cost Category</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Operational / Statutory Basis</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Occupancy Rate</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Occupied Days</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Lodging Revenue (€)</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>Total Revenue (€)</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Revpar (€)</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Trevpar (€)</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>Contribution Margin (€)</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>Fixed Burden Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Daily Gross Revenue @ 100% Occ</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>1,500.00 EUR</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>8 keys: Lodging 975 EUR + F&amp;B 525 EUR</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Year 1 (Ramp-up)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>28.23%</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>100456.2</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>154548</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>125673.28</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>1.09x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Variable Costs per Occupied Day</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>280.25 EUR</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>18.7% variable cost ratio</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 (Stabilized)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>31.36%</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>111618</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>171720</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>139636.98</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>1.21x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - F&amp;B COGS (30% spend)</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>157.50 EUR</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>30% of daily F&amp;B turnover</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Year 3 (Mature)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>32.93%</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>117198.9</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>180306</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>146618.83</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>1.27x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - OTA Commissions (60% OTA @ 15%)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>87.75 EUR</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>15% on 60% OTA booking mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Amenities &amp; Guest Supplies</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>35.00 EUR</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Direct consumables per occupied day</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Unit Contribution Margin (Day)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>1,219.75 EUR</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>81.32% contribution margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Room-Night Unit Margin</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>107.97 EUR</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>79.98% per room-night</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Annual Fixed Overhead (Payroll + OPEX)</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>72,234.00 EUR</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Base operational fixed costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Annual Senior Debt Service</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>43,536.35 EUR</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>15Y French amortization @ 3.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Annual Total Fixed Burden</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>115,770.35 EUR</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Overhead + full debt service</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Operating Break-Even Occupied Days</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>59.2 Days</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>16.2% annual occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Cash Debt Break-Even Occupied Days</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>94.9 Days</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>26.0% annual occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Bank Covenant 1.25x Break-Even Days</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>103.8 Days</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>28.4% annual occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>3. 24-MONTH EMPIRICAL CASH RUNWAY &amp; CASH TROUGH SCHEDULE (SEGOVIA EMPIRICAL WEIGHTS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Occupancy (%)</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Revenue (EUR)</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Var Costs (EUR)</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Contr Margin (EUR)</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Payroll (EUR)</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Fixed OPEX (EUR)</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Debt Svc (EUR)</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>Net Op CF (EUR)</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>Grant/VAT Inflow (EUR)</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Credit Drawn (EUR)</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>Ending Cash (EUR)</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>Total Liquidity (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>5649.75</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>1070.21</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>4579.54</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>-5067.99</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>51682.01</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>101682.01</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>5783.4</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1095.53</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>4687.87</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>-4959.65</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>46722.36</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>96722.36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>9541.799999999999</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>1794.44</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>7747.36</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>-1900.17</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>44822.18</v>
+      </c>
+      <c r="N22" s="12" t="n">
+        <v>94822.17999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>13182.75</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>2448.33</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>10734.42</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>1086.89</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>45909.08</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>95909.08</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>13810.5</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>2580.26</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>11230.24</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>1582.71</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>47491.78</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>97491.78</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>15734.25</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>2922.2</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>12812.05</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>3164.52</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>50656.31</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>100656.31</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>23101.2</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>4245.77</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>18855.43</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>9207.9</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>59864.21</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>109864.21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>27118.8</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>4961.23</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>22157.57</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>12510.04</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>72374.25</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>122374.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>15309</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>2843.22</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>12465.78</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>2818.25</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>75192.5</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>125192.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>12555</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>2345.69</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>10209.31</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>561.78</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>75754.28</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>125754.28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>8464.5</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>1591.85</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>6872.65</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>-2774.87</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>72979.39999999999</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>122979.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>12889.8</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>2380.9</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>10508.9</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>861.37</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>73840.77</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>123840.77</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>6277.5</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>1189.12</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>5088.38</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>-4559.15</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>69281.62</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>119281.62</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>6426</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1217.25</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>5208.75</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>-4438.78</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>163000</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>227842.84</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>277842.84</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>10602</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>1993.83</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>8608.17</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>-1039.36</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>226803.48</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>276803.48</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>14647.5</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>2720.37</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>11927.13</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>2279.6</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>229083.09</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>279083.09</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>15345</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>2866.96</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>12478.04</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>2830.51</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>231913.6</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>281913.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>17482.5</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>3246.89</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>14235.61</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>4588.08</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>153090</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>389591.69</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>439591.69</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>25668</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>4717.52</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>20950.48</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>11302.95</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>400894.64</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>450894.64</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>30132</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>5512.48</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>24619.52</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>14971.99</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>415866.63</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>465866.63</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>17010</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>3159.13</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>13850.86</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>4203.34</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>420069.96</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>470069.96</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>13950</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>2606.32</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>11343.67</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>1696.15</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>421766.11</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>471766.11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>9405</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>1768.72</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>7636.28</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>-2011.25</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>419754.86</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>469754.86</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>14322</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>2645.45</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>11676.55</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>5006.25</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>3628.03</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>2029.02</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>421783.89</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>471783.89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
+++ b/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monte Carlo Risk" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Risk &amp; Copula" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Economics &amp; Runway" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase II Expansion" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4162,4 +4163,723 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PHASE II EXPANSION: LANDSCAPE HOTEL SUITES &amp; BIOLOGICAL RESERVOIR (VALUE-ADD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>1. PHASE II ALL-IN CAPEX &amp; EXECUTION BUDGET (110 M² SUITES + 200 M² POND)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>2. INVESTMENT RETURNS &amp; CAPITAL ALLOCATION METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>CapEx Investment Chapter</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Budget (EUR)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Technical Benchmark / Repercussion</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Return / Underwriting Parameter</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Metric Value</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Strategic Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Pure Building PEM (Foundations, Stone, Timber, Glazing, HVAC, Bath)</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>161,500.00 EUR</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1,468.18 EUR/m² built (110 m²)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Stabilized Year 3 Gross Revenue</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>146,182.50 EUR</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>ADR 290 EUR net | 50% Occ (365 nights)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Contractor PEC - Pure Building (13% GG + 6% BI)</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>192,185.00 EUR</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1,747.14 EUR/m² built</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Stabilized Year 3 Contribution Margin</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>114,020.52 EUR</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>78.00% contribution margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Estate Utilities &amp; Trenching Across 25 Ha (Water, Power, Bio-Sewage)</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>37,485.00 EUR</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>37,485.00 EUR PEC</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Stabilized Year 3 Incremental EBITDA</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>99,620.52 EUR</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>68.15% EBITDA margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>5-Star FF&amp;E, High-End Textiles, Porch &amp; Exterior Hot Tub</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>41,650.00 EUR</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>41,650.00 EUR PEC (2 suites)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Stabilized Year 3 Free Cash Flow (Post-Tax)</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>75,841.41 EUR</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Clean cash flow net of 2% FF&amp;E reserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Biological Pond (200 m² EPDM, Biofilter, Zeolites, Cascade, Flora)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>38,080.00 EUR</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>38,080.00 EUR PEC (190.40 EUR/m² water)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Development Yield on Cost (EBITDA / CapEx)</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>27.67%</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Unlevered gross development yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL CONTRACTOR WORKS PEC (Capítulo 1 al 8)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>309,400.00 EUR</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2,812.73 EUR/m² repercutido</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Return on Invested Capital (ROIC Y3)</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>17.38%</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>+938 bps spread over 8.0% WACC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Architecture, Engineering &amp; Project Management Fees (9.0% PEM)</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>23,400.00 EUR</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Complete technical project &amp; permits</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Simple EBITDA Payback Period</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>3.99 Years</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>47.6 months recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Municipal Taxes, Urban Fees &amp; ICIO (4.5% PEM)</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>11,700.00 EUR</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Segovia rural municipality rate</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Simple Post-Tax FCF Payback Period</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>5.07 Years</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>61.2 months recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Contingency Reserve (5.0% PEC)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>15,470.00 EUR</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Granite rock &amp; unforeseen works</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Year 5 Exit Valuation @ 8.5% Cap Rate</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>1,219,355.23 EUR</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Net gain: +859,385.23 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ALL-IN EXPANSION CAPEX (Net of Deductible VAT)</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>359,970.00 EUR</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>179,985.00 EUR all-in per suite</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>5-Year Post-Tax IRR with Exit (8.5% Cap Rate)</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>40.29%</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>MOIC: 4.37x</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Financing Structure (Zero New Senior Debt)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>100% Retained Cash</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Year 2 LEADER (163k) + VAT Refund (152.2k)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Consolidated Group EBITDA (Phase 1 + 2)</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>188,760.39 EUR</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>+111.76% surge vs Phase 1 baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Consolidated Debt Service Coverage (DSCR)</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>4.34x</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Expands from 2.05x to 4.34x (Zero debt add)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>3. 5-YEAR COMMERCIAL RAMP-UP &amp; CASH FLOW TRAJECTORY SCHEDULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Occupancy (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Nights Sold</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ADR Net (EUR)</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Revenue (EUR)</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Contr Margin (EUR)</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA (EUR)</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>EBIT (EUR)</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Tax 25% (EUR)</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>Net Income (EUR)</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>Free Cash Flow (EUR)</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Discounted FCF (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>273.75</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>109636.88</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>85515.39</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>71115.39</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>54916.74</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>13729.19</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>41187.56</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>55193.47</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>51105.07</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>131564.25</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>102618.47</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>88218.47</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>72019.82000000001</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>18004.96</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>54014.87</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>67582.23</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>57940.87</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>365</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>146182.5</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>114020.52</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>99620.52</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>83421.88</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>20855.47</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>62566.41</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>75841.41</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>60205.35</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>365</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>295.8</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>149106.15</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>116300.94</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>101612.94</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>85414.28999999999</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>21353.57</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>64060.71</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>77277.24000000001</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>56801.08</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>365</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>301.72</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>152088.27</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>118626.95</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>103645.19</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>87446.53999999999</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>21861.64</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>65584.91</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>78741.78999999999</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>53590.34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
+++ b/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Risk &amp; Copula" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Economics &amp; Runway" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase II Expansion" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reform Case" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,11 +28,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.00x"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,11 +71,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00BE123C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001D4ED8"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -100,14 +108,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-        <bgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -143,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,16 +179,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,12 +196,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,12 +216,29 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -573,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -761,425 +792,448 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Reform Case</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Separate post-decline layer: R1-R6 presets, value bridge, CapEx/cover frontier, stress tests and recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>2. THREE CASES (DO NOT CONFUSE THEM)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Revenue Y1</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>EBITDA Y1</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>DSCR Y1</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Use</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Management (upside)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>31.36%</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>154548</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>24279.92</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Headline case: 31.36% mature occupancy, 1.48x the INE market average.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>INE market</t>
+          <t>Management (upside)</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>21.24%</t>
+          <t>31.36%</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>95555</v>
+        <v>154548</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>-18565.58</v>
+        <v>24279.92</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-1.46</v>
+        <v>1.34</v>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Independent benchmark: EBITDA is negative in Year 1 and does not cover debt service.</t>
+          <t>Headline case: 31.36% mature occupancy, 1.48x the INE market average.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>INE market</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>21.24%</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>95555</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>-18565.58</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Independent benchmark: EBITDA is negative in Year 1 and does not cover debt service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>Promoter (original Excel)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>19.20%</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C24" s="8" t="n">
         <v>86275</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D24" s="8" t="n">
         <v>11297</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E24" s="9" t="n">
         <v>0.33</v>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Faithful replication of the author's original university simulator.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>3. KEY INTEGRITY CHECKS (LIVE FORMULAS)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Where</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Assets = liabilities + equity (max absolute)</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Live Model!B62:F62</t>
-        </is>
-      </c>
-      <c r="C27" s="10">
-        <f>IF(MAX(ABS('Live Model'!B62),ABS('Live Model'!C62),ABS('Live Model'!D62),ABS('Live Model'!E62),ABS('Live Model'!F62))&lt;1,"PASS","FAIL")</f>
-        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Live revenue vs. Python (Year 1)</t>
+          <t>Assets = liabilities + equity (max absolute)</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Live Model!E66</t>
+          <t>Live Model!B62:F62</t>
         </is>
       </c>
       <c r="C28" s="10">
-        <f>'Live Model'!E66</f>
+        <f>IF(MAX(ABS('Live Model'!B62),ABS('Live Model'!C62),ABS('Live Model'!D62),ABS('Live Model'!E62),ABS('Live Model'!F62))&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Live EBITDA vs. Python (Year 1)</t>
+          <t>Live revenue vs. Python (Year 1)</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Live Model!E67</t>
+          <t>Live Model!E66</t>
         </is>
       </c>
       <c r="C29" s="10">
-        <f>'Live Model'!E67</f>
+        <f>'Live Model'!E66</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Live DSCR vs. Python (Year 2, binding year)</t>
+          <t>Live EBITDA vs. Python (Year 1)</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Live Model!E68</t>
+          <t>Live Model!E67</t>
         </is>
       </c>
       <c r="C30" s="10">
-        <f>'Live Model'!E68</f>
+        <f>'Live Model'!E67</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Live ending cash vs. Python (Year 1)</t>
+          <t>Live DSCR vs. Python (Year 2, binding year)</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Live Model!E69</t>
+          <t>Live Model!E68</t>
         </is>
       </c>
       <c r="C31" s="10">
-        <f>'Live Model'!E69</f>
+        <f>'Live Model'!E68</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Live ending cash vs. Python (Year 2)</t>
+          <t>Live ending cash vs. Python (Year 1)</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Live Model!E70</t>
+          <t>Live Model!E69</t>
         </is>
       </c>
       <c r="C32" s="10">
-        <f>'Live Model'!E70</f>
+        <f>'Live Model'!E69</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Live net income vs. Python (Year 1)</t>
+          <t>Live ending cash vs. Python (Year 2)</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Live Model!E71</t>
+          <t>Live Model!E70</t>
         </is>
       </c>
       <c r="C33" s="10">
-        <f>'Live Model'!E71</f>
+        <f>'Live Model'!E70</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>DSCR covenant (minimum of Years 1-5 &gt;= 1.25x)</t>
+          <t>Live net income vs. Python (Year 1)</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Live Model!E74</t>
+          <t>Live Model!E71</t>
         </is>
       </c>
       <c r="C34" s="10">
-        <f>'Live Model'!E74</f>
+        <f>'Live Model'!E71</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Senior debt fully amortised by month 240</t>
+          <t>DSCR covenant (minimum of Years 1-5 &gt;= 1.25x)</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Debt Schedule!G264</t>
+          <t>Live Model!E74</t>
         </is>
       </c>
       <c r="C35" s="10">
-        <f>IF(ABS('Debt Schedule'!G264)&lt;1,"PASS","FAIL")</f>
+        <f>'Live Model'!E74</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Sources equal uses at close (management)</t>
+          <t>Senior debt fully amortised by month 240</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Funding &amp; Audit!B27</t>
+          <t>Debt Schedule!G264</t>
         </is>
       </c>
       <c r="C36" s="10">
-        <f>IF(ABS('Funding &amp; Audit'!B27)&lt;1,"PASS","FAIL")</f>
+        <f>IF(ABS('Debt Schedule'!G264)&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>VAT bridge within the EUR 175k limit</t>
+          <t>Sources equal uses at close (management)</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Funding &amp; Audit!B23</t>
+          <t>Funding &amp; Audit!B27</t>
         </is>
       </c>
       <c r="C37" s="10">
-        <f>IF('Funding &amp; Audit'!B23&lt;=175000,"PASS","FAIL")</f>
+        <f>IF(ABS('Funding &amp; Audit'!B27)&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
+          <t>VAT bridge within the EUR 175k limit</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Funding &amp; Audit!B23</t>
+        </is>
+      </c>
+      <c r="C38" s="10">
+        <f>IF('Funding &amp; Audit'!B23&lt;=175000,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
           <t>Phase II phase gate</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Funding &amp; Audit!B38</t>
         </is>
       </c>
-      <c r="C38" s="10">
+      <c r="C39" s="10">
         <f>'Funding &amp; Audit'!B38</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>4. HEADLINE FINDINGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>- The all-in asset cost is EUR 1,050,100 (land, 550 m2 of works, kitchen, FF&amp;E, biopool, digital, fees and contingency). The cash equity plug is EUR 521,090.22, or 49.6% of CapEx, not the 30% in the business plan.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>- The EUR 367,535 facility is 35% LTV, but the binding constraint is the DSCR: the 1.25x cap supports EUR 339,144.92 (32.3% LTV). The requested loan breaches the covenant in Year 2 (1.15x).</t>
+          <t>- The all-in asset cost is EUR 1,050,100 (land, 550 m2 of works, kitchen, FF&amp;E, biopool, digital, fees and contingency). The cash equity plug is EUR 521,090.22, or 49.6% of CapEx, not the 30% in the business plan.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>- The independent INE market case (21.24%) is negative at EBITDA level in Year 1 (EUR -18,565.58) and its DSCR is -1.46x.</t>
+          <t>- The EUR 367,535 facility is 35% LTV, but the binding constraint is the DSCR: the 1.25x cap supports EUR 339,144.92 (32.3% LTV). The requested loan breaches the covenant in Year 2 (1.15x).</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>- The original promoter case (19.2%) replicates the author's university Excel (EUR 86,275 revenue / EUR 11,297 EBITDA) and is structurally insolvent at the debt service level.</t>
+          <t>- The independent INE market case (21.24%) is negative at EBITDA level in Year 1 (EUR -18,565.58) and its DSCR is -1.46x.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>- Phase II needs EUR 435,563.70 but Phase I generates EUR 183,322.64 of cash by the end of Year 2: the gate is negative by EUR 252,241.06.</t>
+          <t>- The original promoter case (19.2%) replicates the author's university Excel (EUR 86,275 revenue / EUR 11,297 EBITDA) and is structurally insolvent at the debt service level.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>- The credit-committee recommendation is DECLINE AS STRUCTURED (RESIZE REQUIRED). The covenant break-even is 32.05% occupancy or an ADR of EUR 86.64; a 10% equity IRR needs EUR 116.36.</t>
+          <t>- Phase II needs EUR 435,563.70 but Phase I generates EUR 183,322.64 of cash by the end of Year 2: the gate is negative by EUR 252,241.06.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>- The Clayton copula puts P(breach of 1.25x) at 50.7% and the worst-1% annual CFADS shortfall at EUR 62,786 against a EUR 13,824 contractual DSRA.</t>
+          <t>- The credit-committee recommendation is DECLINE AS STRUCTURED (RESIZE REQUIRED). The covenant break-even is 32.05% occupancy or an ADR of EUR 86.64; a 10% equity IRR needs EUR 116.36.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
+          <t>- The Clayton copula puts P(breach of 1.25x) at 50.7% and the worst-1% annual CFADS shortfall at EUR 62,786 against a EUR 13,824 contractual DSRA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>- The separate reform / resize layer is also negative: six external F&amp;B covers, +5% ADR and one extra FTE lift mature EBITDA to EUR 71,321 and asset value to EUR 839,075, still EUR 211,025 below the 1.05M CapEx and EUR 299,550 below total project investment. Only the aggressive eight-cover / +10% ADR corner clears 8%, and it still fails the bank test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
           <t>- The model is deliberately honest: the business does not earn its 8.5% cost of capital at the planned occupancy and ADR, and the workbook says so rather than hiding it.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>5. DISCLAIMER</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="44" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>This is a portfolio model built from the author's own university work, public INE data and public convenio tables. It is not investment advice. The management case is an upside case; the market and promoter cases are the honest downside anchors.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A51:F51"/>
+  <mergeCells count="10">
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A43:F43"/>
   </mergeCells>
@@ -4181,6 +4235,1102 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>REFORM / RESIZE CASE - WHAT WOULD HAVE TO BE TRUE AFTER THE DECLINE?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>A separate layer on top of the three as-is cases. It does not rewrite the management, INE market or promoter projections; it asks whether a revenue-led reform can create value. The answer is allowed to be no, and the conservative bank test is EV versus TOTAL project investment (CapEx + IDC + pre-opening + working capital + DSRA), not EV versus CapEx alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1. R1-R6 REFORM PRESETS (ALL SIX ARE SHOWN; NEGATIVE RESULTS ARE NOT HIDDEN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>Reform case</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>CapEx (EUR)</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>Total investment (EUR)</t>
+        </is>
+      </c>
+      <c r="E5" s="42" t="inlineStr">
+        <is>
+          <t>Revenue Y5 (EUR)</t>
+        </is>
+      </c>
+      <c r="F5" s="42" t="inlineStr">
+        <is>
+          <t>EBITDA Y5 (EUR)</t>
+        </is>
+      </c>
+      <c r="G5" s="42" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="H5" s="42" t="inlineStr">
+        <is>
+          <t>EV @ exit cap (EUR)</t>
+        </is>
+      </c>
+      <c r="I5" s="42" t="inlineStr">
+        <is>
+          <t>Gap vs CapEx (EUR)</t>
+        </is>
+      </c>
+      <c r="J5" s="42" t="inlineStr">
+        <is>
+          <t>Gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="K5" s="42" t="inlineStr">
+        <is>
+          <t>Project NPV (EUR)</t>
+        </is>
+      </c>
+      <c r="L5" s="42" t="inlineStr">
+        <is>
+          <t>Project IRR</t>
+        </is>
+      </c>
+      <c r="M5" s="42" t="inlineStr">
+        <is>
+          <t>Equity IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>CAPEX ONLY</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>R1 Capital-only (900k)</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>901800</v>
+      </c>
+      <c r="D6" s="40" t="n">
+        <v>986296.85</v>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>171720</v>
+      </c>
+      <c r="F6" s="40" t="n">
+        <v>37041.58</v>
+      </c>
+      <c r="G6" s="43" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H6" s="40" t="n">
+        <v>435783.29</v>
+      </c>
+      <c r="I6" s="40" t="n">
+        <v>-466016.71</v>
+      </c>
+      <c r="J6" s="40" t="n">
+        <v>-550513.5600000001</v>
+      </c>
+      <c r="K6" s="40" t="n">
+        <v>-450358.56</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>-0.07178</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>-0.164716</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>REVENUE REFORM</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>R2 Revenue reform (1.05M)</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="n">
+        <v>1050100</v>
+      </c>
+      <c r="D7" s="40" t="n">
+        <v>1138625.22</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>253626</v>
+      </c>
+      <c r="F7" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="G7" s="43" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H7" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="I7" s="40" t="n">
+        <v>-211025.06</v>
+      </c>
+      <c r="J7" s="40" t="n">
+        <v>-299550.28</v>
+      </c>
+      <c r="K7" s="40" t="n">
+        <v>-220684.83</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.025297</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0.019578</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>VALUE ENGINEERED</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>R3 Revenue + value engineering (900k)</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>901800</v>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>986296.85</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>253626</v>
+      </c>
+      <c r="F8" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="G8" s="43" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H8" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>-62725.06</v>
+      </c>
+      <c r="J8" s="40" t="n">
+        <v>-147221.91</v>
+      </c>
+      <c r="K8" s="40" t="n">
+        <v>-96377.5</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.053742</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.06250600000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>AGGRESSIVE</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>R4 Aggressive demand (1.05M)</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>1050100</v>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>1138625.22</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>282652</v>
+      </c>
+      <c r="F9" s="40" t="n">
+        <v>92402.75999999999</v>
+      </c>
+      <c r="G9" s="43" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H9" s="40" t="n">
+        <v>1087091.29</v>
+      </c>
+      <c r="I9" s="40" t="n">
+        <v>36991.29</v>
+      </c>
+      <c r="J9" s="40" t="n">
+        <v>-51533.93</v>
+      </c>
+      <c r="K9" s="40" t="n">
+        <v>3721.66</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0.080844</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0.101638</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>RESIZE 850</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>R5 Lean scope (850k)</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="n">
+        <v>846300</v>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>929289.3100000001</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>253626</v>
+      </c>
+      <c r="F10" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="G10" s="43" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H10" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="I10" s="40" t="n">
+        <v>-7225.06</v>
+      </c>
+      <c r="J10" s="40" t="n">
+        <v>-90214.37</v>
+      </c>
+      <c r="K10" s="40" t="n">
+        <v>-49105.91</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.066093</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.080399</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>DOWNSIDE</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>R6 Downside / stress</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="n">
+        <v>965560</v>
+      </c>
+      <c r="D11" s="40" t="n">
+        <v>1051789.19</v>
+      </c>
+      <c r="E11" s="40" t="n">
+        <v>187923</v>
+      </c>
+      <c r="F11" s="40" t="n">
+        <v>2670.95</v>
+      </c>
+      <c r="G11" s="43" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H11" s="40" t="n">
+        <v>26709.5</v>
+      </c>
+      <c r="I11" s="40" t="n">
+        <v>-938850.5</v>
+      </c>
+      <c r="J11" s="40" t="n">
+        <v>-1025079.69</v>
+      </c>
+      <c r="K11" s="40" t="n">
+        <v>-906165.55</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>-0.377608</v>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2. R2 VALUE BRIDGE - MATURE EBITDA AND EV AT THE 8.5% EXIT CAP RATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>Bridge component</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>EBITDA impact (EUR)</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="inlineStr">
+        <is>
+          <t>EV impact @ 8.5% (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Base management EBITDA</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="n">
+        <v>37041.58</v>
+      </c>
+      <c r="C16" s="45" t="n">
+        <v>435783.29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>+ ADR uplift (5%)</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="n">
+        <v>7182.19</v>
+      </c>
+      <c r="C17" s="40" t="n">
+        <v>84496.35000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>+ External F&amp;B (6 covers/day)</t>
+        </is>
+      </c>
+      <c r="B18" s="40" t="n">
+        <v>13697.6</v>
+      </c>
+      <c r="C18" s="40" t="n">
+        <v>161148.24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>+ Experiences</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C19" s="40" t="n">
+        <v>98823.53</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>+ Cost savings</t>
+        </is>
+      </c>
+      <c r="B20" s="40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C20" s="40" t="n">
+        <v>58823.53</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Reform EBITDA and EV</t>
+        </is>
+      </c>
+      <c r="B21" s="45" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="C21" s="45" t="n">
+        <v>839074.9399999999</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Reform enterprise value @ 8.5%</t>
+        </is>
+      </c>
+      <c r="B23" s="45" t="n">
+        <v>839074.9399999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Reform CapEx</t>
+        </is>
+      </c>
+      <c r="B24" s="45" t="n">
+        <v>1050100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Value gap vs CapEx</t>
+        </is>
+      </c>
+      <c r="B25" s="45" t="n">
+        <v>-211025.06</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Total project investment</t>
+        </is>
+      </c>
+      <c r="B26" s="45" t="n">
+        <v>1138625.22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>3. VALUE FRONTIER - EV MINUS TOTAL INVESTMENT (EUR), BY CAPEX AND EXTERNAL COVERS</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="n">
+        <v>-299550.28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="46" t="inlineStr">
+        <is>
+          <t>CapEx (EUR) \ Covers/day</t>
+        </is>
+      </c>
+      <c r="B28" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="48" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="45" t="n">
+        <v>1050100</v>
+      </c>
+      <c r="B29" s="49" t="n">
+        <v>-460698.51</v>
+      </c>
+      <c r="C29" s="49" t="n">
+        <v>-544830.28</v>
+      </c>
+      <c r="D29" s="49" t="n">
+        <v>-299550.28</v>
+      </c>
+      <c r="E29" s="49" t="n">
+        <v>-245834.16</v>
+      </c>
+      <c r="F29" s="49" t="n">
+        <v>-192118.16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="n">
+        <v>950000</v>
+      </c>
+      <c r="B30" s="49" t="n">
+        <v>-357879.98</v>
+      </c>
+      <c r="C30" s="49" t="n">
+        <v>-442011.75</v>
+      </c>
+      <c r="D30" s="49" t="n">
+        <v>-196731.75</v>
+      </c>
+      <c r="E30" s="49" t="n">
+        <v>-143015.63</v>
+      </c>
+      <c r="F30" s="49" t="n">
+        <v>-89299.63</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="45" t="n">
+        <v>850000</v>
+      </c>
+      <c r="B31" s="49" t="n">
+        <v>-255162.93</v>
+      </c>
+      <c r="C31" s="49" t="n">
+        <v>-339294.7</v>
+      </c>
+      <c r="D31" s="49" t="n">
+        <v>-94014.7</v>
+      </c>
+      <c r="E31" s="49" t="n">
+        <v>-40298.58</v>
+      </c>
+      <c r="F31" s="50" t="n">
+        <v>13417.42</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="n">
+        <v>770000</v>
+      </c>
+      <c r="B32" s="49" t="n">
+        <v>-172989.81</v>
+      </c>
+      <c r="C32" s="49" t="n">
+        <v>-257121.58</v>
+      </c>
+      <c r="D32" s="49" t="n">
+        <v>-11841.58</v>
+      </c>
+      <c r="E32" s="50" t="n">
+        <v>41874.54</v>
+      </c>
+      <c r="F32" s="50" t="n">
+        <v>95590.53999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="45" t="n">
+        <v>700000</v>
+      </c>
+      <c r="B33" s="49" t="n">
+        <v>-101088.63</v>
+      </c>
+      <c r="C33" s="49" t="n">
+        <v>-185220.4</v>
+      </c>
+      <c r="D33" s="50" t="n">
+        <v>60059.6</v>
+      </c>
+      <c r="E33" s="50" t="n">
+        <v>113775.72</v>
+      </c>
+      <c r="F33" s="50" t="n">
+        <v>167491.72</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>4. STRESS TESTS - THE REFORM UNDER DEMAND, COST, RATE AND GRANT DELAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Stress case</t>
+        </is>
+      </c>
+      <c r="B37" s="51" t="inlineStr">
+        <is>
+          <t>CapEx (EUR)</t>
+        </is>
+      </c>
+      <c r="C37" s="51" t="inlineStr">
+        <is>
+          <t>Total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="D37" s="51" t="inlineStr">
+        <is>
+          <t>EBITDA Y5 (EUR)</t>
+        </is>
+      </c>
+      <c r="E37" s="51" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="F37" s="51" t="inlineStr">
+        <is>
+          <t>EV (EUR)</t>
+        </is>
+      </c>
+      <c r="G37" s="51" t="inlineStr">
+        <is>
+          <t>Gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="H37" s="51" t="inlineStr">
+        <is>
+          <t>Project NPV (EUR)</t>
+        </is>
+      </c>
+      <c r="I37" s="51" t="inlineStr">
+        <is>
+          <t>Project IRR</t>
+        </is>
+      </c>
+      <c r="J37" s="51" t="inlineStr">
+        <is>
+          <t>Equity IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>As-is reform (R2)</t>
+        </is>
+      </c>
+      <c r="B38" s="40" t="n">
+        <v>1050100</v>
+      </c>
+      <c r="C38" s="40" t="n">
+        <v>1138625.22</v>
+      </c>
+      <c r="D38" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="E38" s="43" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="F38" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="G38" s="40" t="n">
+        <v>-299550.28</v>
+      </c>
+      <c r="H38" s="40" t="n">
+        <v>-220684.83</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>0.025297</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>0.019578</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>R2 + INE 21.24% demand</t>
+        </is>
+      </c>
+      <c r="B39" s="40" t="n">
+        <v>1050100</v>
+      </c>
+      <c r="C39" s="40" t="n">
+        <v>1138625.22</v>
+      </c>
+      <c r="D39" s="40" t="n">
+        <v>27821.26</v>
+      </c>
+      <c r="E39" s="43" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F39" s="40" t="n">
+        <v>327308.94</v>
+      </c>
+      <c r="G39" s="40" t="n">
+        <v>-811316.28</v>
+      </c>
+      <c r="H39" s="40" t="n">
+        <v>-689417.96</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>-0.14632</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>-0.512092</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>R2 + covers -50%</t>
+        </is>
+      </c>
+      <c r="B40" s="40" t="n">
+        <v>1050100</v>
+      </c>
+      <c r="C40" s="40" t="n">
+        <v>1138625.22</v>
+      </c>
+      <c r="D40" s="40" t="n">
+        <v>50472.57</v>
+      </c>
+      <c r="E40" s="43" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F40" s="40" t="n">
+        <v>593794.9399999999</v>
+      </c>
+      <c r="G40" s="40" t="n">
+        <v>-544830.28</v>
+      </c>
+      <c r="H40" s="40" t="n">
+        <v>-441028.47</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>-0.042221</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>-0.102545</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>R3 + CapEx +20%</t>
+        </is>
+      </c>
+      <c r="B41" s="40" t="n">
+        <v>1032160</v>
+      </c>
+      <c r="C41" s="40" t="n">
+        <v>1120197.9</v>
+      </c>
+      <c r="D41" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="E41" s="43" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F41" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="G41" s="40" t="n">
+        <v>-281122.96</v>
+      </c>
+      <c r="H41" s="40" t="n">
+        <v>-206843.7</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>0.028168</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>0.024049</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>R3 + LEADER delayed to Y3</t>
+        </is>
+      </c>
+      <c r="B42" s="40" t="n">
+        <v>901800</v>
+      </c>
+      <c r="C42" s="40" t="n">
+        <v>986296.85</v>
+      </c>
+      <c r="D42" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="E42" s="43" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F42" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="G42" s="40" t="n">
+        <v>-147221.91</v>
+      </c>
+      <c r="H42" s="40" t="n">
+        <v>-105254.39</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>0.052156</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>0.059813</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>R3 + rate +200 bp</t>
+        </is>
+      </c>
+      <c r="B43" s="40" t="n">
+        <v>901800</v>
+      </c>
+      <c r="C43" s="40" t="n">
+        <v>988365</v>
+      </c>
+      <c r="D43" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="E43" s="43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F43" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="G43" s="40" t="n">
+        <v>-149290.06</v>
+      </c>
+      <c r="H43" s="40" t="n">
+        <v>-98445.64999999999</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>0.053216</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>0.054386</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>R3 + conservative demand</t>
+        </is>
+      </c>
+      <c r="B44" s="40" t="n">
+        <v>901800</v>
+      </c>
+      <c r="C44" s="40" t="n">
+        <v>987831.24</v>
+      </c>
+      <c r="D44" s="40" t="n">
+        <v>33333.95</v>
+      </c>
+      <c r="E44" s="43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F44" s="40" t="n">
+        <v>392164.12</v>
+      </c>
+      <c r="G44" s="40" t="n">
+        <v>-595667.12</v>
+      </c>
+      <c r="H44" s="40" t="n">
+        <v>-509916.1</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>-0.096315</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>-0.245461</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>R6 combined downside</t>
+        </is>
+      </c>
+      <c r="B45" s="40" t="n">
+        <v>965560</v>
+      </c>
+      <c r="C45" s="40" t="n">
+        <v>1051789.19</v>
+      </c>
+      <c r="D45" s="40" t="n">
+        <v>-33876</v>
+      </c>
+      <c r="E45" s="43" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="F45" s="40" t="n">
+        <v>-338760</v>
+      </c>
+      <c r="G45" s="40" t="n">
+        <v>-1390549.19</v>
+      </c>
+      <c r="H45" s="40" t="n">
+        <v>-1242114.7</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>5. REFORM RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="52" t="inlineStr">
+        <is>
+          <t>DECLINE AS STRUCTURED - ONLY THE AGGRESSIVE, UNPROVEN DEMAND CASE CLEARS THE WACC</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>The realistic revenue reform (R2: six external covers/day, +5% ADR, one FTE) produces EUR 71,321 of mature EBITDA and EUR 839,075 of asset value. Against the EUR 1,050,100 CapEx that is a gap of EUR -211,025; against total project investment of EUR 1,138,625 the gap is EUR -299,550. R2 still has a project NPV of EUR -220,685 and a project IRR of 2.53%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>The 900k value-engineered case (R3) improves the NPV to EUR -96,378 and the IRR to 5.37%, but still does not clear an 8% WACC. The 850k lean case (R5) reaches EUR -49,106 of NPV and 6.61% IRR, still below the hurdle. The only positive-NPV case is R4 (eight covers/day, +10% ADR, one FTE) at EUR 3,722 of NPV and 8.08% IRR - a negligible margin and a total-investment value gap of EUR -51,534. The combined downside (R6) is deeply negative: EBITDA EUR 2,671, NPV EUR -906,166. The value frontier does show a positive corner at roughly EUR 700k of CapEx (land included) with six or more covers, but that is EUR 450k of non-land spend for an eight-room refurbishment: a scope-reduction thesis, not the current 1.05M budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Conditions attached to any further work</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>- Do not treat the 1.05M eight-room project as the base case for a reform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>- Prove external F&amp;B demand before committing construction capital: a low-cost Phase 0 pop-up/restaurant test, not a full refurbishment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>- If the family wants to proceed, cap the initial capital at the lean scope and keep the second phase behind a demand gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>- Treat the ~700k frontier corner as a different, smaller project: it only works by cutting the non-land budget to about 450k, which is not the eight-room refurbishment currently specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>- Charge the land at its opportunity value; do not describe the project as viable only because the site is already owned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>- Re-run the model with 1.25-1.5 FTE for the external covers, not one FTE, and with INE 21.24% occupancy in the downside.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A57:L57"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A54:L54"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A49:L49"/>
+    <mergeCell ref="A58:L58"/>
+    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="A55:L55"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="A59:L59"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
+++ b/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
@@ -157,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -230,14 +230,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -604,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1137,11 +1136,8 @@
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="n"/>
-    </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>4. HEADLINE FINDINGS</t>
         </is>
@@ -1206,31 +1202,47 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
+          <t>- The management case is 31.36% occupancy, 1.48x the INE 21.24%. It is a weekend-weighted mix, not a flat uplift: 72% weekends, 65% holiday bridges and 10% midweek reconstruct the annual target. 68% of the gap is weekend capture; the thin midweek is what the reform's external F&amp;B covers are trying to fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>- The exit is shown gross and net of 3% selling costs. R2's net value gap is EUR 324,723 against total investment; even the aggressive R4 corner fails the net test at EUR 84,147.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
           <t>- The model is deliberately honest: the business does not earn its 8.5% cost of capital at the planned occupancy and ADR, and the workbook says so rather than hiding it.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>5. DISCLAIMER</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="44" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+    <row r="54" ht="44" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>This is a portfolio model built from the author's own university work, public INE data and public convenio tables. It is not investment advice. The management case is an upside case; the market and promoter cases are the honest downside anchors.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A50:F50"/>
@@ -4245,22 +4257,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4338,15 +4351,20 @@
       </c>
       <c r="K5" s="42" t="inlineStr">
         <is>
+          <t>Net gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="L5" s="42" t="inlineStr">
+        <is>
           <t>Project NPV (EUR)</t>
         </is>
       </c>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="M5" s="42" t="inlineStr">
         <is>
           <t>Project IRR</t>
         </is>
       </c>
-      <c r="M5" s="42" t="inlineStr">
+      <c r="N5" s="42" t="inlineStr">
         <is>
           <t>Equity IRR</t>
         </is>
@@ -4388,12 +4406,15 @@
         <v>-550513.5600000001</v>
       </c>
       <c r="K6" s="40" t="n">
+        <v>-563587.0600000001</v>
+      </c>
+      <c r="L6" s="40" t="n">
         <v>-450358.56</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="M6" s="7" t="n">
         <v>-0.07178</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="N6" s="7" t="n">
         <v>-0.164716</v>
       </c>
     </row>
@@ -4433,12 +4454,15 @@
         <v>-299550.28</v>
       </c>
       <c r="K7" s="40" t="n">
+        <v>-324722.53</v>
+      </c>
+      <c r="L7" s="40" t="n">
         <v>-220684.83</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="M7" s="7" t="n">
         <v>0.025297</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="N7" s="7" t="n">
         <v>0.019578</v>
       </c>
     </row>
@@ -4478,12 +4502,15 @@
         <v>-147221.91</v>
       </c>
       <c r="K8" s="40" t="n">
+        <v>-172394.16</v>
+      </c>
+      <c r="L8" s="40" t="n">
         <v>-96377.5</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="M8" s="7" t="n">
         <v>0.053742</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="N8" s="7" t="n">
         <v>0.06250600000000001</v>
       </c>
     </row>
@@ -4523,12 +4550,15 @@
         <v>-51533.93</v>
       </c>
       <c r="K9" s="40" t="n">
+        <v>-84146.67</v>
+      </c>
+      <c r="L9" s="40" t="n">
         <v>3721.66</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="M9" s="7" t="n">
         <v>0.080844</v>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="N9" s="7" t="n">
         <v>0.101638</v>
       </c>
     </row>
@@ -4568,12 +4598,15 @@
         <v>-90214.37</v>
       </c>
       <c r="K10" s="40" t="n">
+        <v>-115386.62</v>
+      </c>
+      <c r="L10" s="40" t="n">
         <v>-49105.91</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="M10" s="7" t="n">
         <v>0.066093</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="N10" s="7" t="n">
         <v>0.080399</v>
       </c>
     </row>
@@ -4595,30 +4628,35 @@
         <v>1051789.19</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>187923</v>
+        <v>138035.1</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>2670.95</v>
+        <v>-33886.72</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-1.49</v>
+        <v>-3.82</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>26709.5</v>
+        <v>0</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>-938850.5</v>
+        <v>-965560</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>-1025079.69</v>
+        <v>-1051789.19</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>-906165.55</v>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>-0.377608</v>
+        <v>-1051789.19</v>
+      </c>
+      <c r="L11" s="40" t="n">
+        <v>-1021972.82</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -4730,606 +4768,868 @@
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Reform enterprise value @ 8.5%</t>
-        </is>
-      </c>
-      <c r="B23" s="45" t="n">
-        <v>839074.9399999999</v>
+      <c r="A23" s="46" t="inlineStr">
+        <is>
+          <t>Value test</t>
+        </is>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>Gross (EUR)</t>
+        </is>
+      </c>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>Net of exit costs (EUR)</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Reform CapEx</t>
+          <t>Enterprise value</t>
         </is>
       </c>
       <c r="B24" s="45" t="n">
-        <v>1050100</v>
+        <v>839074.9399999999</v>
+      </c>
+      <c r="C24" s="45" t="n">
+        <v>813902.6899999999</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Value gap vs CapEx</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Exit costs</t>
         </is>
       </c>
       <c r="B25" s="45" t="n">
-        <v>-211025.06</v>
+        <v>0</v>
+      </c>
+      <c r="C25" s="45" t="n">
+        <v>-25172.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Total project investment</t>
+          <t>Reform CapEx</t>
         </is>
       </c>
       <c r="B26" s="45" t="n">
-        <v>1138625.22</v>
+        <v>1050100</v>
+      </c>
+      <c r="C26" s="45" t="n">
+        <v>1050100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>Value gap vs CapEx</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="n">
+        <v>-211025.06</v>
+      </c>
+      <c r="C27" s="45" t="n">
+        <v>-236197.31</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Total project investment</t>
+        </is>
+      </c>
+      <c r="B28" s="45" t="n">
+        <v>1138625.22</v>
+      </c>
+      <c r="C28" s="45" t="n">
+        <v>1138625.22</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Value gap vs total investment</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="n">
+        <v>-299550.28</v>
+      </c>
+      <c r="C29" s="45" t="n">
+        <v>-324722.53</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Bridge tie (must be zero)</t>
+        </is>
+      </c>
+      <c r="B30" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>3. VALUE FRONTIER - EV MINUS TOTAL INVESTMENT (EUR), BY CAPEX AND EXTERNAL COVERS</t>
         </is>
       </c>
-      <c r="B27" s="45" t="n">
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>CapEx (EUR) \ Covers/day</t>
+        </is>
+      </c>
+      <c r="B34" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="47" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="45" t="n">
+        <v>1050100</v>
+      </c>
+      <c r="B35" s="48" t="n">
+        <v>-460698.51</v>
+      </c>
+      <c r="C35" s="48" t="n">
+        <v>-544830.28</v>
+      </c>
+      <c r="D35" s="48" t="n">
         <v>-299550.28</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="46" t="inlineStr">
-        <is>
-          <t>CapEx (EUR) \ Covers/day</t>
-        </is>
-      </c>
-      <c r="B28" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="48" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="48" t="n">
-        <v>8</v>
-      </c>
-      <c r="F28" s="48" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="45" t="n">
-        <v>1050100</v>
-      </c>
-      <c r="B29" s="49" t="n">
-        <v>-460698.51</v>
-      </c>
-      <c r="C29" s="49" t="n">
-        <v>-544830.28</v>
-      </c>
-      <c r="D29" s="49" t="n">
-        <v>-299550.28</v>
-      </c>
-      <c r="E29" s="49" t="n">
+      <c r="E35" s="48" t="n">
         <v>-245834.16</v>
       </c>
-      <c r="F29" s="49" t="n">
+      <c r="F35" s="48" t="n">
         <v>-192118.16</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="45" t="n">
+    <row r="36">
+      <c r="A36" s="45" t="n">
         <v>950000</v>
       </c>
-      <c r="B30" s="49" t="n">
+      <c r="B36" s="48" t="n">
         <v>-357879.98</v>
       </c>
-      <c r="C30" s="49" t="n">
+      <c r="C36" s="48" t="n">
         <v>-442011.75</v>
       </c>
-      <c r="D30" s="49" t="n">
+      <c r="D36" s="48" t="n">
         <v>-196731.75</v>
       </c>
-      <c r="E30" s="49" t="n">
+      <c r="E36" s="48" t="n">
         <v>-143015.63</v>
       </c>
-      <c r="F30" s="49" t="n">
+      <c r="F36" s="48" t="n">
         <v>-89299.63</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="45" t="n">
+    <row r="37">
+      <c r="A37" s="45" t="n">
         <v>850000</v>
       </c>
-      <c r="B31" s="49" t="n">
+      <c r="B37" s="48" t="n">
         <v>-255162.93</v>
       </c>
-      <c r="C31" s="49" t="n">
+      <c r="C37" s="48" t="n">
         <v>-339294.7</v>
       </c>
-      <c r="D31" s="49" t="n">
+      <c r="D37" s="48" t="n">
         <v>-94014.7</v>
       </c>
-      <c r="E31" s="49" t="n">
+      <c r="E37" s="48" t="n">
         <v>-40298.58</v>
       </c>
-      <c r="F31" s="50" t="n">
+      <c r="F37" s="49" t="n">
         <v>13417.42</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="45" t="n">
+    <row r="38">
+      <c r="A38" s="45" t="n">
         <v>770000</v>
       </c>
-      <c r="B32" s="49" t="n">
+      <c r="B38" s="48" t="n">
         <v>-172989.81</v>
       </c>
-      <c r="C32" s="49" t="n">
+      <c r="C38" s="48" t="n">
         <v>-257121.58</v>
       </c>
-      <c r="D32" s="49" t="n">
+      <c r="D38" s="48" t="n">
         <v>-11841.58</v>
       </c>
-      <c r="E32" s="50" t="n">
+      <c r="E38" s="49" t="n">
         <v>41874.54</v>
       </c>
-      <c r="F32" s="50" t="n">
+      <c r="F38" s="49" t="n">
         <v>95590.53999999999</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="45" t="n">
+    <row r="39">
+      <c r="A39" s="45" t="n">
         <v>700000</v>
       </c>
-      <c r="B33" s="49" t="n">
+      <c r="B39" s="48" t="n">
         <v>-101088.63</v>
       </c>
-      <c r="C33" s="49" t="n">
+      <c r="C39" s="48" t="n">
         <v>-185220.4</v>
       </c>
-      <c r="D33" s="50" t="n">
+      <c r="D39" s="49" t="n">
         <v>60059.6</v>
       </c>
-      <c r="E33" s="50" t="n">
+      <c r="E39" s="49" t="n">
         <v>113775.72</v>
       </c>
-      <c r="F33" s="50" t="n">
+      <c r="F39" s="49" t="n">
         <v>167491.72</v>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>4. STRESS TESTS - THE REFORM UNDER DEMAND, COST, RATE AND GRANT DELAYS</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="51" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="46" t="inlineStr">
         <is>
           <t>Stress case</t>
         </is>
       </c>
-      <c r="B37" s="51" t="inlineStr">
+      <c r="B43" s="46" t="inlineStr">
         <is>
           <t>CapEx (EUR)</t>
         </is>
       </c>
-      <c r="C37" s="51" t="inlineStr">
+      <c r="C43" s="46" t="inlineStr">
         <is>
           <t>Total inv. (EUR)</t>
         </is>
       </c>
-      <c r="D37" s="51" t="inlineStr">
+      <c r="D43" s="46" t="inlineStr">
         <is>
           <t>EBITDA Y5 (EUR)</t>
         </is>
       </c>
-      <c r="E37" s="51" t="inlineStr">
+      <c r="E43" s="46" t="inlineStr">
         <is>
           <t>Min DSCR</t>
         </is>
       </c>
-      <c r="F37" s="51" t="inlineStr">
+      <c r="F43" s="46" t="inlineStr">
         <is>
           <t>EV (EUR)</t>
         </is>
       </c>
-      <c r="G37" s="51" t="inlineStr">
+      <c r="G43" s="46" t="inlineStr">
         <is>
           <t>Gap vs total inv. (EUR)</t>
         </is>
       </c>
-      <c r="H37" s="51" t="inlineStr">
+      <c r="H43" s="46" t="inlineStr">
+        <is>
+          <t>Net gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="I43" s="46" t="inlineStr">
         <is>
           <t>Project NPV (EUR)</t>
         </is>
       </c>
-      <c r="I37" s="51" t="inlineStr">
+      <c r="J43" s="46" t="inlineStr">
         <is>
           <t>Project IRR</t>
         </is>
       </c>
-      <c r="J37" s="51" t="inlineStr">
+      <c r="K43" s="46" t="inlineStr">
         <is>
           <t>Equity IRR</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>As-is reform (R2)</t>
-        </is>
-      </c>
-      <c r="B38" s="40" t="n">
-        <v>1050100</v>
-      </c>
-      <c r="C38" s="40" t="n">
-        <v>1138625.22</v>
-      </c>
-      <c r="D38" s="40" t="n">
-        <v>71321.37</v>
-      </c>
-      <c r="E38" s="43" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="F38" s="40" t="n">
-        <v>839074.9399999999</v>
-      </c>
-      <c r="G38" s="40" t="n">
-        <v>-299550.28</v>
-      </c>
-      <c r="H38" s="40" t="n">
-        <v>-220684.83</v>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>0.025297</v>
-      </c>
-      <c r="J38" s="7" t="n">
-        <v>0.019578</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>R2 + INE 21.24% demand</t>
-        </is>
-      </c>
-      <c r="B39" s="40" t="n">
-        <v>1050100</v>
-      </c>
-      <c r="C39" s="40" t="n">
-        <v>1138625.22</v>
-      </c>
-      <c r="D39" s="40" t="n">
-        <v>27821.26</v>
-      </c>
-      <c r="E39" s="43" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="F39" s="40" t="n">
-        <v>327308.94</v>
-      </c>
-      <c r="G39" s="40" t="n">
-        <v>-811316.28</v>
-      </c>
-      <c r="H39" s="40" t="n">
-        <v>-689417.96</v>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>-0.14632</v>
-      </c>
-      <c r="J39" s="7" t="n">
-        <v>-0.512092</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>R2 + covers -50%</t>
-        </is>
-      </c>
-      <c r="B40" s="40" t="n">
-        <v>1050100</v>
-      </c>
-      <c r="C40" s="40" t="n">
-        <v>1138625.22</v>
-      </c>
-      <c r="D40" s="40" t="n">
-        <v>50472.57</v>
-      </c>
-      <c r="E40" s="43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F40" s="40" t="n">
-        <v>593794.9399999999</v>
-      </c>
-      <c r="G40" s="40" t="n">
-        <v>-544830.28</v>
-      </c>
-      <c r="H40" s="40" t="n">
-        <v>-441028.47</v>
-      </c>
-      <c r="I40" s="7" t="n">
-        <v>-0.042221</v>
-      </c>
-      <c r="J40" s="7" t="n">
-        <v>-0.102545</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>R3 + CapEx +20%</t>
-        </is>
-      </c>
-      <c r="B41" s="40" t="n">
-        <v>1032160</v>
-      </c>
-      <c r="C41" s="40" t="n">
-        <v>1120197.9</v>
-      </c>
-      <c r="D41" s="40" t="n">
-        <v>71321.37</v>
-      </c>
-      <c r="E41" s="43" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="F41" s="40" t="n">
-        <v>839074.9399999999</v>
-      </c>
-      <c r="G41" s="40" t="n">
-        <v>-281122.96</v>
-      </c>
-      <c r="H41" s="40" t="n">
-        <v>-206843.7</v>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>0.028168</v>
-      </c>
-      <c r="J41" s="7" t="n">
-        <v>0.024049</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>R3 + LEADER delayed to Y3</t>
-        </is>
-      </c>
-      <c r="B42" s="40" t="n">
-        <v>901800</v>
-      </c>
-      <c r="C42" s="40" t="n">
-        <v>986296.85</v>
-      </c>
-      <c r="D42" s="40" t="n">
-        <v>71321.37</v>
-      </c>
-      <c r="E42" s="43" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="F42" s="40" t="n">
-        <v>839074.9399999999</v>
-      </c>
-      <c r="G42" s="40" t="n">
-        <v>-147221.91</v>
-      </c>
-      <c r="H42" s="40" t="n">
-        <v>-105254.39</v>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>0.052156</v>
-      </c>
-      <c r="J42" s="7" t="n">
-        <v>0.059813</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>R3 + rate +200 bp</t>
-        </is>
-      </c>
-      <c r="B43" s="40" t="n">
-        <v>901800</v>
-      </c>
-      <c r="C43" s="40" t="n">
-        <v>988365</v>
-      </c>
-      <c r="D43" s="40" t="n">
-        <v>71321.37</v>
-      </c>
-      <c r="E43" s="43" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="F43" s="40" t="n">
-        <v>839074.9399999999</v>
-      </c>
-      <c r="G43" s="40" t="n">
-        <v>-149290.06</v>
-      </c>
-      <c r="H43" s="40" t="n">
-        <v>-98445.64999999999</v>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>0.053216</v>
-      </c>
-      <c r="J43" s="7" t="n">
-        <v>0.054386</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>R3 + conservative demand</t>
+          <t>As-is reform (R2)</t>
         </is>
       </c>
       <c r="B44" s="40" t="n">
-        <v>901800</v>
+        <v>1050100</v>
       </c>
       <c r="C44" s="40" t="n">
-        <v>987831.24</v>
+        <v>1138625.22</v>
       </c>
       <c r="D44" s="40" t="n">
-        <v>33333.95</v>
+        <v>71321.37</v>
       </c>
       <c r="E44" s="43" t="n">
-        <v>0.12</v>
+        <v>2.13</v>
       </c>
       <c r="F44" s="40" t="n">
-        <v>392164.12</v>
+        <v>839074.9399999999</v>
       </c>
       <c r="G44" s="40" t="n">
-        <v>-595667.12</v>
+        <v>-299550.28</v>
       </c>
       <c r="H44" s="40" t="n">
-        <v>-509916.1</v>
-      </c>
-      <c r="I44" s="7" t="n">
-        <v>-0.096315</v>
+        <v>-324722.53</v>
+      </c>
+      <c r="I44" s="40" t="n">
+        <v>-220684.83</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>-0.245461</v>
+        <v>0.025297</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>0.019578</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
+          <t>R2 + INE 21.24% demand</t>
+        </is>
+      </c>
+      <c r="B45" s="40" t="n">
+        <v>1050100</v>
+      </c>
+      <c r="C45" s="40" t="n">
+        <v>1138625.22</v>
+      </c>
+      <c r="D45" s="40" t="n">
+        <v>27821.26</v>
+      </c>
+      <c r="E45" s="43" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F45" s="40" t="n">
+        <v>327308.94</v>
+      </c>
+      <c r="G45" s="40" t="n">
+        <v>-811316.28</v>
+      </c>
+      <c r="H45" s="40" t="n">
+        <v>-821135.55</v>
+      </c>
+      <c r="I45" s="40" t="n">
+        <v>-689417.96</v>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>-0.14632</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>-0.512092</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>R2 + covers -50%</t>
+        </is>
+      </c>
+      <c r="B46" s="40" t="n">
+        <v>1050100</v>
+      </c>
+      <c r="C46" s="40" t="n">
+        <v>1138625.22</v>
+      </c>
+      <c r="D46" s="40" t="n">
+        <v>50472.57</v>
+      </c>
+      <c r="E46" s="43" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F46" s="40" t="n">
+        <v>593794.9399999999</v>
+      </c>
+      <c r="G46" s="40" t="n">
+        <v>-544830.28</v>
+      </c>
+      <c r="H46" s="40" t="n">
+        <v>-562644.13</v>
+      </c>
+      <c r="I46" s="40" t="n">
+        <v>-441028.47</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>-0.042221</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>-0.102545</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>R3 + CapEx +20%</t>
+        </is>
+      </c>
+      <c r="B47" s="40" t="n">
+        <v>1032160</v>
+      </c>
+      <c r="C47" s="40" t="n">
+        <v>1120197.9</v>
+      </c>
+      <c r="D47" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="E47" s="43" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="F47" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="G47" s="40" t="n">
+        <v>-281122.96</v>
+      </c>
+      <c r="H47" s="40" t="n">
+        <v>-306295.21</v>
+      </c>
+      <c r="I47" s="40" t="n">
+        <v>-206843.7</v>
+      </c>
+      <c r="J47" s="7" t="n">
+        <v>0.028168</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>0.024049</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>R3 + LEADER delayed to Y3</t>
+        </is>
+      </c>
+      <c r="B48" s="40" t="n">
+        <v>901800</v>
+      </c>
+      <c r="C48" s="40" t="n">
+        <v>986296.85</v>
+      </c>
+      <c r="D48" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="E48" s="43" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F48" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="G48" s="40" t="n">
+        <v>-147221.91</v>
+      </c>
+      <c r="H48" s="40" t="n">
+        <v>-172394.16</v>
+      </c>
+      <c r="I48" s="40" t="n">
+        <v>-105254.39</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>0.052156</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>0.059813</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>R3 + no LEADER grant</t>
+        </is>
+      </c>
+      <c r="B49" s="40" t="n">
+        <v>901800</v>
+      </c>
+      <c r="C49" s="40" t="n">
+        <v>986296.85</v>
+      </c>
+      <c r="D49" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="E49" s="43" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F49" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="G49" s="40" t="n">
+        <v>-147221.91</v>
+      </c>
+      <c r="H49" s="40" t="n">
+        <v>-172394.16</v>
+      </c>
+      <c r="I49" s="40" t="n">
+        <v>-216215.47</v>
+      </c>
+      <c r="J49" s="7" t="n">
+        <v>0.022505</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>0.016396</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>R3 + rate +200 bp</t>
+        </is>
+      </c>
+      <c r="B50" s="40" t="n">
+        <v>901800</v>
+      </c>
+      <c r="C50" s="40" t="n">
+        <v>988365</v>
+      </c>
+      <c r="D50" s="40" t="n">
+        <v>71321.37</v>
+      </c>
+      <c r="E50" s="43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F50" s="40" t="n">
+        <v>839074.9399999999</v>
+      </c>
+      <c r="G50" s="40" t="n">
+        <v>-149290.06</v>
+      </c>
+      <c r="H50" s="40" t="n">
+        <v>-174462.31</v>
+      </c>
+      <c r="I50" s="40" t="n">
+        <v>-98445.64999999999</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>0.053216</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>0.054386</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>R3 + conservative demand</t>
+        </is>
+      </c>
+      <c r="B51" s="40" t="n">
+        <v>901800</v>
+      </c>
+      <c r="C51" s="40" t="n">
+        <v>987831.24</v>
+      </c>
+      <c r="D51" s="40" t="n">
+        <v>33333.95</v>
+      </c>
+      <c r="E51" s="43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F51" s="40" t="n">
+        <v>392164.12</v>
+      </c>
+      <c r="G51" s="40" t="n">
+        <v>-595667.12</v>
+      </c>
+      <c r="H51" s="40" t="n">
+        <v>-607432.04</v>
+      </c>
+      <c r="I51" s="40" t="n">
+        <v>-509916.1</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>-0.096315</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>-0.245461</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>R6 combined downside</t>
         </is>
       </c>
-      <c r="B45" s="40" t="n">
+      <c r="B52" s="40" t="n">
         <v>965560</v>
       </c>
-      <c r="C45" s="40" t="n">
+      <c r="C52" s="40" t="n">
         <v>1051789.19</v>
       </c>
-      <c r="D45" s="40" t="n">
-        <v>-33876</v>
-      </c>
-      <c r="E45" s="43" t="n">
+      <c r="D52" s="40" t="n">
+        <v>-33886.72</v>
+      </c>
+      <c r="E52" s="43" t="n">
         <v>-3.82</v>
       </c>
-      <c r="F45" s="40" t="n">
-        <v>-338760</v>
-      </c>
-      <c r="G45" s="40" t="n">
-        <v>-1390549.19</v>
-      </c>
-      <c r="H45" s="40" t="n">
-        <v>-1242114.7</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="F52" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="40" t="n">
+        <v>-1051789.19</v>
+      </c>
+      <c r="H52" s="40" t="n">
+        <v>-1051789.19</v>
+      </c>
+      <c r="I52" s="40" t="n">
+        <v>-1021972.82</v>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="J45" s="6" t="inlineStr">
+      <c r="K52" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>5. REFORM RECOMMENDATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="52" t="inlineStr">
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>5. RATE SENSITIVITY - R2 REFORM AT +0 / +100 / +200 / +300 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="46" t="inlineStr">
+        <is>
+          <t>Rate shock (bp)</t>
+        </is>
+      </c>
+      <c r="B56" s="46" t="inlineStr">
+        <is>
+          <t>Interest rate</t>
+        </is>
+      </c>
+      <c r="C56" s="46" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="D56" s="46" t="inlineStr">
+        <is>
+          <t>Project NPV (EUR)</t>
+        </is>
+      </c>
+      <c r="E56" s="46" t="inlineStr">
+        <is>
+          <t>Gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="F56" s="46" t="inlineStr">
+        <is>
+          <t>Net gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C57" s="43" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="D57" s="40" t="n">
+        <v>-220684.83</v>
+      </c>
+      <c r="E57" s="40" t="n">
+        <v>-299550.28</v>
+      </c>
+      <c r="F57" s="40" t="n">
+        <v>-324722.53</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C58" s="43" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D58" s="40" t="n">
+        <v>-221862.57</v>
+      </c>
+      <c r="E58" s="40" t="n">
+        <v>-300728.02</v>
+      </c>
+      <c r="F58" s="40" t="n">
+        <v>-325900.27</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="50" t="n">
+        <v>200</v>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C59" s="43" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="D59" s="40" t="n">
+        <v>-223093.76</v>
+      </c>
+      <c r="E59" s="40" t="n">
+        <v>-301959.21</v>
+      </c>
+      <c r="F59" s="40" t="n">
+        <v>-327131.46</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="50" t="n">
+        <v>300</v>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C60" s="43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="D60" s="40" t="n">
+        <v>-224375.72</v>
+      </c>
+      <c r="E60" s="40" t="n">
+        <v>-303241.17</v>
+      </c>
+      <c r="F60" s="40" t="n">
+        <v>-328413.42</v>
+      </c>
+    </row>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>6. REFORM RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="51" t="inlineStr">
         <is>
           <t>DECLINE AS STRUCTURED - ONLY THE AGGRESSIVE, UNPROVEN DEMAND CASE CLEARS THE WACC</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>The realistic revenue reform (R2: six external covers/day, +5% ADR, one FTE) produces EUR 71,321 of mature EBITDA and EUR 839,075 of asset value. Against the EUR 1,050,100 CapEx that is a gap of EUR -211,025; against total project investment of EUR 1,138,625 the gap is EUR -299,550. R2 still has a project NPV of EUR -220,685 and a project IRR of 2.53%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>The 900k value-engineered case (R3) improves the NPV to EUR -96,378 and the IRR to 5.37%, but still does not clear an 8% WACC. The 850k lean case (R5) reaches EUR -49,106 of NPV and 6.61% IRR, still below the hurdle. The only positive-NPV case is R4 (eight covers/day, +10% ADR, one FTE) at EUR 3,722 of NPV and 8.08% IRR - a negligible margin and a total-investment value gap of EUR -51,534. The combined downside (R6) is deeply negative: EBITDA EUR 2,671, NPV EUR -906,166. The value frontier does show a positive corner at roughly EUR 700k of CapEx (land included) with six or more covers, but that is EUR 450k of non-land spend for an eight-room refurbishment: a scope-reduction thesis, not the current 1.05M budget.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="65" ht="46" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>The realistic revenue reform (R2: six external covers/day, +5% ADR, one FTE) produces EUR 71,321 of mature EBITDA and EUR 839,075 of asset value. Against the EUR 1,050,100 CapEx that is a gap of EUR -211,025; against total project investment of EUR 1,138,625 the gap is EUR -299,550. After 3.0% exit costs the net gap is EUR -324,723. R2 still has a project NPV of EUR -220,685 and a project IRR of 2.53%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="56" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>The 900k value-engineered case (R3) improves the NPV to EUR -96,378 and the IRR to 5.37%, but still does not clear an 8% WACC. The 850k lean case (R5) reaches EUR -49,106 of NPV and 6.61% IRR, still below the hurdle. The only positive-NPV case is R4 (eight covers/day, +10% ADR, one FTE) at EUR 3,722 of NPV and 8.08% IRR - a negligible margin and a total-investment value gap of EUR -51,534. After 3.0% exit costs the net gap is EUR -84,147, so even the boundary case fails the net test. The combined downside (R6) is deeply negative: EBITDA EUR -33,887, NPV EUR -1,021,973. The value frontier does show a positive corner at roughly EUR 700k of CapEx (land included) with six or more covers, but that is EUR 450k of non-land spend for an eight-room refurbishment: a scope-reduction thesis, not the current 1.05M budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Conditions attached to any further work</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>- Do not treat the 1.05M eight-room project as the base case for a reform.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>- Prove external F&amp;B demand before committing construction capital: a low-cost Phase 0 pop-up/restaurant test, not a full refurbishment.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>- If the family wants to proceed, cap the initial capital at the lean scope and keep the second phase behind a demand gate.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>- Treat the ~700k frontier corner as a different, smaller project: it only works by cutting the non-land budget to about 450k, which is not the eight-room refurbishment currently specified.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>- Charge the land at its opportunity value; do not describe the project as viable only because the site is already owned.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>- Price the exit net of selling costs. The gross cap-rate value flatters every case; the boundary case fails once 3% exit costs are deducted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>- Re-run the model with 1.25-1.5 FTE for the external covers, not one FTE, and with INE 21.24% occupancy in the downside.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A57:L57"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A54:L54"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A49:L49"/>
-    <mergeCell ref="A58:L58"/>
-    <mergeCell ref="A56:L56"/>
-    <mergeCell ref="A55:L55"/>
-    <mergeCell ref="A50:L50"/>
-    <mergeCell ref="A59:L59"/>
+  <mergeCells count="11">
+    <mergeCell ref="A70:N70"/>
+    <mergeCell ref="A69:N69"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A72:N72"/>
+    <mergeCell ref="A64:N64"/>
+    <mergeCell ref="A65:N65"/>
+    <mergeCell ref="A73:N73"/>
+    <mergeCell ref="A71:N71"/>
+    <mergeCell ref="A75:N75"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A74:N74"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
+++ b/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="165" formatCode="0.000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +72,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00BE123C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
       <sz val="12"/>
     </font>
     <font>
@@ -157,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -179,11 +185,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -216,10 +222,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -238,6 +244,8 @@
     <xf numFmtId="3" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -799,7 +807,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Separate post-decline layer: R1-R6 presets, value bridge, CapEx/cover frontier, stress tests and recommendation.</t>
+          <t>Separate post-decline layer: R1-R6 presets, value bridge, CapEx/cover frontier, stress tests, R7 premium cabins and recommendation.</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4269,7 +4277,7 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
@@ -5617,19 +5625,519 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>7. R7 PREMIUM CABINS - A DIFFERENT PRODUCT, SAME 9.5% CAP-RATE HURDLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>R7 replaces the eight-room hotel with six two-bedroom cabins plus the main house. The base case is deliberately the good edge of the band: 6 cabins at 110k all-in, 200 EUR ADR, 50% stabilised occupancy, ten external covers and 45k of experiences. At 120k per cabin the same demand fails the bank-facing net total-investment test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="42" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B79" s="42" t="inlineStr">
+        <is>
+          <t>Cabins</t>
+        </is>
+      </c>
+      <c r="C79" s="42" t="inlineStr">
+        <is>
+          <t>ADR (EUR)</t>
+        </is>
+      </c>
+      <c r="D79" s="42" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="E79" s="42" t="inlineStr">
+        <is>
+          <t>Cost / cabin (EUR)</t>
+        </is>
+      </c>
+      <c r="F79" s="42" t="inlineStr">
+        <is>
+          <t>CapEx (EUR)</t>
+        </is>
+      </c>
+      <c r="G79" s="42" t="inlineStr">
+        <is>
+          <t>Total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="H79" s="42" t="inlineStr">
+        <is>
+          <t>EBITDA Y5 (EUR)</t>
+        </is>
+      </c>
+      <c r="I79" s="42" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="J79" s="42" t="inlineStr">
+        <is>
+          <t>Net gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="K79" s="42" t="inlineStr">
+        <is>
+          <t>Project NPV (EUR)</t>
+        </is>
+      </c>
+      <c r="L79" s="42" t="inlineStr">
+        <is>
+          <t>Project IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>CABINS BASE</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C80" s="40" t="n">
+        <v>200</v>
+      </c>
+      <c r="D80" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E80" s="40" t="n">
+        <v>110000</v>
+      </c>
+      <c r="F80" s="40" t="n">
+        <v>1441600</v>
+      </c>
+      <c r="G80" s="40" t="n">
+        <v>1540760.04</v>
+      </c>
+      <c r="H80" s="40" t="n">
+        <v>155712.5</v>
+      </c>
+      <c r="I80" s="43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J80" s="40" t="n">
+        <v>49146.54</v>
+      </c>
+      <c r="K80" s="40" t="n">
+        <v>76416.23</v>
+      </c>
+      <c r="L80" s="7" t="n">
+        <v>0.092088</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>CABINS STRETCH</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C81" s="40" t="n">
+        <v>230</v>
+      </c>
+      <c r="D81" s="52" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E81" s="40" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F81" s="40" t="n">
+        <v>1708000</v>
+      </c>
+      <c r="G81" s="40" t="n">
+        <v>1814396.63</v>
+      </c>
+      <c r="H81" s="40" t="n">
+        <v>227340.1</v>
+      </c>
+      <c r="I81" s="43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J81" s="40" t="n">
+        <v>506865.44</v>
+      </c>
+      <c r="K81" s="40" t="n">
+        <v>509113.02</v>
+      </c>
+      <c r="L81" s="7" t="n">
+        <v>0.143285</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>CABINS DOWNSIDE</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C82" s="40" t="n">
+        <v>190</v>
+      </c>
+      <c r="D82" s="52" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E82" s="40" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F82" s="40" t="n">
+        <v>1541500</v>
+      </c>
+      <c r="G82" s="40" t="n">
+        <v>1643374.02</v>
+      </c>
+      <c r="H82" s="40" t="n">
+        <v>71597.62</v>
+      </c>
+      <c r="I82" s="43" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J82" s="40" t="n">
+        <v>-988767.2</v>
+      </c>
+      <c r="K82" s="40" t="n">
+        <v>-878138.02</v>
+      </c>
+      <c r="L82" s="7" t="n">
+        <v>-0.092334</v>
+      </c>
+    </row>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>8. R7 COST CORRIDOR - SIX CABINS, 200 EUR ADR, 50% OCCUPANCY (PASS = NET TOTAL-INVESTMENT TEST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="42" t="inlineStr">
+        <is>
+          <t>Cost / cabin (EUR)</t>
+        </is>
+      </c>
+      <c r="B86" s="42" t="inlineStr">
+        <is>
+          <t>CapEx (EUR)</t>
+        </is>
+      </c>
+      <c r="C86" s="42" t="inlineStr">
+        <is>
+          <t>Total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="D86" s="42" t="inlineStr">
+        <is>
+          <t>EBITDA Y5 (EUR)</t>
+        </is>
+      </c>
+      <c r="E86" s="42" t="inlineStr">
+        <is>
+          <t>EV (EUR)</t>
+        </is>
+      </c>
+      <c r="F86" s="42" t="inlineStr">
+        <is>
+          <t>Gap vs CapEx (EUR)</t>
+        </is>
+      </c>
+      <c r="G86" s="42" t="inlineStr">
+        <is>
+          <t>Gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="H86" s="42" t="inlineStr">
+        <is>
+          <t>Net gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="I86" s="42" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="J86" s="42" t="inlineStr">
+        <is>
+          <t>Project NPV (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="45" t="n">
+        <v>110000</v>
+      </c>
+      <c r="B87" s="40" t="n">
+        <v>1441600</v>
+      </c>
+      <c r="C87" s="40" t="n">
+        <v>1540760.04</v>
+      </c>
+      <c r="D87" s="40" t="n">
+        <v>155712.5</v>
+      </c>
+      <c r="E87" s="40" t="n">
+        <v>1639078.95</v>
+      </c>
+      <c r="F87" s="40" t="n">
+        <v>197478.95</v>
+      </c>
+      <c r="G87" s="40" t="n">
+        <v>98318.91</v>
+      </c>
+      <c r="H87" s="49" t="n">
+        <v>49146.54</v>
+      </c>
+      <c r="I87" s="43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J87" s="40" t="n">
+        <v>76416.23</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="45" t="n">
+        <v>120000</v>
+      </c>
+      <c r="B88" s="40" t="n">
+        <v>1508200</v>
+      </c>
+      <c r="C88" s="40" t="n">
+        <v>1609169.17</v>
+      </c>
+      <c r="D88" s="40" t="n">
+        <v>155712.5</v>
+      </c>
+      <c r="E88" s="40" t="n">
+        <v>1639078.95</v>
+      </c>
+      <c r="F88" s="40" t="n">
+        <v>130878.95</v>
+      </c>
+      <c r="G88" s="40" t="n">
+        <v>29909.78</v>
+      </c>
+      <c r="H88" s="48" t="n">
+        <v>-19262.59</v>
+      </c>
+      <c r="I88" s="43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J88" s="40" t="n">
+        <v>10001.46</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="45" t="n">
+        <v>130000</v>
+      </c>
+      <c r="B89" s="40" t="n">
+        <v>1574800</v>
+      </c>
+      <c r="C89" s="40" t="n">
+        <v>1677578.94</v>
+      </c>
+      <c r="D89" s="40" t="n">
+        <v>155712.5</v>
+      </c>
+      <c r="E89" s="40" t="n">
+        <v>1639078.95</v>
+      </c>
+      <c r="F89" s="40" t="n">
+        <v>64278.95</v>
+      </c>
+      <c r="G89" s="40" t="n">
+        <v>-38499.99</v>
+      </c>
+      <c r="H89" s="48" t="n">
+        <v>-87672.36</v>
+      </c>
+      <c r="I89" s="43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J89" s="40" t="n">
+        <v>-56413.95</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="45" t="n">
+        <v>150000</v>
+      </c>
+      <c r="B90" s="40" t="n">
+        <v>1708000</v>
+      </c>
+      <c r="C90" s="40" t="n">
+        <v>1814396.63</v>
+      </c>
+      <c r="D90" s="40" t="n">
+        <v>155712.5</v>
+      </c>
+      <c r="E90" s="40" t="n">
+        <v>1639078.95</v>
+      </c>
+      <c r="F90" s="40" t="n">
+        <v>-68921.05</v>
+      </c>
+      <c r="G90" s="40" t="n">
+        <v>-175317.68</v>
+      </c>
+      <c r="H90" s="48" t="n">
+        <v>-224490.05</v>
+      </c>
+      <c r="I90" s="43" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J90" s="40" t="n">
+        <v>-189242.92</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="45" t="n">
+        <v>180000</v>
+      </c>
+      <c r="B91" s="40" t="n">
+        <v>1907800</v>
+      </c>
+      <c r="C91" s="40" t="n">
+        <v>2019624.19</v>
+      </c>
+      <c r="D91" s="40" t="n">
+        <v>155712.5</v>
+      </c>
+      <c r="E91" s="40" t="n">
+        <v>1639078.95</v>
+      </c>
+      <c r="F91" s="40" t="n">
+        <v>-268721.05</v>
+      </c>
+      <c r="G91" s="40" t="n">
+        <v>-380545.24</v>
+      </c>
+      <c r="H91" s="48" t="n">
+        <v>-429717.61</v>
+      </c>
+      <c r="I91" s="43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J91" s="40" t="n">
+        <v>-388487.41</v>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>9. R7 CABIN RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="53" t="inlineStr">
+        <is>
+          <t>CONDITIONAL PROCEED TO PHASE 0 - PREMIUM CABINS PASS ON PAPER, BUT ONLY AT 110K PER CABIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="46" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>The base cabin case (six two-bedroom cabins, 200 EUR ADR, 50% occupancy, ten external covers, 45k of experiences) produces EUR 155,712 of mature EBITDA and EUR 1,639,079 of enterprise value at a 9.5% cap rate. Against total investment of EUR 1,540,760 that is a net gap of EUR +49,147 after 3.0% selling costs: it passes, but by roughly 3.2% of the capital at risk. The project NPV is EUR +76,416, the project IRR 9.21% and the minimum DSCR 1.41x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="56" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>The corridor is narrow. At 120k per cabin the same demand fails the net total-investment test, and at 150k it only works if the ADR moves to 230 EUR and occupancy to 55% (the stretch case: EBITDA EUR 227,340, net gap EUR +506,865). The 180k ultra-luxury unit fails with the demand this market pays. The downside (five cabins, 190 EUR, 45% occupancy) produces EBITDA EUR 71,598, a minimum DSCR of 0.79x and a net gap of EUR -988,767: it is a demand failure, not a construction-cost problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>R7 conditions attached to any further work</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>- Run the Phase 0 demand test before committing construction capital: two cabins plus the house for one season, or a restaurant/experience pop-up. The gates are 45% occupancy, 190 EUR realised ADR, eight external covers a day and 25k of experiences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>- Keep the all-in cabin cost at or below 110k. At 120k the same demand band fails the net total-investment test; at 130k or more the gap is negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>- Do not budget the 180k ultra-luxury unit. It only works at 250 EUR ADR or more, which the Segovia comparables do not support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>- Treat the 45k of agronomic experiences as an operating programme with a host, a calendar and marketing, not as passive income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>- Charge the land at its 250k opportunity value; the case does not pass by treating the site as free.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="20">
+    <mergeCell ref="A77:N77"/>
+    <mergeCell ref="A64:N64"/>
+    <mergeCell ref="A73:N73"/>
+    <mergeCell ref="A103:N103"/>
     <mergeCell ref="A70:N70"/>
     <mergeCell ref="A69:N69"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A72:N72"/>
-    <mergeCell ref="A64:N64"/>
     <mergeCell ref="A65:N65"/>
-    <mergeCell ref="A73:N73"/>
-    <mergeCell ref="A71:N71"/>
     <mergeCell ref="A75:N75"/>
     <mergeCell ref="A66:N66"/>
     <mergeCell ref="A74:N74"/>
+    <mergeCell ref="A101:N101"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A104:N104"/>
+    <mergeCell ref="A95:N95"/>
+    <mergeCell ref="A71:N71"/>
+    <mergeCell ref="A97:N97"/>
+    <mergeCell ref="A100:N100"/>
+    <mergeCell ref="A96:N96"/>
+    <mergeCell ref="A72:N72"/>
+    <mergeCell ref="A102:N102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
+++ b/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
@@ -28,12 +28,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.00x"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0x"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +82,12 @@
       <b val="1"/>
       <color rgb="000F766E"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00BE123C"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -163,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -185,16 +194,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,10 +231,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -246,6 +255,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4265,13 +4282,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:N150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
@@ -6116,15 +6133,609 @@
         </is>
       </c>
     </row>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>10. R7 VALUATION CROSS-CHECK - DEVELOPMENT YIELD vs EXIT CAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>The positive gap is a development spread: the asset is built at a 10.1% yield on cost and sold at a 9.5% cap. The break-even exit cap is only 30bp above the assumption; at no compression the net gap is just the exit costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Development yield on cost</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="n">
+        <v>0.1011</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Exit cap rate</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="n">
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>Break-even exit cap (net of costs)</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="n">
+        <v>0.098</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>Cap-rate headroom (bp)</t>
+        </is>
+      </c>
+      <c r="B112" s="54" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>No-compression net gap (EUR)</t>
+        </is>
+      </c>
+      <c r="B113" s="40" t="n">
+        <v>-46222.8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>Break-even EBITDA, net (EUR)</t>
+        </is>
+      </c>
+      <c r="B114" s="40" t="n">
+        <v>150899.18</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA headroom (EUR)</t>
+        </is>
+      </c>
+      <c r="B115" s="40" t="n">
+        <v>4813.32</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>Implied exit multiple</t>
+        </is>
+      </c>
+      <c r="B116" s="43" t="n">
+        <v>10.53</v>
+      </c>
+    </row>
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" s="42" t="inlineStr">
+        <is>
+          <t>Exit multiple</t>
+        </is>
+      </c>
+      <c r="B118" s="42" t="inlineStr">
+        <is>
+          <t>EV (EUR)</t>
+        </is>
+      </c>
+      <c r="C118" s="42" t="inlineStr">
+        <is>
+          <t>Net exit value (EUR)</t>
+        </is>
+      </c>
+      <c r="D118" s="42" t="inlineStr">
+        <is>
+          <t>Net gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="55" t="n">
+        <v>9</v>
+      </c>
+      <c r="B119" s="40" t="n">
+        <v>1401412.5</v>
+      </c>
+      <c r="C119" s="40" t="n">
+        <v>1359370.12</v>
+      </c>
+      <c r="D119" s="48" t="n">
+        <v>-181389.92</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B120" s="40" t="n">
+        <v>1634981.25</v>
+      </c>
+      <c r="C120" s="40" t="n">
+        <v>1585931.81</v>
+      </c>
+      <c r="D120" s="49" t="n">
+        <v>45171.77</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="55" t="n">
+        <v>12</v>
+      </c>
+      <c r="B121" s="40" t="n">
+        <v>1868550</v>
+      </c>
+      <c r="C121" s="40" t="n">
+        <v>1812493.5</v>
+      </c>
+      <c r="D121" s="49" t="n">
+        <v>271733.46</v>
+      </c>
+    </row>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>11. R7 COST-INFLATION STRESS - REAL COST GROWTH, FLAT REAL PRICES</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="42" t="inlineStr">
+        <is>
+          <t>Cost inflation / yr</t>
+        </is>
+      </c>
+      <c r="B125" s="42" t="inlineStr">
+        <is>
+          <t>EBITDA Y5 (EUR)</t>
+        </is>
+      </c>
+      <c r="C125" s="42" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="D125" s="42" t="inlineStr">
+        <is>
+          <t>DSCR Y5</t>
+        </is>
+      </c>
+      <c r="E125" s="42" t="inlineStr">
+        <is>
+          <t>EV (EUR)</t>
+        </is>
+      </c>
+      <c r="F125" s="42" t="inlineStr">
+        <is>
+          <t>Net gap vs total inv. (EUR)</t>
+        </is>
+      </c>
+      <c r="G125" s="42" t="inlineStr">
+        <is>
+          <t>Project NPV (EUR)</t>
+        </is>
+      </c>
+      <c r="H125" s="42" t="inlineStr">
+        <is>
+          <t>Project IRR</t>
+        </is>
+      </c>
+      <c r="I125" s="42" t="inlineStr">
+        <is>
+          <t>Net test</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="B126" s="40" t="n">
+        <v>155712.5</v>
+      </c>
+      <c r="C126" s="56" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="D126" s="43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E126" s="40" t="n">
+        <v>1639078.95</v>
+      </c>
+      <c r="F126" s="40" t="n">
+        <v>49146.54</v>
+      </c>
+      <c r="G126" s="40" t="n">
+        <v>76416.23</v>
+      </c>
+      <c r="H126" s="7" t="n">
+        <v>0.092088</v>
+      </c>
+      <c r="I126" s="57" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="56" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="B127" s="40" t="n">
+        <v>136911.79</v>
+      </c>
+      <c r="C127" s="56" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="D127" s="43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E127" s="40" t="n">
+        <v>1441176.74</v>
+      </c>
+      <c r="F127" s="40" t="n">
+        <v>-142818.6</v>
+      </c>
+      <c r="G127" s="40" t="n">
+        <v>-83984.03</v>
+      </c>
+      <c r="H127" s="7" t="n">
+        <v>0.06605999999999999</v>
+      </c>
+      <c r="I127" s="58" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="56" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="B128" s="40" t="n">
+        <v>132035.38</v>
+      </c>
+      <c r="C128" s="56" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="D128" s="43" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E128" s="40" t="n">
+        <v>1389846.11</v>
+      </c>
+      <c r="F128" s="40" t="n">
+        <v>-192609.31</v>
+      </c>
+      <c r="G128" s="40" t="n">
+        <v>-125501.41</v>
+      </c>
+      <c r="H128" s="7" t="n">
+        <v>0.058889</v>
+      </c>
+      <c r="I128" s="58" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="56" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="B129" s="40" t="n">
+        <v>127087.08</v>
+      </c>
+      <c r="C129" s="56" t="n">
+        <v>0.2218</v>
+      </c>
+      <c r="D129" s="43" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E129" s="40" t="n">
+        <v>1337758.74</v>
+      </c>
+      <c r="F129" s="40" t="n">
+        <v>-243134.06</v>
+      </c>
+      <c r="G129" s="40" t="n">
+        <v>-167596.64</v>
+      </c>
+      <c r="H129" s="7" t="n">
+        <v>0.051413</v>
+      </c>
+      <c r="I129" s="58" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>12. R7 DISTRESS PLAYBOOK (DOWNSIDE CASE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="32" customHeight="1">
+      <c r="A132" s="59" t="inlineStr">
+        <is>
+          <t>THE LENDER IS REPAID ON SALE, BUT THE EQUITY IS WIPED OUT - DO NOT THROW A CURE AT A DEMAND FAILURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="133"/>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Minimum DSCR / year</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>0.79x in Year 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Cumulative CFADS shortfall (EUR)</t>
+        </is>
+      </c>
+      <c r="B135" s="40" t="n">
+        <v>4577.04</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Equity cure to 1.25x DSCR (EUR)</t>
+        </is>
+      </c>
+      <c r="B136" s="40" t="n">
+        <v>17455.75</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>Six-month DSRA (EUR)</t>
+        </is>
+      </c>
+      <c r="B137" s="40" t="n">
+        <v>20292.72</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>Net exit value (EUR)</t>
+        </is>
+      </c>
+      <c r="B138" s="40" t="n">
+        <v>654606.8199999999</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>Debt outstanding at exit (EUR)</t>
+        </is>
+      </c>
+      <c r="B139" s="40" t="n">
+        <v>457236.43</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>Lender recovery</t>
+        </is>
+      </c>
+      <c r="B140" s="56" t="n">
+        <v>1.4317</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>Equity at exit (EUR)</t>
+        </is>
+      </c>
+      <c r="B141" s="40" t="n">
+        <v>197370.39</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>Equity invested (EUR)</t>
+        </is>
+      </c>
+      <c r="B142" s="40" t="n">
+        <v>1113342.89</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>Equity recovery</t>
+        </is>
+      </c>
+      <c r="B143" s="56" t="n">
+        <v>0.1773</v>
+      </c>
+    </row>
+    <row r="144"/>
+    <row r="145">
+      <c r="A145" s="42" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B145" s="42" t="inlineStr">
+        <is>
+          <t>CFADS (EUR)</t>
+        </is>
+      </c>
+      <c r="C145" s="42" t="inlineStr">
+        <is>
+          <t>Debt service (EUR)</t>
+        </is>
+      </c>
+      <c r="D145" s="42" t="inlineStr">
+        <is>
+          <t>Shortfall (EUR)</t>
+        </is>
+      </c>
+      <c r="E145" s="42" t="inlineStr">
+        <is>
+          <t>DSCR</t>
+        </is>
+      </c>
+      <c r="F145" s="42" t="inlineStr">
+        <is>
+          <t>Ending cash (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B146" s="40" t="n">
+        <v>17004</v>
+      </c>
+      <c r="C146" s="40" t="n">
+        <v>21581.04</v>
+      </c>
+      <c r="D146" s="40" t="n">
+        <v>4577.04</v>
+      </c>
+      <c r="E146" s="43" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F146" s="40" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B147" s="40" t="n">
+        <v>43248.35</v>
+      </c>
+      <c r="C147" s="40" t="n">
+        <v>40585.44</v>
+      </c>
+      <c r="D147" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F147" s="40" t="n">
+        <v>173204.5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B148" s="40" t="n">
+        <v>58730.24</v>
+      </c>
+      <c r="C148" s="40" t="n">
+        <v>40585.44</v>
+      </c>
+      <c r="D148" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F148" s="40" t="n">
+        <v>191349.3</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B149" s="40" t="n">
+        <v>58730.24</v>
+      </c>
+      <c r="C149" s="40" t="n">
+        <v>40585.44</v>
+      </c>
+      <c r="D149" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" s="43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F149" s="40" t="n">
+        <v>209494.1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="B150" s="40" t="n">
+        <v>58730.24</v>
+      </c>
+      <c r="C150" s="40" t="n">
+        <v>40585.44</v>
+      </c>
+      <c r="D150" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F150" s="40" t="n">
+        <v>227638.9</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="A77:N77"/>
     <mergeCell ref="A64:N64"/>
     <mergeCell ref="A73:N73"/>
     <mergeCell ref="A103:N103"/>
+    <mergeCell ref="A132:N132"/>
     <mergeCell ref="A70:N70"/>
     <mergeCell ref="A69:N69"/>
     <mergeCell ref="A65:N65"/>
+    <mergeCell ref="A108:N108"/>
     <mergeCell ref="A75:N75"/>
     <mergeCell ref="A66:N66"/>
     <mergeCell ref="A74:N74"/>

--- a/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
+++ b/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
@@ -649,7 +649,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>A live, formula-driven management case alongside the independent INE market case and a faithful replication of the original promoter simulator.</t>
+          <t>A live, formula-driven management case alongside the independent INE market case and a re-modelled promoter case calibrated to the presentation headline.</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Promoter (original Excel)</t>
+          <t>Promoter (re-modelled)</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Faithful replication of the author's original university simulator.</t>
+          <t>Re-modelled from the presentation headline; not a replication (README section 2).</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>- The original promoter case (19.2%) replicates the author's university Excel (EUR 86,275 revenue / EUR 11,297 EBITDA) and is structurally insolvent at the debt service level.</t>
+          <t>- The promoter case (19.2%) is re-modelled to the presentation's headline pair (EUR 86,275 revenue / EUR 11,297 EBITDA) and is structurally insolvent at the debt service level. It is not a replication of the source workbooks.</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>Original Excel (491 / 2,555 room-nights)</t>
+          <t>Promoter case (491 room-nights in Year 1)</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>19.20% occupancy, 491 room-nights, 72 house-nights, 859 meals at EUR 20, 4.5% / 25-year debt, no grant and the original EUR 729k cost base. Replicates the original university Excel exactly.</t>
+          <t>19.20% occupancy, 491 room-nights, 72 house-nights, 859 covers at EUR 20, 4.5% / 25-year debt, no grant and the original EUR 725k cost base. Re-modelled, not replicated: see README section 2.</t>
         </is>
       </c>
     </row>
@@ -10494,12 +10494,12 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>RULE_13_PROMOTER_REPLICATION</t>
+          <t>RULE_13_PROMOTER_CALIBRATION</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Promoter-case replication of the original simulator</t>
+          <t>Promoter-case calibration to the presentation headline</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">

--- a/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
+++ b/data/La_Dehesa_del_Castrillo_Financial_Model.xlsx
@@ -172,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -217,6 +217,9 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -649,7 +652,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>A live, formula-driven management case alongside the independent INE market case and a re-modelled promoter case calibrated to the presentation headline.</t>
+          <t>A live, formula-driven management case alongside the independent INE market case and a re-modelled promoter case whose 86,275 revenue is a model construct, not a source figure (README section 2).</t>
         </is>
       </c>
     </row>
@@ -941,7 +944,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Re-modelled from the presentation headline; not a replication (README section 2).</t>
+          <t>Re-modelled: 86,275 is a model construct (EUR 20 ticket), not a source figure; not a replication (README section 2).</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1195,7 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>- The promoter case (19.2%) is re-modelled to the presentation's headline pair (EUR 86,275 revenue / EUR 11,297 EBITDA) and is structurally insolvent at the debt service level. It is not a replication of the source workbooks.</t>
+          <t>- The promoter case (19.2%) is a re-modelling, not a replication: 86,275 is its own revenue construct (EUR 20 ticket) and 11,297 is the deck literal. It is structurally insolvent at the debt service level.</t>
         </is>
       </c>
     </row>
@@ -1315,52 +1318,52 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>Model Specification</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>Tail Dep. (Lower / Upper)</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>Mean DSCR (Year 2)</t>
         </is>
       </c>
-      <c r="D4" s="35" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>Median DSCR (Year 2)</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>VaR 95% (5th pct)</t>
         </is>
       </c>
-      <c r="F4" s="35" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>VaR 99% (1st pct)</t>
         </is>
       </c>
-      <c r="G4" s="35" t="inlineStr">
+      <c r="G4" s="36" t="inlineStr">
         <is>
           <t>CVaR 99% (Worst 1%)</t>
         </is>
       </c>
-      <c r="H4" s="35" t="inlineStr">
+      <c r="H4" s="36" t="inlineStr">
         <is>
           <t>P(DSCR &lt; 1.25x)</t>
         </is>
       </c>
-      <c r="I4" s="35" t="inlineStr">
+      <c r="I4" s="36" t="inlineStr">
         <is>
           <t>P(DSCR &lt; 1.00x)</t>
         </is>
       </c>
-      <c r="J4" s="35" t="inlineStr">
+      <c r="J4" s="36" t="inlineStr">
         <is>
           <t>CVaR 99% Deficit (EUR)</t>
         </is>
@@ -1531,12 +1534,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Underwriting Parameter</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Credit Committee Benchmark</t>
         </is>
@@ -1810,67 +1813,67 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>Metric / Cost Category</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>Operational / Statutory Basis</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="F4" s="35" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="G4" s="35" t="inlineStr">
+      <c r="G4" s="36" t="inlineStr">
         <is>
           <t>Occupancy Rate</t>
         </is>
       </c>
-      <c r="H4" s="35" t="inlineStr">
+      <c r="H4" s="36" t="inlineStr">
         <is>
           <t>Occupied Days</t>
         </is>
       </c>
-      <c r="I4" s="35" t="inlineStr">
+      <c r="I4" s="36" t="inlineStr">
         <is>
           <t>Lodging Revenue (Eur)</t>
         </is>
       </c>
-      <c r="J4" s="35" t="inlineStr">
+      <c r="J4" s="36" t="inlineStr">
         <is>
           <t>Total Revenue (Eur)</t>
         </is>
       </c>
-      <c r="K4" s="35" t="inlineStr">
+      <c r="K4" s="36" t="inlineStr">
         <is>
           <t>Revpar (Eur)</t>
         </is>
       </c>
-      <c r="L4" s="35" t="inlineStr">
+      <c r="L4" s="36" t="inlineStr">
         <is>
           <t>Trevpar (Eur)</t>
         </is>
       </c>
-      <c r="M4" s="35" t="inlineStr">
+      <c r="M4" s="36" t="inlineStr">
         <is>
           <t>Cash Margin (Eur)</t>
         </is>
       </c>
-      <c r="N4" s="35" t="inlineStr">
+      <c r="N4" s="36" t="inlineStr">
         <is>
           <t>Fixed Burden Coverage</t>
         </is>
@@ -2213,77 +2216,77 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>Occupancy (%)</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>Revenue (EUR)</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>Var Costs (EUR)</t>
         </is>
       </c>
-      <c r="F19" s="35" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>Contr Margin (EUR)</t>
         </is>
       </c>
-      <c r="G19" s="35" t="inlineStr">
+      <c r="G19" s="36" t="inlineStr">
         <is>
           <t>Payroll (EUR)</t>
         </is>
       </c>
-      <c r="H19" s="35" t="inlineStr">
+      <c r="H19" s="36" t="inlineStr">
         <is>
           <t>Fixed OPEX (EUR)</t>
         </is>
       </c>
-      <c r="I19" s="35" t="inlineStr">
+      <c r="I19" s="36" t="inlineStr">
         <is>
           <t>Debt Svc (EUR)</t>
         </is>
       </c>
-      <c r="J19" s="35" t="inlineStr">
+      <c r="J19" s="36" t="inlineStr">
         <is>
           <t>Operating CF (EUR)</t>
         </is>
       </c>
-      <c r="K19" s="35" t="inlineStr">
+      <c r="K19" s="36" t="inlineStr">
         <is>
           <t>LEADER Grant (EUR)</t>
         </is>
       </c>
-      <c r="L19" s="35" t="inlineStr">
+      <c r="L19" s="36" t="inlineStr">
         <is>
           <t>VAT Refund (EUR)</t>
         </is>
       </c>
-      <c r="M19" s="35" t="inlineStr">
+      <c r="M19" s="36" t="inlineStr">
         <is>
           <t>Revolver Draw (EUR)</t>
         </is>
       </c>
-      <c r="N19" s="35" t="inlineStr">
+      <c r="N19" s="36" t="inlineStr">
         <is>
           <t>Ending Cash (EUR)</t>
         </is>
       </c>
-      <c r="O19" s="35" t="inlineStr">
+      <c r="O19" s="36" t="inlineStr">
         <is>
           <t>Total Liquidity (EUR)</t>
         </is>
@@ -2437,51 +2440,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="41" t="n">
+      <c r="A23" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="41" t="inlineStr">
+      <c r="B23" s="42" t="inlineStr">
         <is>
           <t>Abril</t>
         </is>
       </c>
-      <c r="C23" s="41" t="n">
+      <c r="C23" s="42" t="n">
         <v>27.9</v>
       </c>
-      <c r="D23" s="41" t="n">
+      <c r="D23" s="42" t="n">
         <v>12555</v>
       </c>
-      <c r="E23" s="41" t="n">
+      <c r="E23" s="42" t="n">
         <v>3224.55</v>
       </c>
-      <c r="F23" s="41" t="n">
+      <c r="F23" s="42" t="n">
         <v>9330.450000000001</v>
       </c>
-      <c r="G23" s="41" t="n">
+      <c r="G23" s="42" t="n">
         <v>5006.25</v>
       </c>
-      <c r="H23" s="41" t="n">
+      <c r="H23" s="42" t="n">
         <v>2541.67</v>
       </c>
-      <c r="I23" s="41" t="n">
+      <c r="I23" s="42" t="n">
         <v>1225.12</v>
       </c>
-      <c r="J23" s="41" t="n">
+      <c r="J23" s="42" t="n">
         <v>-589.34</v>
       </c>
-      <c r="K23" s="41" t="n">
+      <c r="K23" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="41" t="n">
+      <c r="L23" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="41" t="n">
+      <c r="M23" s="42" t="n">
         <v>589.34</v>
       </c>
-      <c r="N23" s="41" t="n">
+      <c r="N23" s="42" t="n">
         <v>15000</v>
       </c>
-      <c r="O23" s="41" t="n">
+      <c r="O23" s="42" t="n">
         <v>187004.01</v>
       </c>
     </row>
@@ -3514,32 +3517,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>CapEx Investment Chapter</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>Budget (EUR)</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>Technical Benchmark / Repercussion</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>Return / Underwriting Parameter</t>
         </is>
       </c>
-      <c r="F4" s="35" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>Metric Value</t>
         </is>
       </c>
-      <c r="G4" s="35" t="inlineStr">
+      <c r="G4" s="36" t="inlineStr">
         <is>
           <t>Strategic Interpretation</t>
         </is>
@@ -4010,62 +4013,62 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>Occupancy (%)</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>Nights Sold</t>
         </is>
       </c>
-      <c r="D26" s="35" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>ADR Net (EUR)</t>
         </is>
       </c>
-      <c r="E26" s="35" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>Revenue (EUR)</t>
         </is>
       </c>
-      <c r="F26" s="35" t="inlineStr">
+      <c r="F26" s="36" t="inlineStr">
         <is>
           <t>Contr Margin (EUR)</t>
         </is>
       </c>
-      <c r="G26" s="35" t="inlineStr">
+      <c r="G26" s="36" t="inlineStr">
         <is>
           <t>EBITDA (EUR)</t>
         </is>
       </c>
-      <c r="H26" s="35" t="inlineStr">
+      <c r="H26" s="36" t="inlineStr">
         <is>
           <t>EBIT (EUR)</t>
         </is>
       </c>
-      <c r="I26" s="35" t="inlineStr">
+      <c r="I26" s="36" t="inlineStr">
         <is>
           <t>Tax 25% (EUR)</t>
         </is>
       </c>
-      <c r="J26" s="35" t="inlineStr">
+      <c r="J26" s="36" t="inlineStr">
         <is>
           <t>Net Income (EUR)</t>
         </is>
       </c>
-      <c r="K26" s="35" t="inlineStr">
+      <c r="K26" s="36" t="inlineStr">
         <is>
           <t>Free Cash Flow (EUR)</t>
         </is>
       </c>
-      <c r="L26" s="35" t="inlineStr">
+      <c r="L26" s="36" t="inlineStr">
         <is>
           <t>Discounted FCF (EUR)</t>
         </is>
@@ -4324,72 +4327,72 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Reform case</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>CapEx (EUR)</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Total investment (EUR)</t>
         </is>
       </c>
-      <c r="E5" s="42" t="inlineStr">
+      <c r="E5" s="43" t="inlineStr">
         <is>
           <t>Revenue Y5 (EUR)</t>
         </is>
       </c>
-      <c r="F5" s="42" t="inlineStr">
+      <c r="F5" s="43" t="inlineStr">
         <is>
           <t>EBITDA Y5 (EUR)</t>
         </is>
       </c>
-      <c r="G5" s="42" t="inlineStr">
+      <c r="G5" s="43" t="inlineStr">
         <is>
           <t>Min DSCR</t>
         </is>
       </c>
-      <c r="H5" s="42" t="inlineStr">
+      <c r="H5" s="43" t="inlineStr">
         <is>
           <t>EV @ exit cap (EUR)</t>
         </is>
       </c>
-      <c r="I5" s="42" t="inlineStr">
+      <c r="I5" s="43" t="inlineStr">
         <is>
           <t>Gap vs CapEx (EUR)</t>
         </is>
       </c>
-      <c r="J5" s="42" t="inlineStr">
+      <c r="J5" s="43" t="inlineStr">
         <is>
           <t>Gap vs total inv. (EUR)</t>
         </is>
       </c>
-      <c r="K5" s="42" t="inlineStr">
+      <c r="K5" s="43" t="inlineStr">
         <is>
           <t>Net gap vs total inv. (EUR)</t>
         </is>
       </c>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="L5" s="43" t="inlineStr">
         <is>
           <t>Project NPV (EUR)</t>
         </is>
       </c>
-      <c r="M5" s="42" t="inlineStr">
+      <c r="M5" s="43" t="inlineStr">
         <is>
           <t>Project IRR</t>
         </is>
       </c>
-      <c r="N5" s="42" t="inlineStr">
+      <c r="N5" s="43" t="inlineStr">
         <is>
           <t>Equity IRR</t>
         </is>
@@ -4406,34 +4409,34 @@
           <t>R1 Capital-only (900k)</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n">
+      <c r="C6" s="41" t="n">
         <v>901800</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="41" t="n">
         <v>986296.85</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="41" t="n">
         <v>171720</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="41" t="n">
         <v>37041.58</v>
       </c>
-      <c r="G6" s="43" t="n">
+      <c r="G6" s="44" t="n">
         <v>1.34</v>
       </c>
-      <c r="H6" s="40" t="n">
+      <c r="H6" s="41" t="n">
         <v>435783.29</v>
       </c>
-      <c r="I6" s="40" t="n">
+      <c r="I6" s="41" t="n">
         <v>-466016.71</v>
       </c>
-      <c r="J6" s="40" t="n">
+      <c r="J6" s="41" t="n">
         <v>-550513.5600000001</v>
       </c>
-      <c r="K6" s="40" t="n">
+      <c r="K6" s="41" t="n">
         <v>-563587.0600000001</v>
       </c>
-      <c r="L6" s="40" t="n">
+      <c r="L6" s="41" t="n">
         <v>-450358.56</v>
       </c>
       <c r="M6" s="7" t="n">
@@ -4454,34 +4457,34 @@
           <t>R2 Revenue reform (1.05M)</t>
         </is>
       </c>
-      <c r="C7" s="40" t="n">
+      <c r="C7" s="41" t="n">
         <v>1050100</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="41" t="n">
         <v>1138625.22</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="41" t="n">
         <v>253626</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="41" t="n">
         <v>71321.37</v>
       </c>
-      <c r="G7" s="43" t="n">
+      <c r="G7" s="44" t="n">
         <v>2.13</v>
       </c>
-      <c r="H7" s="40" t="n">
+      <c r="H7" s="41" t="n">
         <v>839074.9399999999</v>
       </c>
-      <c r="I7" s="40" t="n">
+      <c r="I7" s="41" t="n">
         <v>-211025.06</v>
       </c>
-      <c r="J7" s="40" t="n">
+      <c r="J7" s="41" t="n">
         <v>-299550.28</v>
       </c>
-      <c r="K7" s="40" t="n">
+      <c r="K7" s="41" t="n">
         <v>-324722.53</v>
       </c>
-      <c r="L7" s="40" t="n">
+      <c r="L7" s="41" t="n">
         <v>-220684.83</v>
       </c>
       <c r="M7" s="7" t="n">
@@ -4502,34 +4505,34 @@
           <t>R3 Revenue + value engineering (900k)</t>
         </is>
       </c>
-      <c r="C8" s="40" t="n">
+      <c r="C8" s="41" t="n">
         <v>901800</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="41" t="n">
         <v>986296.85</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="41" t="n">
         <v>253626</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="41" t="n">
         <v>71321.37</v>
       </c>
-      <c r="G8" s="43" t="n">
+      <c r="G8" s="44" t="n">
         <v>2.44</v>
       </c>
-      <c r="H8" s="40" t="n">
+      <c r="H8" s="41" t="n">
         <v>839074.9399999999</v>
       </c>
-      <c r="I8" s="40" t="n">
+      <c r="I8" s="41" t="n">
         <v>-62725.06</v>
       </c>
-      <c r="J8" s="40" t="n">
+      <c r="J8" s="41" t="n">
         <v>-147221.91</v>
       </c>
-      <c r="K8" s="40" t="n">
+      <c r="K8" s="41" t="n">
         <v>-172394.16</v>
       </c>
-      <c r="L8" s="40" t="n">
+      <c r="L8" s="41" t="n">
         <v>-96377.5</v>
       </c>
       <c r="M8" s="7" t="n">
@@ -4550,34 +4553,34 @@
           <t>R4 Aggressive demand (1.05M)</t>
         </is>
       </c>
-      <c r="C9" s="40" t="n">
+      <c r="C9" s="41" t="n">
         <v>1050100</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="41" t="n">
         <v>1138625.22</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="41" t="n">
         <v>282652</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="41" t="n">
         <v>92402.75999999999</v>
       </c>
-      <c r="G9" s="43" t="n">
+      <c r="G9" s="44" t="n">
         <v>2.72</v>
       </c>
-      <c r="H9" s="40" t="n">
+      <c r="H9" s="41" t="n">
         <v>1087091.29</v>
       </c>
-      <c r="I9" s="40" t="n">
+      <c r="I9" s="41" t="n">
         <v>36991.29</v>
       </c>
-      <c r="J9" s="40" t="n">
+      <c r="J9" s="41" t="n">
         <v>-51533.93</v>
       </c>
-      <c r="K9" s="40" t="n">
+      <c r="K9" s="41" t="n">
         <v>-84146.67</v>
       </c>
-      <c r="L9" s="40" t="n">
+      <c r="L9" s="41" t="n">
         <v>3721.66</v>
       </c>
       <c r="M9" s="7" t="n">
@@ -4598,34 +4601,34 @@
           <t>R5 Lean scope (850k)</t>
         </is>
       </c>
-      <c r="C10" s="40" t="n">
+      <c r="C10" s="41" t="n">
         <v>846300</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="41" t="n">
         <v>929289.3100000001</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="41" t="n">
         <v>253626</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="41" t="n">
         <v>71321.37</v>
       </c>
-      <c r="G10" s="43" t="n">
+      <c r="G10" s="44" t="n">
         <v>2.57</v>
       </c>
-      <c r="H10" s="40" t="n">
+      <c r="H10" s="41" t="n">
         <v>839074.9399999999</v>
       </c>
-      <c r="I10" s="40" t="n">
+      <c r="I10" s="41" t="n">
         <v>-7225.06</v>
       </c>
-      <c r="J10" s="40" t="n">
+      <c r="J10" s="41" t="n">
         <v>-90214.37</v>
       </c>
-      <c r="K10" s="40" t="n">
+      <c r="K10" s="41" t="n">
         <v>-115386.62</v>
       </c>
-      <c r="L10" s="40" t="n">
+      <c r="L10" s="41" t="n">
         <v>-49105.91</v>
       </c>
       <c r="M10" s="7" t="n">
@@ -4646,34 +4649,34 @@
           <t>R6 Downside / stress</t>
         </is>
       </c>
-      <c r="C11" s="40" t="n">
+      <c r="C11" s="41" t="n">
         <v>965560</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="41" t="n">
         <v>1051789.19</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="41" t="n">
         <v>138035.1</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="41" t="n">
         <v>-33886.72</v>
       </c>
-      <c r="G11" s="43" t="n">
+      <c r="G11" s="44" t="n">
         <v>-3.82</v>
       </c>
-      <c r="H11" s="40" t="n">
+      <c r="H11" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="40" t="n">
+      <c r="I11" s="41" t="n">
         <v>-965560</v>
       </c>
-      <c r="J11" s="40" t="n">
+      <c r="J11" s="41" t="n">
         <v>-1051789.19</v>
       </c>
-      <c r="K11" s="40" t="n">
+      <c r="K11" s="41" t="n">
         <v>-1051789.19</v>
       </c>
-      <c r="L11" s="40" t="n">
+      <c r="L11" s="41" t="n">
         <v>-1021972.82</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -4697,17 +4700,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t>Bridge component</t>
         </is>
       </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B15" s="45" t="inlineStr">
         <is>
           <t>EBITDA impact (EUR)</t>
         </is>
       </c>
-      <c r="C15" s="44" t="inlineStr">
+      <c r="C15" s="45" t="inlineStr">
         <is>
           <t>EV impact @ 8.5% (EUR)</t>
         </is>
@@ -4719,10 +4722,10 @@
           <t>Base management EBITDA</t>
         </is>
       </c>
-      <c r="B16" s="45" t="n">
+      <c r="B16" s="46" t="n">
         <v>37041.58</v>
       </c>
-      <c r="C16" s="45" t="n">
+      <c r="C16" s="46" t="n">
         <v>435783.29</v>
       </c>
     </row>
@@ -4732,10 +4735,10 @@
           <t>+ ADR uplift (5%)</t>
         </is>
       </c>
-      <c r="B17" s="40" t="n">
+      <c r="B17" s="41" t="n">
         <v>7182.19</v>
       </c>
-      <c r="C17" s="40" t="n">
+      <c r="C17" s="41" t="n">
         <v>84496.35000000001</v>
       </c>
     </row>
@@ -4745,10 +4748,10 @@
           <t>+ External F&amp;B (6 covers/day)</t>
         </is>
       </c>
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="41" t="n">
         <v>13697.6</v>
       </c>
-      <c r="C18" s="40" t="n">
+      <c r="C18" s="41" t="n">
         <v>161148.24</v>
       </c>
     </row>
@@ -4758,10 +4761,10 @@
           <t>+ Experiences</t>
         </is>
       </c>
-      <c r="B19" s="40" t="n">
+      <c r="B19" s="41" t="n">
         <v>8400</v>
       </c>
-      <c r="C19" s="40" t="n">
+      <c r="C19" s="41" t="n">
         <v>98823.53</v>
       </c>
     </row>
@@ -4771,10 +4774,10 @@
           <t>+ Cost savings</t>
         </is>
       </c>
-      <c r="B20" s="40" t="n">
+      <c r="B20" s="41" t="n">
         <v>5000</v>
       </c>
-      <c r="C20" s="40" t="n">
+      <c r="C20" s="41" t="n">
         <v>58823.53</v>
       </c>
     </row>
@@ -4784,26 +4787,26 @@
           <t>Reform EBITDA and EV</t>
         </is>
       </c>
-      <c r="B21" s="45" t="n">
+      <c r="B21" s="46" t="n">
         <v>71321.37</v>
       </c>
-      <c r="C21" s="45" t="n">
+      <c r="C21" s="46" t="n">
         <v>839074.9399999999</v>
       </c>
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="46" t="inlineStr">
+      <c r="A23" s="47" t="inlineStr">
         <is>
           <t>Value test</t>
         </is>
       </c>
-      <c r="B23" s="46" t="inlineStr">
+      <c r="B23" s="47" t="inlineStr">
         <is>
           <t>Gross (EUR)</t>
         </is>
       </c>
-      <c r="C23" s="46" t="inlineStr">
+      <c r="C23" s="47" t="inlineStr">
         <is>
           <t>Net of exit costs (EUR)</t>
         </is>
@@ -4815,10 +4818,10 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B24" s="45" t="n">
+      <c r="B24" s="46" t="n">
         <v>839074.9399999999</v>
       </c>
-      <c r="C24" s="45" t="n">
+      <c r="C24" s="46" t="n">
         <v>813902.6899999999</v>
       </c>
     </row>
@@ -4828,10 +4831,10 @@
           <t>Exit costs</t>
         </is>
       </c>
-      <c r="B25" s="45" t="n">
+      <c r="B25" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="45" t="n">
+      <c r="C25" s="46" t="n">
         <v>-25172.25</v>
       </c>
     </row>
@@ -4841,10 +4844,10 @@
           <t>Reform CapEx</t>
         </is>
       </c>
-      <c r="B26" s="45" t="n">
+      <c r="B26" s="46" t="n">
         <v>1050100</v>
       </c>
-      <c r="C26" s="45" t="n">
+      <c r="C26" s="46" t="n">
         <v>1050100</v>
       </c>
     </row>
@@ -4854,10 +4857,10 @@
           <t>Value gap vs CapEx</t>
         </is>
       </c>
-      <c r="B27" s="45" t="n">
+      <c r="B27" s="46" t="n">
         <v>-211025.06</v>
       </c>
-      <c r="C27" s="45" t="n">
+      <c r="C27" s="46" t="n">
         <v>-236197.31</v>
       </c>
     </row>
@@ -4867,10 +4870,10 @@
           <t>Total project investment</t>
         </is>
       </c>
-      <c r="B28" s="45" t="n">
+      <c r="B28" s="46" t="n">
         <v>1138625.22</v>
       </c>
-      <c r="C28" s="45" t="n">
+      <c r="C28" s="46" t="n">
         <v>1138625.22</v>
       </c>
     </row>
@@ -4880,10 +4883,10 @@
           <t>Value gap vs total investment</t>
         </is>
       </c>
-      <c r="B29" s="45" t="n">
+      <c r="B29" s="46" t="n">
         <v>-299550.28</v>
       </c>
-      <c r="C29" s="45" t="n">
+      <c r="C29" s="46" t="n">
         <v>-324722.53</v>
       </c>
     </row>
@@ -4893,10 +4896,10 @@
           <t>Bridge tie (must be zero)</t>
         </is>
       </c>
-      <c r="B30" s="45" t="n">
+      <c r="B30" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C30" s="45" t="n">
+      <c r="C30" s="46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4910,124 +4913,124 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>CapEx (EUR) \ Covers/day</t>
         </is>
       </c>
-      <c r="B34" s="47" t="n">
+      <c r="B34" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="C34" s="47" t="n">
+      <c r="C34" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="48" t="n">
         <v>6</v>
       </c>
-      <c r="E34" s="47" t="n">
+      <c r="E34" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="F34" s="47" t="n">
+      <c r="F34" s="48" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="45" t="n">
+      <c r="A35" s="46" t="n">
         <v>1050100</v>
       </c>
-      <c r="B35" s="48" t="n">
+      <c r="B35" s="49" t="n">
         <v>-460698.51</v>
       </c>
-      <c r="C35" s="48" t="n">
+      <c r="C35" s="49" t="n">
         <v>-544830.28</v>
       </c>
-      <c r="D35" s="48" t="n">
+      <c r="D35" s="49" t="n">
         <v>-299550.28</v>
       </c>
-      <c r="E35" s="48" t="n">
+      <c r="E35" s="49" t="n">
         <v>-245834.16</v>
       </c>
-      <c r="F35" s="48" t="n">
+      <c r="F35" s="49" t="n">
         <v>-192118.16</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="45" t="n">
+      <c r="A36" s="46" t="n">
         <v>950000</v>
       </c>
-      <c r="B36" s="48" t="n">
+      <c r="B36" s="49" t="n">
         <v>-357879.98</v>
       </c>
-      <c r="C36" s="48" t="n">
+      <c r="C36" s="49" t="n">
         <v>-442011.75</v>
       </c>
-      <c r="D36" s="48" t="n">
+      <c r="D36" s="49" t="n">
         <v>-196731.75</v>
       </c>
-      <c r="E36" s="48" t="n">
+      <c r="E36" s="49" t="n">
         <v>-143015.63</v>
       </c>
-      <c r="F36" s="48" t="n">
+      <c r="F36" s="49" t="n">
         <v>-89299.63</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="45" t="n">
+      <c r="A37" s="46" t="n">
         <v>850000</v>
       </c>
-      <c r="B37" s="48" t="n">
+      <c r="B37" s="49" t="n">
         <v>-255162.93</v>
       </c>
-      <c r="C37" s="48" t="n">
+      <c r="C37" s="49" t="n">
         <v>-339294.7</v>
       </c>
-      <c r="D37" s="48" t="n">
+      <c r="D37" s="49" t="n">
         <v>-94014.7</v>
       </c>
-      <c r="E37" s="48" t="n">
+      <c r="E37" s="49" t="n">
         <v>-40298.58</v>
       </c>
-      <c r="F37" s="49" t="n">
+      <c r="F37" s="50" t="n">
         <v>13417.42</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="45" t="n">
+      <c r="A38" s="46" t="n">
         <v>770000</v>
       </c>
-      <c r="B38" s="48" t="n">
+      <c r="B38" s="49" t="n">
         <v>-172989.81</v>
       </c>
-      <c r="C38" s="48" t="n">
+      <c r="C38" s="49" t="n">
         <v>-257121.58</v>
       </c>
-      <c r="D38" s="48" t="n">
+      <c r="D38" s="49" t="n">
         <v>-11841.58</v>
       </c>
-      <c r="E38" s="49" t="n">
+      <c r="E38" s="50" t="n">
         <v>41874.54</v>
       </c>
-      <c r="F38" s="49" t="n">
+      <c r="F38" s="50" t="n">
         <v>95590.53999999999</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="45" t="n">
+      <c r="A39" s="46" t="n">
         <v>700000</v>
       </c>
-      <c r="B39" s="48" t="n">
+      <c r="B39" s="49" t="n">
         <v>-101088.63</v>
       </c>
-      <c r="C39" s="48" t="n">
+      <c r="C39" s="49" t="n">
         <v>-185220.4</v>
       </c>
-      <c r="D39" s="49" t="n">
+      <c r="D39" s="50" t="n">
         <v>60059.6</v>
       </c>
-      <c r="E39" s="49" t="n">
+      <c r="E39" s="50" t="n">
         <v>113775.72</v>
       </c>
-      <c r="F39" s="49" t="n">
+      <c r="F39" s="50" t="n">
         <v>167491.72</v>
       </c>
     </row>
@@ -5041,57 +5044,57 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>Stress case</t>
         </is>
       </c>
-      <c r="B43" s="46" t="inlineStr">
+      <c r="B43" s="47" t="inlineStr">
         <is>
           <t>CapEx (EUR)</t>
         </is>
       </c>
-      <c r="C43" s="46" t="inlineStr">
+      <c r="C43" s="47" t="inlineStr">
         <is>
           <t>Total inv. (EUR)</t>
         </is>
       </c>
-      <c r="D43" s="46" t="inlineStr">
+      <c r="D43" s="47" t="inlineStr">
         <is>
           <t>EBITDA Y5 (EUR)</t>
         </is>
       </c>
-      <c r="E43" s="46" t="inlineStr">
+      <c r="E43" s="47" t="inlineStr">
         <is>
           <t>Min DSCR</t>
         </is>
       </c>
-      <c r="F43" s="46" t="inlineStr">
+      <c r="F43" s="47" t="inlineStr">
         <is>
           <t>EV (EUR)</t>
         </is>
       </c>
-      <c r="G43" s="46" t="inlineStr">
+      <c r="G43" s="47" t="inlineStr">
         <is>
           <t>Gap vs total inv. (EUR)</t>
         </is>
       </c>
-      <c r="H43" s="46" t="inlineStr">
+      <c r="H43" s="47" t="inlineStr">
         <is>
           <t>Net gap vs total inv. (EUR)</t>
         </is>
       </c>
-      <c r="I43" s="46" t="inlineStr">
+      <c r="I43" s="47" t="inlineStr">
         <is>
           <t>Project NPV (EUR)</t>
         </is>
       </c>
-      <c r="J43" s="46" t="inlineStr">
+      <c r="J43" s="47" t="inlineStr">
         <is>
           <t>Project IRR</t>
         </is>
       </c>
-      <c r="K43" s="46" t="inlineStr">
+      <c r="K43" s="47" t="inlineStr">
         <is>
           <t>Equity IRR</t>
         </is>
@@ -5103,28 +5106,28 @@
           <t>As-is reform (R2)</t>
         </is>
       </c>
-      <c r="B44" s="40" t="n">
+      <c r="B44" s="41" t="n">
         <v>1050100</v>
       </c>
-      <c r="C44" s="40" t="n">
+      <c r="C44" s="41" t="n">
         <v>1138625.22</v>
       </c>
-      <c r="D44" s="40" t="n">
+      <c r="D44" s="41" t="n">
         <v>71321.37</v>
       </c>
-      <c r="E44" s="43" t="n">
+      <c r="E44" s="44" t="n">
         <v>2.13</v>
       </c>
-      <c r="F44" s="40" t="n">
+      <c r="F44" s="41" t="n">
         <v>839074.9399999999</v>
       </c>
-      <c r="G44" s="40" t="n">
+      <c r="G44" s="41" t="n">
         <v>-299550.28</v>
       </c>
-      <c r="H44" s="40" t="n">
+      <c r="H44" s="41" t="n">
         <v>-324722.53</v>
       </c>
-      <c r="I44" s="40" t="n">
+      <c r="I44" s="41" t="n">
         <v>-220684.83</v>
       </c>
       <c r="J44" s="7" t="n">
@@ -5140,28 +5143,28 @@
           <t>R2 + INE 21.24% demand</t>
         </is>
       </c>
-      <c r="B45" s="40" t="n">
+      <c r="B45" s="41" t="n">
         <v>1050100</v>
       </c>
-      <c r="C45" s="40" t="n">
+      <c r="C45" s="41" t="n">
         <v>1138625.22</v>
       </c>
-      <c r="D45" s="40" t="n">
+      <c r="D45" s="41" t="n">
         <v>27821.26</v>
       </c>
-      <c r="E45" s="43" t="n">
+      <c r="E45" s="44" t="n">
         <v>-0.08</v>
       </c>
-      <c r="F45" s="40" t="n">
+      <c r="F45" s="41" t="n">
         <v>327308.94</v>
       </c>
-      <c r="G45" s="40" t="n">
+      <c r="G45" s="41" t="n">
         <v>-811316.28</v>
       </c>
-      <c r="H45" s="40" t="n">
+      <c r="H45" s="41" t="n">
         <v>-821135.55</v>
       </c>
-      <c r="I45" s="40" t="n">
+      <c r="I45" s="41" t="n">
         <v>-689417.96</v>
       </c>
       <c r="J45" s="7" t="n">
@@ -5177,28 +5180,28 @@
           <t>R2 + covers -50%</t>
         </is>
       </c>
-      <c r="B46" s="40" t="n">
+      <c r="B46" s="41" t="n">
         <v>1050100</v>
       </c>
-      <c r="C46" s="40" t="n">
+      <c r="C46" s="41" t="n">
         <v>1138625.22</v>
       </c>
-      <c r="D46" s="40" t="n">
+      <c r="D46" s="41" t="n">
         <v>50472.57</v>
       </c>
-      <c r="E46" s="43" t="n">
+      <c r="E46" s="44" t="n">
         <v>1.48</v>
       </c>
-      <c r="F46" s="40" t="n">
+      <c r="F46" s="41" t="n">
         <v>593794.9399999999</v>
       </c>
-      <c r="G46" s="40" t="n">
+      <c r="G46" s="41" t="n">
         <v>-544830.28</v>
       </c>
-      <c r="H46" s="40" t="n">
+      <c r="H46" s="41" t="n">
         <v>-562644.13</v>
       </c>
-      <c r="I46" s="40" t="n">
+      <c r="I46" s="41" t="n">
         <v>-441028.47</v>
       </c>
       <c r="J46" s="7" t="n">
@@ -5214,28 +5217,28 @@
           <t>R3 + CapEx +20%</t>
         </is>
       </c>
-      <c r="B47" s="40" t="n">
+      <c r="B47" s="41" t="n">
         <v>1032160</v>
       </c>
-      <c r="C47" s="40" t="n">
+      <c r="C47" s="41" t="n">
         <v>1120197.9</v>
       </c>
-      <c r="D47" s="40" t="n">
+      <c r="D47" s="41" t="n">
         <v>71321.37</v>
       </c>
-      <c r="E47" s="43" t="n">
+      <c r="E47" s="44" t="n">
         <v>2.17</v>
       </c>
-      <c r="F47" s="40" t="n">
+      <c r="F47" s="41" t="n">
         <v>839074.9399999999</v>
       </c>
-      <c r="G47" s="40" t="n">
+      <c r="G47" s="41" t="n">
         <v>-281122.96</v>
       </c>
-      <c r="H47" s="40" t="n">
+      <c r="H47" s="41" t="n">
         <v>-306295.21</v>
       </c>
-      <c r="I47" s="40" t="n">
+      <c r="I47" s="41" t="n">
         <v>-206843.7</v>
       </c>
       <c r="J47" s="7" t="n">
@@ -5251,28 +5254,28 @@
           <t>R3 + LEADER delayed to Y3</t>
         </is>
       </c>
-      <c r="B48" s="40" t="n">
+      <c r="B48" s="41" t="n">
         <v>901800</v>
       </c>
-      <c r="C48" s="40" t="n">
+      <c r="C48" s="41" t="n">
         <v>986296.85</v>
       </c>
-      <c r="D48" s="40" t="n">
+      <c r="D48" s="41" t="n">
         <v>71321.37</v>
       </c>
-      <c r="E48" s="43" t="n">
+      <c r="E48" s="44" t="n">
         <v>2.44</v>
       </c>
-      <c r="F48" s="40" t="n">
+      <c r="F48" s="41" t="n">
         <v>839074.9399999999</v>
       </c>
-      <c r="G48" s="40" t="n">
+      <c r="G48" s="41" t="n">
         <v>-147221.91</v>
       </c>
-      <c r="H48" s="40" t="n">
+      <c r="H48" s="41" t="n">
         <v>-172394.16</v>
       </c>
-      <c r="I48" s="40" t="n">
+      <c r="I48" s="41" t="n">
         <v>-105254.39</v>
       </c>
       <c r="J48" s="7" t="n">
@@ -5288,28 +5291,28 @@
           <t>R3 + no LEADER grant</t>
         </is>
       </c>
-      <c r="B49" s="40" t="n">
+      <c r="B49" s="41" t="n">
         <v>901800</v>
       </c>
-      <c r="C49" s="40" t="n">
+      <c r="C49" s="41" t="n">
         <v>986296.85</v>
       </c>
-      <c r="D49" s="40" t="n">
+      <c r="D49" s="41" t="n">
         <v>71321.37</v>
       </c>
-      <c r="E49" s="43" t="n">
+      <c r="E49" s="44" t="n">
         <v>2.44</v>
       </c>
-      <c r="F49" s="40" t="n">
+      <c r="F49" s="41" t="n">
         <v>839074.9399999999</v>
       </c>
-      <c r="G49" s="40" t="n">
+      <c r="G49" s="41" t="n">
         <v>-147221.91</v>
       </c>
-      <c r="H49" s="40" t="n">
+      <c r="H49" s="41" t="n">
         <v>-172394.16</v>
       </c>
-      <c r="I49" s="40" t="n">
+      <c r="I49" s="41" t="n">
         <v>-216215.47</v>
       </c>
       <c r="J49" s="7" t="n">
@@ -5325,28 +5328,28 @@
           <t>R3 + rate +200 bp</t>
         </is>
       </c>
-      <c r="B50" s="40" t="n">
+      <c r="B50" s="41" t="n">
         <v>901800</v>
       </c>
-      <c r="C50" s="40" t="n">
+      <c r="C50" s="41" t="n">
         <v>988365</v>
       </c>
-      <c r="D50" s="40" t="n">
+      <c r="D50" s="41" t="n">
         <v>71321.37</v>
       </c>
-      <c r="E50" s="43" t="n">
+      <c r="E50" s="44" t="n">
         <v>1.92</v>
       </c>
-      <c r="F50" s="40" t="n">
+      <c r="F50" s="41" t="n">
         <v>839074.9399999999</v>
       </c>
-      <c r="G50" s="40" t="n">
+      <c r="G50" s="41" t="n">
         <v>-149290.06</v>
       </c>
-      <c r="H50" s="40" t="n">
+      <c r="H50" s="41" t="n">
         <v>-174462.31</v>
       </c>
-      <c r="I50" s="40" t="n">
+      <c r="I50" s="41" t="n">
         <v>-98445.64999999999</v>
       </c>
       <c r="J50" s="7" t="n">
@@ -5362,28 +5365,28 @@
           <t>R3 + conservative demand</t>
         </is>
       </c>
-      <c r="B51" s="40" t="n">
+      <c r="B51" s="41" t="n">
         <v>901800</v>
       </c>
-      <c r="C51" s="40" t="n">
+      <c r="C51" s="41" t="n">
         <v>987831.24</v>
       </c>
-      <c r="D51" s="40" t="n">
+      <c r="D51" s="41" t="n">
         <v>33333.95</v>
       </c>
-      <c r="E51" s="43" t="n">
+      <c r="E51" s="44" t="n">
         <v>0.12</v>
       </c>
-      <c r="F51" s="40" t="n">
+      <c r="F51" s="41" t="n">
         <v>392164.12</v>
       </c>
-      <c r="G51" s="40" t="n">
+      <c r="G51" s="41" t="n">
         <v>-595667.12</v>
       </c>
-      <c r="H51" s="40" t="n">
+      <c r="H51" s="41" t="n">
         <v>-607432.04</v>
       </c>
-      <c r="I51" s="40" t="n">
+      <c r="I51" s="41" t="n">
         <v>-509916.1</v>
       </c>
       <c r="J51" s="7" t="n">
@@ -5399,28 +5402,28 @@
           <t>R6 combined downside</t>
         </is>
       </c>
-      <c r="B52" s="40" t="n">
+      <c r="B52" s="41" t="n">
         <v>965560</v>
       </c>
-      <c r="C52" s="40" t="n">
+      <c r="C52" s="41" t="n">
         <v>1051789.19</v>
       </c>
-      <c r="D52" s="40" t="n">
+      <c r="D52" s="41" t="n">
         <v>-33886.72</v>
       </c>
-      <c r="E52" s="43" t="n">
+      <c r="E52" s="44" t="n">
         <v>-3.82</v>
       </c>
-      <c r="F52" s="40" t="n">
+      <c r="F52" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="40" t="n">
+      <c r="G52" s="41" t="n">
         <v>-1051789.19</v>
       </c>
-      <c r="H52" s="40" t="n">
+      <c r="H52" s="41" t="n">
         <v>-1051789.19</v>
       </c>
-      <c r="I52" s="40" t="n">
+      <c r="I52" s="41" t="n">
         <v>-1021972.82</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
@@ -5444,114 +5447,114 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>Rate shock (bp)</t>
         </is>
       </c>
-      <c r="B56" s="46" t="inlineStr">
+      <c r="B56" s="47" t="inlineStr">
         <is>
           <t>Interest rate</t>
         </is>
       </c>
-      <c r="C56" s="46" t="inlineStr">
+      <c r="C56" s="47" t="inlineStr">
         <is>
           <t>Min DSCR</t>
         </is>
       </c>
-      <c r="D56" s="46" t="inlineStr">
+      <c r="D56" s="47" t="inlineStr">
         <is>
           <t>Project NPV (EUR)</t>
         </is>
       </c>
-      <c r="E56" s="46" t="inlineStr">
+      <c r="E56" s="47" t="inlineStr">
         <is>
           <t>Gap vs total inv. (EUR)</t>
         </is>
       </c>
-      <c r="F56" s="46" t="inlineStr">
+      <c r="F56" s="47" t="inlineStr">
         <is>
           <t>Net gap vs total inv. (EUR)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="50" t="n">
+      <c r="A57" s="51" t="n">
         <v>0</v>
       </c>
       <c r="B57" s="7" t="n">
         <v>0.04</v>
       </c>
-      <c r="C57" s="43" t="n">
+      <c r="C57" s="44" t="n">
         <v>2.13</v>
       </c>
-      <c r="D57" s="40" t="n">
+      <c r="D57" s="41" t="n">
         <v>-220684.83</v>
       </c>
-      <c r="E57" s="40" t="n">
+      <c r="E57" s="41" t="n">
         <v>-299550.28</v>
       </c>
-      <c r="F57" s="40" t="n">
+      <c r="F57" s="41" t="n">
         <v>-324722.53</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="50" t="n">
+      <c r="A58" s="51" t="n">
         <v>100</v>
       </c>
       <c r="B58" s="7" t="n">
         <v>0.05</v>
       </c>
-      <c r="C58" s="43" t="n">
+      <c r="C58" s="44" t="n">
         <v>1.96</v>
       </c>
-      <c r="D58" s="40" t="n">
+      <c r="D58" s="41" t="n">
         <v>-221862.57</v>
       </c>
-      <c r="E58" s="40" t="n">
+      <c r="E58" s="41" t="n">
         <v>-300728.02</v>
       </c>
-      <c r="F58" s="40" t="n">
+      <c r="F58" s="41" t="n">
         <v>-325900.27</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="50" t="n">
+      <c r="A59" s="51" t="n">
         <v>200</v>
       </c>
       <c r="B59" s="7" t="n">
         <v>0.06</v>
       </c>
-      <c r="C59" s="43" t="n">
+      <c r="C59" s="44" t="n">
         <v>1.65</v>
       </c>
-      <c r="D59" s="40" t="n">
+      <c r="D59" s="41" t="n">
         <v>-223093.76</v>
       </c>
-      <c r="E59" s="40" t="n">
+      <c r="E59" s="41" t="n">
         <v>-301959.21</v>
       </c>
-      <c r="F59" s="40" t="n">
+      <c r="F59" s="41" t="n">
         <v>-327131.46</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="50" t="n">
+      <c r="A60" s="51" t="n">
         <v>300</v>
       </c>
       <c r="B60" s="7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C60" s="43" t="n">
+      <c r="C60" s="44" t="n">
         <v>1.41</v>
       </c>
-      <c r="D60" s="40" t="n">
+      <c r="D60" s="41" t="n">
         <v>-224375.72</v>
       </c>
-      <c r="E60" s="40" t="n">
+      <c r="E60" s="41" t="n">
         <v>-303241.17</v>
       </c>
-      <c r="F60" s="40" t="n">
+      <c r="F60" s="41" t="n">
         <v>-328413.42</v>
       </c>
     </row>
@@ -5565,7 +5568,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="51" t="inlineStr">
+      <c r="A64" s="52" t="inlineStr">
         <is>
           <t>DECLINE AS STRUCTURED - ONLY THE AGGRESSIVE, UNPROVEN DEMAND CASE CLEARS THE WACC</t>
         </is>
@@ -5658,62 +5661,62 @@
     </row>
     <row r="78"/>
     <row r="79">
-      <c r="A79" s="42" t="inlineStr">
+      <c r="A79" s="43" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B79" s="42" t="inlineStr">
+      <c r="B79" s="43" t="inlineStr">
         <is>
           <t>Cabins</t>
         </is>
       </c>
-      <c r="C79" s="42" t="inlineStr">
+      <c r="C79" s="43" t="inlineStr">
         <is>
           <t>ADR (EUR)</t>
         </is>
       </c>
-      <c r="D79" s="42" t="inlineStr">
+      <c r="D79" s="43" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="E79" s="42" t="inlineStr">
+      <c r="E79" s="43" t="inlineStr">
         <is>
           <t>Cost / cabin (EUR)</t>
         </is>
       </c>
-      <c r="F79" s="42" t="inlineStr">
+      <c r="F79" s="43" t="inlineStr">
         <is>
           <t>CapEx (EUR)</t>
         </is>
       </c>
-      <c r="G79" s="42" t="inlineStr">
+      <c r="G79" s="43" t="inlineStr">
         <is>
           <t>Total inv. (EUR)</t>
         </is>
       </c>
-      <c r="H79" s="42" t="inlineStr">
+      <c r="H79" s="43" t="inlineStr">
         <is>
           <t>EBITDA Y5 (EUR)</t>
         </is>
       </c>
-      <c r="I79" s="42" t="inlineStr">
+      <c r="I79" s="43" t="inlineStr">
         <is>
           <t>Min DSCR</t>
         </is>
       </c>
-      <c r="J79" s="42" t="inlineStr">
+      <c r="J79" s="43" t="inlineStr">
         <is>
           <t>Net gap vs total inv. (EUR)</t>
         </is>
       </c>
-      <c r="K79" s="42" t="inlineStr">
+      <c r="K79" s="43" t="inlineStr">
         <is>
           <t>Project NPV (EUR)</t>
         </is>
       </c>
-      <c r="L79" s="42" t="inlineStr">
+      <c r="L79" s="43" t="inlineStr">
         <is>
           <t>Project IRR</t>
         </is>
@@ -5728,31 +5731,31 @@
       <c r="B80" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C80" s="40" t="n">
+      <c r="C80" s="41" t="n">
         <v>200</v>
       </c>
-      <c r="D80" s="52" t="n">
+      <c r="D80" s="53" t="n">
         <v>0.5</v>
       </c>
-      <c r="E80" s="40" t="n">
+      <c r="E80" s="41" t="n">
         <v>110000</v>
       </c>
-      <c r="F80" s="40" t="n">
+      <c r="F80" s="41" t="n">
         <v>1441600</v>
       </c>
-      <c r="G80" s="40" t="n">
+      <c r="G80" s="41" t="n">
         <v>1540760.04</v>
       </c>
-      <c r="H80" s="40" t="n">
+      <c r="H80" s="41" t="n">
         <v>155712.5</v>
       </c>
-      <c r="I80" s="43" t="n">
+      <c r="I80" s="44" t="n">
         <v>1.41</v>
       </c>
-      <c r="J80" s="40" t="n">
+      <c r="J80" s="41" t="n">
         <v>49146.54</v>
       </c>
-      <c r="K80" s="40" t="n">
+      <c r="K80" s="41" t="n">
         <v>76416.23</v>
       </c>
       <c r="L80" s="7" t="n">
@@ -5768,31 +5771,31 @@
       <c r="B81" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C81" s="40" t="n">
+      <c r="C81" s="41" t="n">
         <v>230</v>
       </c>
-      <c r="D81" s="52" t="n">
+      <c r="D81" s="53" t="n">
         <v>0.55</v>
       </c>
-      <c r="E81" s="40" t="n">
+      <c r="E81" s="41" t="n">
         <v>150000</v>
       </c>
-      <c r="F81" s="40" t="n">
+      <c r="F81" s="41" t="n">
         <v>1708000</v>
       </c>
-      <c r="G81" s="40" t="n">
+      <c r="G81" s="41" t="n">
         <v>1814396.63</v>
       </c>
-      <c r="H81" s="40" t="n">
+      <c r="H81" s="41" t="n">
         <v>227340.1</v>
       </c>
-      <c r="I81" s="43" t="n">
+      <c r="I81" s="44" t="n">
         <v>3.3</v>
       </c>
-      <c r="J81" s="40" t="n">
+      <c r="J81" s="41" t="n">
         <v>506865.44</v>
       </c>
-      <c r="K81" s="40" t="n">
+      <c r="K81" s="41" t="n">
         <v>509113.02</v>
       </c>
       <c r="L81" s="7" t="n">
@@ -5808,31 +5811,31 @@
       <c r="B82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C82" s="40" t="n">
+      <c r="C82" s="41" t="n">
         <v>190</v>
       </c>
-      <c r="D82" s="52" t="n">
+      <c r="D82" s="53" t="n">
         <v>0.45</v>
       </c>
-      <c r="E82" s="40" t="n">
+      <c r="E82" s="41" t="n">
         <v>150000</v>
       </c>
-      <c r="F82" s="40" t="n">
+      <c r="F82" s="41" t="n">
         <v>1541500</v>
       </c>
-      <c r="G82" s="40" t="n">
+      <c r="G82" s="41" t="n">
         <v>1643374.02</v>
       </c>
-      <c r="H82" s="40" t="n">
+      <c r="H82" s="41" t="n">
         <v>71597.62</v>
       </c>
-      <c r="I82" s="43" t="n">
+      <c r="I82" s="44" t="n">
         <v>0.79</v>
       </c>
-      <c r="J82" s="40" t="n">
+      <c r="J82" s="41" t="n">
         <v>-988767.2</v>
       </c>
-      <c r="K82" s="40" t="n">
+      <c r="K82" s="41" t="n">
         <v>-878138.02</v>
       </c>
       <c r="L82" s="7" t="n">
@@ -5849,214 +5852,214 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="42" t="inlineStr">
+      <c r="A86" s="43" t="inlineStr">
         <is>
           <t>Cost / cabin (EUR)</t>
         </is>
       </c>
-      <c r="B86" s="42" t="inlineStr">
+      <c r="B86" s="43" t="inlineStr">
         <is>
           <t>CapEx (EUR)</t>
         </is>
       </c>
-      <c r="C86" s="42" t="inlineStr">
+      <c r="C86" s="43" t="inlineStr">
         <is>
           <t>Total inv. (EUR)</t>
         </is>
       </c>
-      <c r="D86" s="42" t="inlineStr">
+      <c r="D86" s="43" t="inlineStr">
         <is>
           <t>EBITDA Y5 (EUR)</t>
         </is>
       </c>
-      <c r="E86" s="42" t="inlineStr">
+      <c r="E86" s="43" t="inlineStr">
         <is>
           <t>EV (EUR)</t>
         </is>
       </c>
-      <c r="F86" s="42" t="inlineStr">
+      <c r="F86" s="43" t="inlineStr">
         <is>
           <t>Gap vs CapEx (EUR)</t>
         </is>
       </c>
-      <c r="G86" s="42" t="inlineStr">
+      <c r="G86" s="43" t="inlineStr">
         <is>
           <t>Gap vs total inv. (EUR)</t>
         </is>
       </c>
-      <c r="H86" s="42" t="inlineStr">
+      <c r="H86" s="43" t="inlineStr">
         <is>
           <t>Net gap vs total inv. (EUR)</t>
         </is>
       </c>
-      <c r="I86" s="42" t="inlineStr">
+      <c r="I86" s="43" t="inlineStr">
         <is>
           <t>Min DSCR</t>
         </is>
       </c>
-      <c r="J86" s="42" t="inlineStr">
+      <c r="J86" s="43" t="inlineStr">
         <is>
           <t>Project NPV (EUR)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="45" t="n">
+      <c r="A87" s="46" t="n">
         <v>110000</v>
       </c>
-      <c r="B87" s="40" t="n">
+      <c r="B87" s="41" t="n">
         <v>1441600</v>
       </c>
-      <c r="C87" s="40" t="n">
+      <c r="C87" s="41" t="n">
         <v>1540760.04</v>
       </c>
-      <c r="D87" s="40" t="n">
+      <c r="D87" s="41" t="n">
         <v>155712.5</v>
       </c>
-      <c r="E87" s="40" t="n">
+      <c r="E87" s="41" t="n">
         <v>1639078.95</v>
       </c>
-      <c r="F87" s="40" t="n">
+      <c r="F87" s="41" t="n">
         <v>197478.95</v>
       </c>
-      <c r="G87" s="40" t="n">
+      <c r="G87" s="41" t="n">
         <v>98318.91</v>
       </c>
-      <c r="H87" s="49" t="n">
+      <c r="H87" s="50" t="n">
         <v>49146.54</v>
       </c>
-      <c r="I87" s="43" t="n">
+      <c r="I87" s="44" t="n">
         <v>1.41</v>
       </c>
-      <c r="J87" s="40" t="n">
+      <c r="J87" s="41" t="n">
         <v>76416.23</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="45" t="n">
+      <c r="A88" s="46" t="n">
         <v>120000</v>
       </c>
-      <c r="B88" s="40" t="n">
+      <c r="B88" s="41" t="n">
         <v>1508200</v>
       </c>
-      <c r="C88" s="40" t="n">
+      <c r="C88" s="41" t="n">
         <v>1609169.17</v>
       </c>
-      <c r="D88" s="40" t="n">
+      <c r="D88" s="41" t="n">
         <v>155712.5</v>
       </c>
-      <c r="E88" s="40" t="n">
+      <c r="E88" s="41" t="n">
         <v>1639078.95</v>
       </c>
-      <c r="F88" s="40" t="n">
+      <c r="F88" s="41" t="n">
         <v>130878.95</v>
       </c>
-      <c r="G88" s="40" t="n">
+      <c r="G88" s="41" t="n">
         <v>29909.78</v>
       </c>
-      <c r="H88" s="48" t="n">
+      <c r="H88" s="49" t="n">
         <v>-19262.59</v>
       </c>
-      <c r="I88" s="43" t="n">
+      <c r="I88" s="44" t="n">
         <v>1.35</v>
       </c>
-      <c r="J88" s="40" t="n">
+      <c r="J88" s="41" t="n">
         <v>10001.46</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="45" t="n">
+      <c r="A89" s="46" t="n">
         <v>130000</v>
       </c>
-      <c r="B89" s="40" t="n">
+      <c r="B89" s="41" t="n">
         <v>1574800</v>
       </c>
-      <c r="C89" s="40" t="n">
+      <c r="C89" s="41" t="n">
         <v>1677578.94</v>
       </c>
-      <c r="D89" s="40" t="n">
+      <c r="D89" s="41" t="n">
         <v>155712.5</v>
       </c>
-      <c r="E89" s="40" t="n">
+      <c r="E89" s="41" t="n">
         <v>1639078.95</v>
       </c>
-      <c r="F89" s="40" t="n">
+      <c r="F89" s="41" t="n">
         <v>64278.95</v>
       </c>
-      <c r="G89" s="40" t="n">
+      <c r="G89" s="41" t="n">
         <v>-38499.99</v>
       </c>
-      <c r="H89" s="48" t="n">
+      <c r="H89" s="49" t="n">
         <v>-87672.36</v>
       </c>
-      <c r="I89" s="43" t="n">
+      <c r="I89" s="44" t="n">
         <v>1.29</v>
       </c>
-      <c r="J89" s="40" t="n">
+      <c r="J89" s="41" t="n">
         <v>-56413.95</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="45" t="n">
+      <c r="A90" s="46" t="n">
         <v>150000</v>
       </c>
-      <c r="B90" s="40" t="n">
+      <c r="B90" s="41" t="n">
         <v>1708000</v>
       </c>
-      <c r="C90" s="40" t="n">
+      <c r="C90" s="41" t="n">
         <v>1814396.63</v>
       </c>
-      <c r="D90" s="40" t="n">
+      <c r="D90" s="41" t="n">
         <v>155712.5</v>
       </c>
-      <c r="E90" s="40" t="n">
+      <c r="E90" s="41" t="n">
         <v>1639078.95</v>
       </c>
-      <c r="F90" s="40" t="n">
+      <c r="F90" s="41" t="n">
         <v>-68921.05</v>
       </c>
-      <c r="G90" s="40" t="n">
+      <c r="G90" s="41" t="n">
         <v>-175317.68</v>
       </c>
-      <c r="H90" s="48" t="n">
+      <c r="H90" s="49" t="n">
         <v>-224490.05</v>
       </c>
-      <c r="I90" s="43" t="n">
+      <c r="I90" s="44" t="n">
         <v>1.19</v>
       </c>
-      <c r="J90" s="40" t="n">
+      <c r="J90" s="41" t="n">
         <v>-189242.92</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="45" t="n">
+      <c r="A91" s="46" t="n">
         <v>180000</v>
       </c>
-      <c r="B91" s="40" t="n">
+      <c r="B91" s="41" t="n">
         <v>1907800</v>
       </c>
-      <c r="C91" s="40" t="n">
+      <c r="C91" s="41" t="n">
         <v>2019624.19</v>
       </c>
-      <c r="D91" s="40" t="n">
+      <c r="D91" s="41" t="n">
         <v>155712.5</v>
       </c>
-      <c r="E91" s="40" t="n">
+      <c r="E91" s="41" t="n">
         <v>1639078.95</v>
       </c>
-      <c r="F91" s="40" t="n">
+      <c r="F91" s="41" t="n">
         <v>-268721.05</v>
       </c>
-      <c r="G91" s="40" t="n">
+      <c r="G91" s="41" t="n">
         <v>-380545.24</v>
       </c>
-      <c r="H91" s="48" t="n">
+      <c r="H91" s="49" t="n">
         <v>-429717.61</v>
       </c>
-      <c r="I91" s="43" t="n">
+      <c r="I91" s="44" t="n">
         <v>1.07</v>
       </c>
-      <c r="J91" s="40" t="n">
+      <c r="J91" s="41" t="n">
         <v>-388487.41</v>
       </c>
     </row>
@@ -6070,7 +6073,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="53" t="inlineStr">
+      <c r="A95" s="54" t="inlineStr">
         <is>
           <t>CONDITIONAL PROCEED TO PHASE 0 - PREMIUM CABINS PASS ON PAPER, BUT ONLY AT 110K PER CABIN</t>
         </is>
@@ -6185,7 +6188,7 @@
           <t>Cap-rate headroom (bp)</t>
         </is>
       </c>
-      <c r="B112" s="54" t="n">
+      <c r="B112" s="55" t="n">
         <v>30.3</v>
       </c>
     </row>
@@ -6195,7 +6198,7 @@
           <t>No-compression net gap (EUR)</t>
         </is>
       </c>
-      <c r="B113" s="40" t="n">
+      <c r="B113" s="41" t="n">
         <v>-46222.8</v>
       </c>
     </row>
@@ -6205,7 +6208,7 @@
           <t>Break-even EBITDA, net (EUR)</t>
         </is>
       </c>
-      <c r="B114" s="40" t="n">
+      <c r="B114" s="41" t="n">
         <v>150899.18</v>
       </c>
     </row>
@@ -6215,7 +6218,7 @@
           <t>EBITDA headroom (EUR)</t>
         </is>
       </c>
-      <c r="B115" s="40" t="n">
+      <c r="B115" s="41" t="n">
         <v>4813.32</v>
       </c>
     </row>
@@ -6225,72 +6228,72 @@
           <t>Implied exit multiple</t>
         </is>
       </c>
-      <c r="B116" s="43" t="n">
+      <c r="B116" s="44" t="n">
         <v>10.53</v>
       </c>
     </row>
     <row r="117"/>
     <row r="118">
-      <c r="A118" s="42" t="inlineStr">
+      <c r="A118" s="43" t="inlineStr">
         <is>
           <t>Exit multiple</t>
         </is>
       </c>
-      <c r="B118" s="42" t="inlineStr">
+      <c r="B118" s="43" t="inlineStr">
         <is>
           <t>EV (EUR)</t>
         </is>
       </c>
-      <c r="C118" s="42" t="inlineStr">
+      <c r="C118" s="43" t="inlineStr">
         <is>
           <t>Net exit value (EUR)</t>
         </is>
       </c>
-      <c r="D118" s="42" t="inlineStr">
+      <c r="D118" s="43" t="inlineStr">
         <is>
           <t>Net gap vs total inv. (EUR)</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="55" t="n">
+      <c r="A119" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="B119" s="40" t="n">
+      <c r="B119" s="41" t="n">
         <v>1401412.5</v>
       </c>
-      <c r="C119" s="40" t="n">
+      <c r="C119" s="41" t="n">
         <v>1359370.12</v>
       </c>
-      <c r="D119" s="48" t="n">
+      <c r="D119" s="49" t="n">
         <v>-181389.92</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="55" t="n">
+      <c r="A120" s="56" t="n">
         <v>10.5</v>
       </c>
-      <c r="B120" s="40" t="n">
+      <c r="B120" s="41" t="n">
         <v>1634981.25</v>
       </c>
-      <c r="C120" s="40" t="n">
+      <c r="C120" s="41" t="n">
         <v>1585931.81</v>
       </c>
-      <c r="D120" s="49" t="n">
+      <c r="D120" s="50" t="n">
         <v>45171.77</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="55" t="n">
+      <c r="A121" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="B121" s="40" t="n">
+      <c r="B121" s="41" t="n">
         <v>1868550</v>
       </c>
-      <c r="C121" s="40" t="n">
+      <c r="C121" s="41" t="n">
         <v>1812493.5</v>
       </c>
-      <c r="D121" s="49" t="n">
+      <c r="D121" s="50" t="n">
         <v>271733.46</v>
       </c>
     </row>
@@ -6304,171 +6307,171 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="42" t="inlineStr">
+      <c r="A125" s="43" t="inlineStr">
         <is>
           <t>Cost inflation / yr</t>
         </is>
       </c>
-      <c r="B125" s="42" t="inlineStr">
+      <c r="B125" s="43" t="inlineStr">
         <is>
           <t>EBITDA Y5 (EUR)</t>
         </is>
       </c>
-      <c r="C125" s="42" t="inlineStr">
+      <c r="C125" s="43" t="inlineStr">
         <is>
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="D125" s="42" t="inlineStr">
+      <c r="D125" s="43" t="inlineStr">
         <is>
           <t>DSCR Y5</t>
         </is>
       </c>
-      <c r="E125" s="42" t="inlineStr">
+      <c r="E125" s="43" t="inlineStr">
         <is>
           <t>EV (EUR)</t>
         </is>
       </c>
-      <c r="F125" s="42" t="inlineStr">
+      <c r="F125" s="43" t="inlineStr">
         <is>
           <t>Net gap vs total inv. (EUR)</t>
         </is>
       </c>
-      <c r="G125" s="42" t="inlineStr">
+      <c r="G125" s="43" t="inlineStr">
         <is>
           <t>Project NPV (EUR)</t>
         </is>
       </c>
-      <c r="H125" s="42" t="inlineStr">
+      <c r="H125" s="43" t="inlineStr">
         <is>
           <t>Project IRR</t>
         </is>
       </c>
-      <c r="I125" s="42" t="inlineStr">
+      <c r="I125" s="43" t="inlineStr">
         <is>
           <t>Net test</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="56" t="n">
+      <c r="A126" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="B126" s="40" t="n">
+      <c r="B126" s="41" t="n">
         <v>155712.5</v>
       </c>
-      <c r="C126" s="56" t="n">
+      <c r="C126" s="57" t="n">
         <v>0.2717</v>
       </c>
-      <c r="D126" s="43" t="n">
+      <c r="D126" s="44" t="n">
         <v>3.15</v>
       </c>
-      <c r="E126" s="40" t="n">
+      <c r="E126" s="41" t="n">
         <v>1639078.95</v>
       </c>
-      <c r="F126" s="40" t="n">
+      <c r="F126" s="41" t="n">
         <v>49146.54</v>
       </c>
-      <c r="G126" s="40" t="n">
+      <c r="G126" s="41" t="n">
         <v>76416.23</v>
       </c>
       <c r="H126" s="7" t="n">
         <v>0.092088</v>
       </c>
-      <c r="I126" s="57" t="inlineStr">
+      <c r="I126" s="58" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="56" t="n">
+      <c r="A127" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="B127" s="40" t="n">
+      <c r="B127" s="41" t="n">
         <v>136911.79</v>
       </c>
-      <c r="C127" s="56" t="n">
+      <c r="C127" s="57" t="n">
         <v>0.2389</v>
       </c>
-      <c r="D127" s="43" t="n">
+      <c r="D127" s="44" t="n">
         <v>2.78</v>
       </c>
-      <c r="E127" s="40" t="n">
+      <c r="E127" s="41" t="n">
         <v>1441176.74</v>
       </c>
-      <c r="F127" s="40" t="n">
+      <c r="F127" s="41" t="n">
         <v>-142818.6</v>
       </c>
-      <c r="G127" s="40" t="n">
+      <c r="G127" s="41" t="n">
         <v>-83984.03</v>
       </c>
       <c r="H127" s="7" t="n">
         <v>0.06605999999999999</v>
       </c>
-      <c r="I127" s="58" t="inlineStr">
+      <c r="I127" s="59" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="56" t="n">
+      <c r="A128" s="57" t="n">
         <v>0.025</v>
       </c>
-      <c r="B128" s="40" t="n">
+      <c r="B128" s="41" t="n">
         <v>132035.38</v>
       </c>
-      <c r="C128" s="56" t="n">
+      <c r="C128" s="57" t="n">
         <v>0.2304</v>
       </c>
-      <c r="D128" s="43" t="n">
+      <c r="D128" s="44" t="n">
         <v>2.69</v>
       </c>
-      <c r="E128" s="40" t="n">
+      <c r="E128" s="41" t="n">
         <v>1389846.11</v>
       </c>
-      <c r="F128" s="40" t="n">
+      <c r="F128" s="41" t="n">
         <v>-192609.31</v>
       </c>
-      <c r="G128" s="40" t="n">
+      <c r="G128" s="41" t="n">
         <v>-125501.41</v>
       </c>
       <c r="H128" s="7" t="n">
         <v>0.058889</v>
       </c>
-      <c r="I128" s="58" t="inlineStr">
+      <c r="I128" s="59" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="56" t="n">
+      <c r="A129" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="B129" s="40" t="n">
+      <c r="B129" s="41" t="n">
         <v>127087.08</v>
       </c>
-      <c r="C129" s="56" t="n">
+      <c r="C129" s="57" t="n">
         <v>0.2218</v>
       </c>
-      <c r="D129" s="43" t="n">
+      <c r="D129" s="44" t="n">
         <v>2.59</v>
       </c>
-      <c r="E129" s="40" t="n">
+      <c r="E129" s="41" t="n">
         <v>1337758.74</v>
       </c>
-      <c r="F129" s="40" t="n">
+      <c r="F129" s="41" t="n">
         <v>-243134.06</v>
       </c>
-      <c r="G129" s="40" t="n">
+      <c r="G129" s="41" t="n">
         <v>-167596.64</v>
       </c>
       <c r="H129" s="7" t="n">
         <v>0.051413</v>
       </c>
-      <c r="I129" s="58" t="inlineStr">
+      <c r="I129" s="59" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -6483,7 +6486,7 @@
       </c>
     </row>
     <row r="132" ht="32" customHeight="1">
-      <c r="A132" s="59" t="inlineStr">
+      <c r="A132" s="60" t="inlineStr">
         <is>
           <t>THE LENDER IS REPAID ON SALE, BUT THE EQUITY IS WIPED OUT - DO NOT THROW A CURE AT A DEMAND FAILURE</t>
         </is>
@@ -6508,7 +6511,7 @@
           <t>Cumulative CFADS shortfall (EUR)</t>
         </is>
       </c>
-      <c r="B135" s="40" t="n">
+      <c r="B135" s="41" t="n">
         <v>4577.04</v>
       </c>
     </row>
@@ -6518,7 +6521,7 @@
           <t>Equity cure to 1.25x DSCR (EUR)</t>
         </is>
       </c>
-      <c r="B136" s="40" t="n">
+      <c r="B136" s="41" t="n">
         <v>17455.75</v>
       </c>
     </row>
@@ -6528,7 +6531,7 @@
           <t>Six-month DSRA (EUR)</t>
         </is>
       </c>
-      <c r="B137" s="40" t="n">
+      <c r="B137" s="41" t="n">
         <v>20292.72</v>
       </c>
     </row>
@@ -6538,7 +6541,7 @@
           <t>Net exit value (EUR)</t>
         </is>
       </c>
-      <c r="B138" s="40" t="n">
+      <c r="B138" s="41" t="n">
         <v>654606.8199999999</v>
       </c>
     </row>
@@ -6548,7 +6551,7 @@
           <t>Debt outstanding at exit (EUR)</t>
         </is>
       </c>
-      <c r="B139" s="40" t="n">
+      <c r="B139" s="41" t="n">
         <v>457236.43</v>
       </c>
     </row>
@@ -6558,7 +6561,7 @@
           <t>Lender recovery</t>
         </is>
       </c>
-      <c r="B140" s="56" t="n">
+      <c r="B140" s="57" t="n">
         <v>1.4317</v>
       </c>
     </row>
@@ -6568,7 +6571,7 @@
           <t>Equity at exit (EUR)</t>
         </is>
       </c>
-      <c r="B141" s="40" t="n">
+      <c r="B141" s="41" t="n">
         <v>197370.39</v>
       </c>
     </row>
@@ -6578,7 +6581,7 @@
           <t>Equity invested (EUR)</t>
         </is>
       </c>
-      <c r="B142" s="40" t="n">
+      <c r="B142" s="41" t="n">
         <v>1113342.89</v>
       </c>
     </row>
@@ -6588,140 +6591,140 @@
           <t>Equity recovery</t>
         </is>
       </c>
-      <c r="B143" s="56" t="n">
+      <c r="B143" s="57" t="n">
         <v>0.1773</v>
       </c>
     </row>
     <row r="144"/>
     <row r="145">
-      <c r="A145" s="42" t="inlineStr">
+      <c r="A145" s="43" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B145" s="42" t="inlineStr">
+      <c r="B145" s="43" t="inlineStr">
         <is>
           <t>CFADS (EUR)</t>
         </is>
       </c>
-      <c r="C145" s="42" t="inlineStr">
+      <c r="C145" s="43" t="inlineStr">
         <is>
           <t>Debt service (EUR)</t>
         </is>
       </c>
-      <c r="D145" s="42" t="inlineStr">
+      <c r="D145" s="43" t="inlineStr">
         <is>
           <t>Shortfall (EUR)</t>
         </is>
       </c>
-      <c r="E145" s="42" t="inlineStr">
+      <c r="E145" s="43" t="inlineStr">
         <is>
           <t>DSCR</t>
         </is>
       </c>
-      <c r="F145" s="42" t="inlineStr">
+      <c r="F145" s="43" t="inlineStr">
         <is>
           <t>Ending cash (EUR)</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="50" t="n">
+      <c r="A146" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B146" s="40" t="n">
+      <c r="B146" s="41" t="n">
         <v>17004</v>
       </c>
-      <c r="C146" s="40" t="n">
+      <c r="C146" s="41" t="n">
         <v>21581.04</v>
       </c>
-      <c r="D146" s="40" t="n">
+      <c r="D146" s="41" t="n">
         <v>4577.04</v>
       </c>
-      <c r="E146" s="43" t="n">
+      <c r="E146" s="44" t="n">
         <v>0.79</v>
       </c>
-      <c r="F146" s="40" t="n">
+      <c r="F146" s="41" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="50" t="n">
+      <c r="A147" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B147" s="40" t="n">
+      <c r="B147" s="41" t="n">
         <v>43248.35</v>
       </c>
-      <c r="C147" s="40" t="n">
+      <c r="C147" s="41" t="n">
         <v>40585.44</v>
       </c>
-      <c r="D147" s="40" t="n">
+      <c r="D147" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="E147" s="43" t="n">
+      <c r="E147" s="44" t="n">
         <v>1.07</v>
       </c>
-      <c r="F147" s="40" t="n">
+      <c r="F147" s="41" t="n">
         <v>173204.5</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="50" t="n">
+      <c r="A148" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B148" s="40" t="n">
+      <c r="B148" s="41" t="n">
         <v>58730.24</v>
       </c>
-      <c r="C148" s="40" t="n">
+      <c r="C148" s="41" t="n">
         <v>40585.44</v>
       </c>
-      <c r="D148" s="40" t="n">
+      <c r="D148" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="E148" s="43" t="n">
+      <c r="E148" s="44" t="n">
         <v>1.45</v>
       </c>
-      <c r="F148" s="40" t="n">
+      <c r="F148" s="41" t="n">
         <v>191349.3</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="50" t="n">
+      <c r="A149" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B149" s="40" t="n">
+      <c r="B149" s="41" t="n">
         <v>58730.24</v>
       </c>
-      <c r="C149" s="40" t="n">
+      <c r="C149" s="41" t="n">
         <v>40585.44</v>
       </c>
-      <c r="D149" s="40" t="n">
+      <c r="D149" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="E149" s="43" t="n">
+      <c r="E149" s="44" t="n">
         <v>1.45</v>
       </c>
-      <c r="F149" s="40" t="n">
+      <c r="F149" s="41" t="n">
         <v>209494.1</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="50" t="n">
+      <c r="A150" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B150" s="40" t="n">
+      <c r="B150" s="41" t="n">
         <v>58730.24</v>
       </c>
-      <c r="C150" s="40" t="n">
+      <c r="C150" s="41" t="n">
         <v>40585.44</v>
       </c>
-      <c r="D150" s="40" t="n">
+      <c r="D150" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="E150" s="43" t="n">
+      <c r="E150" s="44" t="n">
         <v>1.45</v>
       </c>
-      <c r="F150" s="40" t="n">
+      <c r="F150" s="41" t="n">
         <v>227638.9</v>
       </c>
     </row>
@@ -6779,7 +6782,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Change any blue input and the Live Model recalculates. The report tabs are Python snapshots and do not recalculate.</t>
+          <t>Change any blue input and the Live Model recalculates. Ten tabs are generated artefacts: Read Me &amp; Checks, Executive Scorecard, 3-Statement Model, Debt Schedule (formula-driven), Scenario Stress-Testing, Monte Carlo Risk, Credit Risk &amp; Copula, Unit Economics &amp; Runway, Phase II Expansion and Reform Case. Inputs, Live Model and Funding &amp; Audit are the live tabs.</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10502,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Promoter-case calibration to the presentation headline</t>
+          <t>Promoter case: declared calibration, not source reconciliation</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -10507,19 +10510,19 @@
           <t>INFO</t>
         </is>
       </c>
-      <c r="D55" s="27" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="D55" s="30" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>revenue=86275.0, ebitda=11297.0</t>
+          <t>model_revenue=86275.0, model_ebitda=11297.0, plan_occupied_days=66.325, plan_revenue_formula=99487.5, plan_ebitda_formula=26701.31, plan_revenue_conclusiones_b5=74851, deck_revenue_b11=96628, deck_ebitda_b12=11297, plan_restaurant_ticket_b19=25</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>{'revenue': 86275.0, 'ebitda': 11297.0}</t>
+          <t>No source-consistent target</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10616,7 @@
           <t>AUDIT VERDICT</t>
         </is>
       </c>
-      <c r="B59" s="30" t="inlineStr">
+      <c r="B59" s="31" t="inlineStr">
         <is>
           <t>CONDITIONAL - 5 MATERIAL EXCEPTION(S)</t>
         </is>
@@ -10664,7 +10667,7 @@
     <row r="67" ht="40" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>- The audit verdict is CONDITIONAL - 5 MATERIAL EXCEPTION(S): 10 of 16 rules pass. This is deliberate, not a bug.</t>
+          <t>- The audit verdict is CONDITIONAL - 5 MATERIAL EXCEPTION(S): 9 of 16 rules pass, 1 is not applicable. This is deliberate, not a bug.</t>
         </is>
       </c>
     </row>
@@ -10713,27 +10716,27 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>Underwriting Metric</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Year 1 (Ramp-up)</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Year 2 (First Amortising Year)</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Year 3 (Mature)</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>Benchmark / Covenant</t>
         </is>
@@ -10745,17 +10748,17 @@
           <t>Gross Revenue (EUR)</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>154,548.00</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>171,720.00</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>171,720.00</t>
         </is>
@@ -10767,27 +10770,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>EBITDA (EUR)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>24,279.92</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>37,041.58</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>37,041.58</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>Margin 15.7% to 21.6%</t>
         </is>
@@ -10799,17 +10802,17 @@
           <t>FF&amp;E Reserve (3%) (EUR)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>4,636.44</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>5,151.60</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>5,151.60</t>
         </is>
@@ -10821,27 +10824,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>CFADS (EBITDA - FF&amp;E - tax) (EUR)</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>19,643.48</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>31,889.98</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>31,889.98</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>Cash actually available to the lender</t>
         </is>
@@ -10853,17 +10856,17 @@
           <t>Net Income (EUR)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>-45,605.68</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>-27,983.40</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>-22,825.59</t>
         </is>
@@ -10875,27 +10878,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Ending Cash (EUR)</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>20,700.88</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>183,322.64</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>187,564.98</t>
         </is>
       </c>
-      <c r="E10" s="33" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t>After close-day uses; see Funding &amp; Audit</t>
         </is>
@@ -10907,17 +10910,17 @@
           <t>Senior Debt Balance (EUR)</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>367,535.00</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>354,348.76</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>340,625.29</t>
         </is>
@@ -10929,27 +10932,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Debt Service Coverage (DSCR)</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>1.34x</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>1.15x</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>1.15x</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>Bank covenant floor &gt;= 1.25x</t>
         </is>
@@ -10961,17 +10964,17 @@
           <t>Interest Coverage (ICR)</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>1.65x</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>2.56x</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>2.66x</t>
         </is>
@@ -10983,27 +10986,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Balance Sheet Discrepancy</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t>Strict double-entry equality</t>
         </is>
@@ -11018,12 +11021,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -11207,107 +11210,107 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Gross Margin</t>
         </is>
       </c>
-      <c r="D3" s="31" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>Labor Expense</t>
         </is>
       </c>
-      <c r="E3" s="31" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>Fixed Opex</t>
         </is>
       </c>
-      <c r="F3" s="31" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>Ebitda</t>
         </is>
       </c>
-      <c r="G3" s="31" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="H3" s="31" t="inlineStr">
+      <c r="H3" s="32" t="inlineStr">
         <is>
           <t>Ebit</t>
         </is>
       </c>
-      <c r="I3" s="31" t="inlineStr">
+      <c r="I3" s="32" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="J3" s="31" t="inlineStr">
+      <c r="J3" s="32" t="inlineStr">
         <is>
           <t>Ebt</t>
         </is>
       </c>
-      <c r="K3" s="31" t="inlineStr">
+      <c r="K3" s="32" t="inlineStr">
         <is>
           <t>Corporate Tax</t>
         </is>
       </c>
-      <c r="L3" s="31" t="inlineStr">
+      <c r="L3" s="32" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="M3" s="31" t="inlineStr">
+      <c r="M3" s="32" t="inlineStr">
         <is>
           <t>Cfo</t>
         </is>
       </c>
-      <c r="N3" s="31" t="inlineStr">
+      <c r="N3" s="32" t="inlineStr">
         <is>
           <t>Cfi</t>
         </is>
       </c>
-      <c r="O3" s="31" t="inlineStr">
+      <c r="O3" s="32" t="inlineStr">
         <is>
           <t>Cff</t>
         </is>
       </c>
-      <c r="P3" s="31" t="inlineStr">
+      <c r="P3" s="32" t="inlineStr">
         <is>
           <t>Ending Cash</t>
         </is>
       </c>
-      <c r="Q3" s="31" t="inlineStr">
+      <c r="Q3" s="32" t="inlineStr">
         <is>
           <t>Net Ppe</t>
         </is>
       </c>
-      <c r="R3" s="31" t="inlineStr">
+      <c r="R3" s="32" t="inlineStr">
         <is>
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="S3" s="31" t="inlineStr">
+      <c r="S3" s="32" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
-      <c r="T3" s="31" t="inlineStr">
+      <c r="T3" s="32" t="inlineStr">
         <is>
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="U3" s="31" t="inlineStr">
+      <c r="U3" s="32" t="inlineStr">
         <is>
           <t>Balance Sheet Discrepancy</t>
         </is>
@@ -11682,7 +11685,7 @@
           <t>Principal</t>
         </is>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="37">
         <f>Inputs!$B$33</f>
         <v/>
       </c>
@@ -11693,7 +11696,7 @@
           <t>Annual interest rate</t>
         </is>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="38">
         <f>Inputs!$B$34</f>
         <v/>
       </c>
@@ -11704,7 +11707,7 @@
           <t>Tenure (years)</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="39">
         <f>Inputs!$B$35</f>
         <v/>
       </c>
@@ -11715,7 +11718,7 @@
           <t>Grace (months)</t>
         </is>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="39">
         <f>Inputs!$B$36</f>
         <v/>
       </c>
@@ -11726,7 +11729,7 @@
           <t>Monthly rate</t>
         </is>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="40">
         <f>B5/12</f>
         <v/>
       </c>
@@ -11737,7 +11740,7 @@
           <t>Amortisation months</t>
         </is>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="39">
         <f>B6*12-B7</f>
         <v/>
       </c>
@@ -11748,7 +11751,7 @@
           <t>Monthly payment</t>
         </is>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="37">
         <f>IF(B8&gt;0,B4*B8*(1+B8)^B9/((1+B8)^B9-1),B4/B9)</f>
         <v/>
       </c>
@@ -11759,7 +11762,7 @@
           <t>Annual service (Year 2+)</t>
         </is>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>ROUND(B10,2)*12</f>
         <v/>
       </c>
@@ -11770,7 +11773,7 @@
           <t>Total months</t>
         </is>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="39">
         <f>B6*12</f>
         <v/>
       </c>
@@ -11825,7 +11828,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="n">
+      <c r="A16" s="41" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8">
@@ -11858,7 +11861,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="n">
+      <c r="A17" s="41" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8">
@@ -11891,7 +11894,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="n">
+      <c r="A18" s="41" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8">
@@ -11924,7 +11927,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="n">
+      <c r="A19" s="41" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8">
@@ -11957,7 +11960,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="n">
+      <c r="A20" s="41" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8">
@@ -12034,10 +12037,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="n">
+      <c r="A25" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="40">
+      <c r="B25" s="41">
         <f>ROUNDUP(A25/12,0)</f>
         <v/>
       </c>
@@ -12063,11 +12066,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="40">
+      <c r="A26" s="41">
         <f>A25+1</f>
         <v/>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="41">
         <f>ROUNDUP(A26/12,0)</f>
         <v/>
       </c>
@@ -12093,11 +12096,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="40">
+      <c r="A27" s="41">
         <f>A26+1</f>
         <v/>
       </c>
-      <c r="B27" s="40">
+      <c r="B27" s="41">
         <f>ROUNDUP(A27/12,0)</f>
         <v/>
       </c>
@@ -12123,11 +12126,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="40">
+      <c r="A28" s="41">
         <f>A27+1</f>
         <v/>
       </c>
-      <c r="B28" s="40">
+      <c r="B28" s="41">
         <f>ROUNDUP(A28/12,0)</f>
         <v/>
       </c>
@@ -12153,11 +12156,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="40">
+      <c r="A29" s="41">
         <f>A28+1</f>
         <v/>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="41">
         <f>ROUNDUP(A29/12,0)</f>
         <v/>
       </c>
@@ -12183,11 +12186,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="40">
+      <c r="A30" s="41">
         <f>A29+1</f>
         <v/>
       </c>
-      <c r="B30" s="40">
+      <c r="B30" s="41">
         <f>ROUNDUP(A30/12,0)</f>
         <v/>
       </c>
@@ -12213,11 +12216,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="40">
+      <c r="A31" s="41">
         <f>A30+1</f>
         <v/>
       </c>
-      <c r="B31" s="40">
+      <c r="B31" s="41">
         <f>ROUNDUP(A31/12,0)</f>
         <v/>
       </c>
@@ -12243,11 +12246,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="40">
+      <c r="A32" s="41">
         <f>A31+1</f>
         <v/>
       </c>
-      <c r="B32" s="40">
+      <c r="B32" s="41">
         <f>ROUNDUP(A32/12,0)</f>
         <v/>
       </c>
@@ -12273,11 +12276,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="40">
+      <c r="A33" s="41">
         <f>A32+1</f>
         <v/>
       </c>
-      <c r="B33" s="40">
+      <c r="B33" s="41">
         <f>ROUNDUP(A33/12,0)</f>
         <v/>
       </c>
@@ -12303,11 +12306,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="40">
+      <c r="A34" s="41">
         <f>A33+1</f>
         <v/>
       </c>
-      <c r="B34" s="40">
+      <c r="B34" s="41">
         <f>ROUNDUP(A34/12,0)</f>
         <v/>
       </c>
@@ -12333,11 +12336,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="40">
+      <c r="A35" s="41">
         <f>A34+1</f>
         <v/>
       </c>
-      <c r="B35" s="40">
+      <c r="B35" s="41">
         <f>ROUNDUP(A35/12,0)</f>
         <v/>
       </c>
@@ -12363,11 +12366,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="40">
+      <c r="A36" s="41">
         <f>A35+1</f>
         <v/>
       </c>
-      <c r="B36" s="40">
+      <c r="B36" s="41">
         <f>ROUNDUP(A36/12,0)</f>
         <v/>
       </c>
@@ -12393,11 +12396,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="40">
+      <c r="A37" s="41">
         <f>A36+1</f>
         <v/>
       </c>
-      <c r="B37" s="40">
+      <c r="B37" s="41">
         <f>ROUNDUP(A37/12,0)</f>
         <v/>
       </c>
@@ -12423,11 +12426,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="40">
+      <c r="A38" s="41">
         <f>A37+1</f>
         <v/>
       </c>
-      <c r="B38" s="40">
+      <c r="B38" s="41">
         <f>ROUNDUP(A38/12,0)</f>
         <v/>
       </c>
@@ -12453,11 +12456,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="40">
+      <c r="A39" s="41">
         <f>A38+1</f>
         <v/>
       </c>
-      <c r="B39" s="40">
+      <c r="B39" s="41">
         <f>ROUNDUP(A39/12,0)</f>
         <v/>
       </c>
@@ -12483,11 +12486,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="40">
+      <c r="A40" s="41">
         <f>A39+1</f>
         <v/>
       </c>
-      <c r="B40" s="40">
+      <c r="B40" s="41">
         <f>ROUNDUP(A40/12,0)</f>
         <v/>
       </c>
@@ -12513,11 +12516,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="40">
+      <c r="A41" s="41">
         <f>A40+1</f>
         <v/>
       </c>
-      <c r="B41" s="40">
+      <c r="B41" s="41">
         <f>ROUNDUP(A41/12,0)</f>
         <v/>
       </c>
@@ -12543,11 +12546,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="40">
+      <c r="A42" s="41">
         <f>A41+1</f>
         <v/>
       </c>
-      <c r="B42" s="40">
+      <c r="B42" s="41">
         <f>ROUNDUP(A42/12,0)</f>
         <v/>
       </c>
@@ -12573,11 +12576,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="40">
+      <c r="A43" s="41">
         <f>A42+1</f>
         <v/>
       </c>
-      <c r="B43" s="40">
+      <c r="B43" s="41">
         <f>ROUNDUP(A43/12,0)</f>
         <v/>
       </c>
@@ -12603,11 +12606,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="40">
+      <c r="A44" s="41">
         <f>A43+1</f>
         <v/>
       </c>
-      <c r="B44" s="40">
+      <c r="B44" s="41">
         <f>ROUNDUP(A44/12,0)</f>
         <v/>
       </c>
@@ -12633,11 +12636,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="40">
+      <c r="A45" s="41">
         <f>A44+1</f>
         <v/>
       </c>
-      <c r="B45" s="40">
+      <c r="B45" s="41">
         <f>ROUNDUP(A45/12,0)</f>
         <v/>
       </c>
@@ -12663,11 +12666,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="40">
+      <c r="A46" s="41">
         <f>A45+1</f>
         <v/>
       </c>
-      <c r="B46" s="40">
+      <c r="B46" s="41">
         <f>ROUNDUP(A46/12,0)</f>
         <v/>
       </c>
@@ -12693,11 +12696,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="40">
+      <c r="A47" s="41">
         <f>A46+1</f>
         <v/>
       </c>
-      <c r="B47" s="40">
+      <c r="B47" s="41">
         <f>ROUNDUP(A47/12,0)</f>
         <v/>
       </c>
@@ -12723,11 +12726,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="40">
+      <c r="A48" s="41">
         <f>A47+1</f>
         <v/>
       </c>
-      <c r="B48" s="40">
+      <c r="B48" s="41">
         <f>ROUNDUP(A48/12,0)</f>
         <v/>
       </c>
@@ -12753,11 +12756,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="40">
+      <c r="A49" s="41">
         <f>A48+1</f>
         <v/>
       </c>
-      <c r="B49" s="40">
+      <c r="B49" s="41">
         <f>ROUNDUP(A49/12,0)</f>
         <v/>
       </c>
@@ -12783,11 +12786,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="40">
+      <c r="A50" s="41">
         <f>A49+1</f>
         <v/>
       </c>
-      <c r="B50" s="40">
+      <c r="B50" s="41">
         <f>ROUNDUP(A50/12,0)</f>
         <v/>
       </c>
@@ -12813,11 +12816,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="40">
+      <c r="A51" s="41">
         <f>A50+1</f>
         <v/>
       </c>
-      <c r="B51" s="40">
+      <c r="B51" s="41">
         <f>ROUNDUP(A51/12,0)</f>
         <v/>
       </c>
@@ -12843,11 +12846,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="40">
+      <c r="A52" s="41">
         <f>A51+1</f>
         <v/>
       </c>
-      <c r="B52" s="40">
+      <c r="B52" s="41">
         <f>ROUNDUP(A52/12,0)</f>
         <v/>
       </c>
@@ -12873,11 +12876,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="40">
+      <c r="A53" s="41">
         <f>A52+1</f>
         <v/>
       </c>
-      <c r="B53" s="40">
+      <c r="B53" s="41">
         <f>ROUNDUP(A53/12,0)</f>
         <v/>
       </c>
@@ -12903,11 +12906,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="40">
+      <c r="A54" s="41">
         <f>A53+1</f>
         <v/>
       </c>
-      <c r="B54" s="40">
+      <c r="B54" s="41">
         <f>ROUNDUP(A54/12,0)</f>
         <v/>
       </c>
@@ -12933,11 +12936,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="40">
+      <c r="A55" s="41">
         <f>A54+1</f>
         <v/>
       </c>
-      <c r="B55" s="40">
+      <c r="B55" s="41">
         <f>ROUNDUP(A55/12,0)</f>
         <v/>
       </c>
@@ -12963,11 +12966,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="40">
+      <c r="A56" s="41">
         <f>A55+1</f>
         <v/>
       </c>
-      <c r="B56" s="40">
+      <c r="B56" s="41">
         <f>ROUNDUP(A56/12,0)</f>
         <v/>
       </c>
@@ -12993,11 +12996,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="40">
+      <c r="A57" s="41">
         <f>A56+1</f>
         <v/>
       </c>
-      <c r="B57" s="40">
+      <c r="B57" s="41">
         <f>ROUNDUP(A57/12,0)</f>
         <v/>
       </c>
@@ -13023,11 +13026,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="40">
+      <c r="A58" s="41">
         <f>A57+1</f>
         <v/>
       </c>
-      <c r="B58" s="40">
+      <c r="B58" s="41">
         <f>ROUNDUP(A58/12,0)</f>
         <v/>
       </c>
@@ -13053,11 +13056,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="40">
+      <c r="A59" s="41">
         <f>A58+1</f>
         <v/>
       </c>
-      <c r="B59" s="40">
+      <c r="B59" s="41">
         <f>ROUNDUP(A59/12,0)</f>
         <v/>
       </c>
@@ -13083,11 +13086,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="40">
+      <c r="A60" s="41">
         <f>A59+1</f>
         <v/>
       </c>
-      <c r="B60" s="40">
+      <c r="B60" s="41">
         <f>ROUNDUP(A60/12,0)</f>
         <v/>
       </c>
@@ -13113,11 +13116,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="40">
+      <c r="A61" s="41">
         <f>A60+1</f>
         <v/>
       </c>
-      <c r="B61" s="40">
+      <c r="B61" s="41">
         <f>ROUNDUP(A61/12,0)</f>
         <v/>
       </c>
@@ -13143,11 +13146,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="40">
+      <c r="A62" s="41">
         <f>A61+1</f>
         <v/>
       </c>
-      <c r="B62" s="40">
+      <c r="B62" s="41">
         <f>ROUNDUP(A62/12,0)</f>
         <v/>
       </c>
@@ -13173,11 +13176,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="40">
+      <c r="A63" s="41">
         <f>A62+1</f>
         <v/>
       </c>
-      <c r="B63" s="40">
+      <c r="B63" s="41">
         <f>ROUNDUP(A63/12,0)</f>
         <v/>
       </c>
@@ -13203,11 +13206,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="40">
+      <c r="A64" s="41">
         <f>A63+1</f>
         <v/>
       </c>
-      <c r="B64" s="40">
+      <c r="B64" s="41">
         <f>ROUNDUP(A64/12,0)</f>
         <v/>
       </c>
@@ -13233,11 +13236,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="40">
+      <c r="A65" s="41">
         <f>A64+1</f>
         <v/>
       </c>
-      <c r="B65" s="40">
+      <c r="B65" s="41">
         <f>ROUNDUP(A65/12,0)</f>
         <v/>
       </c>
@@ -13263,11 +13266,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="40">
+      <c r="A66" s="41">
         <f>A65+1</f>
         <v/>
       </c>
-      <c r="B66" s="40">
+      <c r="B66" s="41">
         <f>ROUNDUP(A66/12,0)</f>
         <v/>
       </c>
@@ -13293,11 +13296,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="40">
+      <c r="A67" s="41">
         <f>A66+1</f>
         <v/>
       </c>
-      <c r="B67" s="40">
+      <c r="B67" s="41">
         <f>ROUNDUP(A67/12,0)</f>
         <v/>
       </c>
@@ -13323,11 +13326,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="40">
+      <c r="A68" s="41">
         <f>A67+1</f>
         <v/>
       </c>
-      <c r="B68" s="40">
+      <c r="B68" s="41">
         <f>ROUNDUP(A68/12,0)</f>
         <v/>
       </c>
@@ -13353,11 +13356,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="40">
+      <c r="A69" s="41">
         <f>A68+1</f>
         <v/>
       </c>
-      <c r="B69" s="40">
+      <c r="B69" s="41">
         <f>ROUNDUP(A69/12,0)</f>
         <v/>
       </c>
@@ -13383,11 +13386,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="40">
+      <c r="A70" s="41">
         <f>A69+1</f>
         <v/>
       </c>
-      <c r="B70" s="40">
+      <c r="B70" s="41">
         <f>ROUNDUP(A70/12,0)</f>
         <v/>
       </c>
@@ -13413,11 +13416,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="40">
+      <c r="A71" s="41">
         <f>A70+1</f>
         <v/>
       </c>
-      <c r="B71" s="40">
+      <c r="B71" s="41">
         <f>ROUNDUP(A71/12,0)</f>
         <v/>
       </c>
@@ -13443,11 +13446,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="40">
+      <c r="A72" s="41">
         <f>A71+1</f>
         <v/>
       </c>
-      <c r="B72" s="40">
+      <c r="B72" s="41">
         <f>ROUNDUP(A72/12,0)</f>
         <v/>
       </c>
@@ -13473,11 +13476,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="40">
+      <c r="A73" s="41">
         <f>A72+1</f>
         <v/>
       </c>
-      <c r="B73" s="40">
+      <c r="B73" s="41">
         <f>ROUNDUP(A73/12,0)</f>
         <v/>
       </c>
@@ -13503,11 +13506,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="40">
+      <c r="A74" s="41">
         <f>A73+1</f>
         <v/>
       </c>
-      <c r="B74" s="40">
+      <c r="B74" s="41">
         <f>ROUNDUP(A74/12,0)</f>
         <v/>
       </c>
@@ -13533,11 +13536,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="40">
+      <c r="A75" s="41">
         <f>A74+1</f>
         <v/>
       </c>
-      <c r="B75" s="40">
+      <c r="B75" s="41">
         <f>ROUNDUP(A75/12,0)</f>
         <v/>
       </c>
@@ -13563,11 +13566,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="40">
+      <c r="A76" s="41">
         <f>A75+1</f>
         <v/>
       </c>
-      <c r="B76" s="40">
+      <c r="B76" s="41">
         <f>ROUNDUP(A76/12,0)</f>
         <v/>
       </c>
@@ -13593,11 +13596,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="40">
+      <c r="A77" s="41">
         <f>A76+1</f>
         <v/>
       </c>
-      <c r="B77" s="40">
+      <c r="B77" s="41">
         <f>ROUNDUP(A77/12,0)</f>
         <v/>
       </c>
@@ -13623,11 +13626,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="40">
+      <c r="A78" s="41">
         <f>A77+1</f>
         <v/>
       </c>
-      <c r="B78" s="40">
+      <c r="B78" s="41">
         <f>ROUNDUP(A78/12,0)</f>
         <v/>
       </c>
@@ -13653,11 +13656,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="40">
+      <c r="A79" s="41">
         <f>A78+1</f>
         <v/>
       </c>
-      <c r="B79" s="40">
+      <c r="B79" s="41">
         <f>ROUNDUP(A79/12,0)</f>
         <v/>
       </c>
@@ -13683,11 +13686,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="40">
+      <c r="A80" s="41">
         <f>A79+1</f>
         <v/>
       </c>
-      <c r="B80" s="40">
+      <c r="B80" s="41">
         <f>ROUNDUP(A80/12,0)</f>
         <v/>
       </c>
@@ -13713,11 +13716,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="40">
+      <c r="A81" s="41">
         <f>A80+1</f>
         <v/>
       </c>
-      <c r="B81" s="40">
+      <c r="B81" s="41">
         <f>ROUNDUP(A81/12,0)</f>
         <v/>
       </c>
@@ -13743,11 +13746,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="40">
+      <c r="A82" s="41">
         <f>A81+1</f>
         <v/>
       </c>
-      <c r="B82" s="40">
+      <c r="B82" s="41">
         <f>ROUNDUP(A82/12,0)</f>
         <v/>
       </c>
@@ -13773,11 +13776,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="40">
+      <c r="A83" s="41">
         <f>A82+1</f>
         <v/>
       </c>
-      <c r="B83" s="40">
+      <c r="B83" s="41">
         <f>ROUNDUP(A83/12,0)</f>
         <v/>
       </c>
@@ -13803,11 +13806,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="40">
+      <c r="A84" s="41">
         <f>A83+1</f>
         <v/>
       </c>
-      <c r="B84" s="40">
+      <c r="B84" s="41">
         <f>ROUNDUP(A84/12,0)</f>
         <v/>
       </c>
@@ -13833,11 +13836,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="40">
+      <c r="A85" s="41">
         <f>A84+1</f>
         <v/>
       </c>
-      <c r="B85" s="40">
+      <c r="B85" s="41">
         <f>ROUNDUP(A85/12,0)</f>
         <v/>
       </c>
@@ -13863,11 +13866,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="40">
+      <c r="A86" s="41">
         <f>A85+1</f>
         <v/>
       </c>
-      <c r="B86" s="40">
+      <c r="B86" s="41">
         <f>ROUNDUP(A86/12,0)</f>
         <v/>
       </c>
@@ -13893,11 +13896,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="40">
+      <c r="A87" s="41">
         <f>A86+1</f>
         <v/>
       </c>
-      <c r="B87" s="40">
+      <c r="B87" s="41">
         <f>ROUNDUP(A87/12,0)</f>
         <v/>
       </c>
@@ -13923,11 +13926,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="40">
+      <c r="A88" s="41">
         <f>A87+1</f>
         <v/>
       </c>
-      <c r="B88" s="40">
+      <c r="B88" s="41">
         <f>ROUNDUP(A88/12,0)</f>
         <v/>
       </c>
@@ -13953,11 +13956,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="40">
+      <c r="A89" s="41">
         <f>A88+1</f>
         <v/>
       </c>
-      <c r="B89" s="40">
+      <c r="B89" s="41">
         <f>ROUNDUP(A89/12,0)</f>
         <v/>
       </c>
@@ -13983,11 +13986,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="40">
+      <c r="A90" s="41">
         <f>A89+1</f>
         <v/>
       </c>
-      <c r="B90" s="40">
+      <c r="B90" s="41">
         <f>ROUNDUP(A90/12,0)</f>
         <v/>
       </c>
@@ -14013,11 +14016,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="40">
+      <c r="A91" s="41">
         <f>A90+1</f>
         <v/>
       </c>
-      <c r="B91" s="40">
+      <c r="B91" s="41">
         <f>ROUNDUP(A91/12,0)</f>
         <v/>
       </c>
@@ -14043,11 +14046,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="40">
+      <c r="A92" s="41">
         <f>A91+1</f>
         <v/>
       </c>
-      <c r="B92" s="40">
+      <c r="B92" s="41">
         <f>ROUNDUP(A92/12,0)</f>
         <v/>
       </c>
@@ -14073,11 +14076,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="40">
+      <c r="A93" s="41">
         <f>A92+1</f>
         <v/>
       </c>
-      <c r="B93" s="40">
+      <c r="B93" s="41">
         <f>ROUNDUP(A93/12,0)</f>
         <v/>
       </c>
@@ -14103,11 +14106,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="40">
+      <c r="A94" s="41">
         <f>A93+1</f>
         <v/>
       </c>
-      <c r="B94" s="40">
+      <c r="B94" s="41">
         <f>ROUNDUP(A94/12,0)</f>
         <v/>
       </c>
@@ -14133,11 +14136,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="40">
+      <c r="A95" s="41">
         <f>A94+1</f>
         <v/>
       </c>
-      <c r="B95" s="40">
+      <c r="B95" s="41">
         <f>ROUNDUP(A95/12,0)</f>
         <v/>
       </c>
@@ -14163,11 +14166,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="40">
+      <c r="A96" s="41">
         <f>A95+1</f>
         <v/>
       </c>
-      <c r="B96" s="40">
+      <c r="B96" s="41">
         <f>ROUNDUP(A96/12,0)</f>
         <v/>
       </c>
@@ -14193,11 +14196,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="40">
+      <c r="A97" s="41">
         <f>A96+1</f>
         <v/>
       </c>
-      <c r="B97" s="40">
+      <c r="B97" s="41">
         <f>ROUNDUP(A97/12,0)</f>
         <v/>
       </c>
@@ -14223,11 +14226,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="40">
+      <c r="A98" s="41">
         <f>A97+1</f>
         <v/>
       </c>
-      <c r="B98" s="40">
+      <c r="B98" s="41">
         <f>ROUNDUP(A98/12,0)</f>
         <v/>
       </c>
@@ -14253,11 +14256,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="40">
+      <c r="A99" s="41">
         <f>A98+1</f>
         <v/>
       </c>
-      <c r="B99" s="40">
+      <c r="B99" s="41">
         <f>ROUNDUP(A99/12,0)</f>
         <v/>
       </c>
@@ -14283,11 +14286,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="40">
+      <c r="A100" s="41">
         <f>A99+1</f>
         <v/>
       </c>
-      <c r="B100" s="40">
+      <c r="B100" s="41">
         <f>ROUNDUP(A100/12,0)</f>
         <v/>
       </c>
@@ -14313,11 +14316,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="40">
+      <c r="A101" s="41">
         <f>A100+1</f>
         <v/>
       </c>
-      <c r="B101" s="40">
+      <c r="B101" s="41">
         <f>ROUNDUP(A101/12,0)</f>
         <v/>
       </c>
@@ -14343,11 +14346,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="40">
+      <c r="A102" s="41">
         <f>A101+1</f>
         <v/>
       </c>
-      <c r="B102" s="40">
+      <c r="B102" s="41">
         <f>ROUNDUP(A102/12,0)</f>
         <v/>
       </c>
@@ -14373,11 +14376,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="40">
+      <c r="A103" s="41">
         <f>A102+1</f>
         <v/>
       </c>
-      <c r="B103" s="40">
+      <c r="B103" s="41">
         <f>ROUNDUP(A103/12,0)</f>
         <v/>
       </c>
@@ -14403,11 +14406,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="40">
+      <c r="A104" s="41">
         <f>A103+1</f>
         <v/>
       </c>
-      <c r="B104" s="40">
+      <c r="B104" s="41">
         <f>ROUNDUP(A104/12,0)</f>
         <v/>
       </c>
@@ -14433,11 +14436,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="40">
+      <c r="A105" s="41">
         <f>A104+1</f>
         <v/>
       </c>
-      <c r="B105" s="40">
+      <c r="B105" s="41">
         <f>ROUNDUP(A105/12,0)</f>
         <v/>
       </c>
@@ -14463,11 +14466,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="40">
+      <c r="A106" s="41">
         <f>A105+1</f>
         <v/>
       </c>
-      <c r="B106" s="40">
+      <c r="B106" s="41">
         <f>ROUNDUP(A106/12,0)</f>
         <v/>
       </c>
@@ -14493,11 +14496,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="40">
+      <c r="A107" s="41">
         <f>A106+1</f>
         <v/>
       </c>
-      <c r="B107" s="40">
+      <c r="B107" s="41">
         <f>ROUNDUP(A107/12,0)</f>
         <v/>
       </c>
@@ -14523,11 +14526,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="40">
+      <c r="A108" s="41">
         <f>A107+1</f>
         <v/>
       </c>
-      <c r="B108" s="40">
+      <c r="B108" s="41">
         <f>ROUNDUP(A108/12,0)</f>
         <v/>
       </c>
@@ -14553,11 +14556,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="40">
+      <c r="A109" s="41">
         <f>A108+1</f>
         <v/>
       </c>
-      <c r="B109" s="40">
+      <c r="B109" s="41">
         <f>ROUNDUP(A109/12,0)</f>
         <v/>
       </c>
@@ -14583,11 +14586,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="40">
+      <c r="A110" s="41">
         <f>A109+1</f>
         <v/>
       </c>
-      <c r="B110" s="40">
+      <c r="B110" s="41">
         <f>ROUNDUP(A110/12,0)</f>
         <v/>
       </c>
@@ -14613,11 +14616,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="40">
+      <c r="A111" s="41">
         <f>A110+1</f>
         <v/>
       </c>
-      <c r="B111" s="40">
+      <c r="B111" s="41">
         <f>ROUNDUP(A111/12,0)</f>
         <v/>
       </c>
@@ -14643,11 +14646,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="40">
+      <c r="A112" s="41">
         <f>A111+1</f>
         <v/>
       </c>
-      <c r="B112" s="40">
+      <c r="B112" s="41">
         <f>ROUNDUP(A112/12,0)</f>
         <v/>
       </c>
@@ -14673,11 +14676,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="40">
+      <c r="A113" s="41">
         <f>A112+1</f>
         <v/>
       </c>
-      <c r="B113" s="40">
+      <c r="B113" s="41">
         <f>ROUNDUP(A113/12,0)</f>
         <v/>
       </c>
@@ -14703,11 +14706,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="40">
+      <c r="A114" s="41">
         <f>A113+1</f>
         <v/>
       </c>
-      <c r="B114" s="40">
+      <c r="B114" s="41">
         <f>ROUNDUP(A114/12,0)</f>
         <v/>
       </c>
@@ -14733,11 +14736,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="40">
+      <c r="A115" s="41">
         <f>A114+1</f>
         <v/>
       </c>
-      <c r="B115" s="40">
+      <c r="B115" s="41">
         <f>ROUNDUP(A115/12,0)</f>
         <v/>
       </c>
@@ -14763,11 +14766,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="40">
+      <c r="A116" s="41">
         <f>A115+1</f>
         <v/>
       </c>
-      <c r="B116" s="40">
+      <c r="B116" s="41">
         <f>ROUNDUP(A116/12,0)</f>
         <v/>
       </c>
@@ -14793,11 +14796,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="40">
+      <c r="A117" s="41">
         <f>A116+1</f>
         <v/>
       </c>
-      <c r="B117" s="40">
+      <c r="B117" s="41">
         <f>ROUNDUP(A117/12,0)</f>
         <v/>
       </c>
@@ -14823,11 +14826,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="40">
+      <c r="A118" s="41">
         <f>A117+1</f>
         <v/>
       </c>
-      <c r="B118" s="40">
+      <c r="B118" s="41">
         <f>ROUNDUP(A118/12,0)</f>
         <v/>
       </c>
@@ -14853,11 +14856,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="40">
+      <c r="A119" s="41">
         <f>A118+1</f>
         <v/>
       </c>
-      <c r="B119" s="40">
+      <c r="B119" s="41">
         <f>ROUNDUP(A119/12,0)</f>
         <v/>
       </c>
@@ -14883,11 +14886,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="40">
+      <c r="A120" s="41">
         <f>A119+1</f>
         <v/>
       </c>
-      <c r="B120" s="40">
+      <c r="B120" s="41">
         <f>ROUNDUP(A120/12,0)</f>
         <v/>
       </c>
@@ -14913,11 +14916,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="40">
+      <c r="A121" s="41">
         <f>A120+1</f>
         <v/>
       </c>
-      <c r="B121" s="40">
+      <c r="B121" s="41">
         <f>ROUNDUP(A121/12,0)</f>
         <v/>
       </c>
@@ -14943,11 +14946,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="40">
+      <c r="A122" s="41">
         <f>A121+1</f>
         <v/>
       </c>
-      <c r="B122" s="40">
+      <c r="B122" s="41">
         <f>ROUNDUP(A122/12,0)</f>
         <v/>
       </c>
@@ -14973,11 +14976,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="40">
+      <c r="A123" s="41">
         <f>A122+1</f>
         <v/>
       </c>
-      <c r="B123" s="40">
+      <c r="B123" s="41">
         <f>ROUNDUP(A123/12,0)</f>
         <v/>
       </c>
@@ -15003,11 +15006,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="40">
+      <c r="A124" s="41">
         <f>A123+1</f>
         <v/>
       </c>
-      <c r="B124" s="40">
+      <c r="B124" s="41">
         <f>ROUNDUP(A124/12,0)</f>
         <v/>
       </c>
@@ -15033,11 +15036,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="40">
+      <c r="A125" s="41">
         <f>A124+1</f>
         <v/>
       </c>
-      <c r="B125" s="40">
+      <c r="B125" s="41">
         <f>ROUNDUP(A125/12,0)</f>
         <v/>
       </c>
@@ -15063,11 +15066,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="40">
+      <c r="A126" s="41">
         <f>A125+1</f>
         <v/>
       </c>
-      <c r="B126" s="40">
+      <c r="B126" s="41">
         <f>ROUNDUP(A126/12,0)</f>
         <v/>
       </c>
@@ -15093,11 +15096,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="40">
+      <c r="A127" s="41">
         <f>A126+1</f>
         <v/>
       </c>
-      <c r="B127" s="40">
+      <c r="B127" s="41">
         <f>ROUNDUP(A127/12,0)</f>
         <v/>
       </c>
@@ -15123,11 +15126,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="40">
+      <c r="A128" s="41">
         <f>A127+1</f>
         <v/>
       </c>
-      <c r="B128" s="40">
+      <c r="B128" s="41">
         <f>ROUNDUP(A128/12,0)</f>
         <v/>
       </c>
@@ -15153,11 +15156,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="40">
+      <c r="A129" s="41">
         <f>A128+1</f>
         <v/>
       </c>
-      <c r="B129" s="40">
+      <c r="B129" s="41">
         <f>ROUNDUP(A129/12,0)</f>
         <v/>
       </c>
@@ -15183,11 +15186,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="40">
+      <c r="A130" s="41">
         <f>A129+1</f>
         <v/>
       </c>
-      <c r="B130" s="40">
+      <c r="B130" s="41">
         <f>ROUNDUP(A130/12,0)</f>
         <v/>
       </c>
@@ -15213,11 +15216,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="40">
+      <c r="A131" s="41">
         <f>A130+1</f>
         <v/>
       </c>
-      <c r="B131" s="40">
+      <c r="B131" s="41">
         <f>ROUNDUP(A131/12,0)</f>
         <v/>
       </c>
@@ -15243,11 +15246,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="40">
+      <c r="A132" s="41">
         <f>A131+1</f>
         <v/>
       </c>
-      <c r="B132" s="40">
+      <c r="B132" s="41">
         <f>ROUNDUP(A132/12,0)</f>
         <v/>
       </c>
@@ -15273,11 +15276,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="40">
+      <c r="A133" s="41">
         <f>A132+1</f>
         <v/>
       </c>
-      <c r="B133" s="40">
+      <c r="B133" s="41">
         <f>ROUNDUP(A133/12,0)</f>
         <v/>
       </c>
@@ -15303,11 +15306,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="40">
+      <c r="A134" s="41">
         <f>A133+1</f>
         <v/>
       </c>
-      <c r="B134" s="40">
+      <c r="B134" s="41">
         <f>ROUNDUP(A134/12,0)</f>
         <v/>
       </c>
@@ -15333,11 +15336,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="40">
+      <c r="A135" s="41">
         <f>A134+1</f>
         <v/>
       </c>
-      <c r="B135" s="40">
+      <c r="B135" s="41">
         <f>ROUNDUP(A135/12,0)</f>
         <v/>
       </c>
@@ -15363,11 +15366,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="40">
+      <c r="A136" s="41">
         <f>A135+1</f>
         <v/>
       </c>
-      <c r="B136" s="40">
+      <c r="B136" s="41">
         <f>ROUNDUP(A136/12,0)</f>
         <v/>
       </c>
@@ -15393,11 +15396,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="40">
+      <c r="A137" s="41">
         <f>A136+1</f>
         <v/>
       </c>
-      <c r="B137" s="40">
+      <c r="B137" s="41">
         <f>ROUNDUP(A137/12,0)</f>
         <v/>
       </c>
@@ -15423,11 +15426,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="40">
+      <c r="A138" s="41">
         <f>A137+1</f>
         <v/>
       </c>
-      <c r="B138" s="40">
+      <c r="B138" s="41">
         <f>ROUNDUP(A138/12,0)</f>
         <v/>
       </c>
@@ -15453,11 +15456,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="40">
+      <c r="A139" s="41">
         <f>A138+1</f>
         <v/>
       </c>
-      <c r="B139" s="40">
+      <c r="B139" s="41">
         <f>ROUNDUP(A139/12,0)</f>
         <v/>
       </c>
@@ -15483,11 +15486,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="40">
+      <c r="A140" s="41">
         <f>A139+1</f>
         <v/>
       </c>
-      <c r="B140" s="40">
+      <c r="B140" s="41">
         <f>ROUNDUP(A140/12,0)</f>
         <v/>
       </c>
@@ -15513,11 +15516,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="40">
+      <c r="A141" s="41">
         <f>A140+1</f>
         <v/>
       </c>
-      <c r="B141" s="40">
+      <c r="B141" s="41">
         <f>ROUNDUP(A141/12,0)</f>
         <v/>
       </c>
@@ -15543,11 +15546,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="40">
+      <c r="A142" s="41">
         <f>A141+1</f>
         <v/>
       </c>
-      <c r="B142" s="40">
+      <c r="B142" s="41">
         <f>ROUNDUP(A142/12,0)</f>
         <v/>
       </c>
@@ -15573,11 +15576,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="40">
+      <c r="A143" s="41">
         <f>A142+1</f>
         <v/>
       </c>
-      <c r="B143" s="40">
+      <c r="B143" s="41">
         <f>ROUNDUP(A143/12,0)</f>
         <v/>
       </c>
@@ -15603,11 +15606,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="40">
+      <c r="A144" s="41">
         <f>A143+1</f>
         <v/>
       </c>
-      <c r="B144" s="40">
+      <c r="B144" s="41">
         <f>ROUNDUP(A144/12,0)</f>
         <v/>
       </c>
@@ -15633,11 +15636,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="40">
+      <c r="A145" s="41">
         <f>A144+1</f>
         <v/>
       </c>
-      <c r="B145" s="40">
+      <c r="B145" s="41">
         <f>ROUNDUP(A145/12,0)</f>
         <v/>
       </c>
@@ -15663,11 +15666,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="40">
+      <c r="A146" s="41">
         <f>A145+1</f>
         <v/>
       </c>
-      <c r="B146" s="40">
+      <c r="B146" s="41">
         <f>ROUNDUP(A146/12,0)</f>
         <v/>
       </c>
@@ -15693,11 +15696,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="40">
+      <c r="A147" s="41">
         <f>A146+1</f>
         <v/>
       </c>
-      <c r="B147" s="40">
+      <c r="B147" s="41">
         <f>ROUNDUP(A147/12,0)</f>
         <v/>
       </c>
@@ -15723,11 +15726,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="40">
+      <c r="A148" s="41">
         <f>A147+1</f>
         <v/>
       </c>
-      <c r="B148" s="40">
+      <c r="B148" s="41">
         <f>ROUNDUP(A148/12,0)</f>
         <v/>
       </c>
@@ -15753,11 +15756,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="40">
+      <c r="A149" s="41">
         <f>A148+1</f>
         <v/>
       </c>
-      <c r="B149" s="40">
+      <c r="B149" s="41">
         <f>ROUNDUP(A149/12,0)</f>
         <v/>
       </c>
@@ -15783,11 +15786,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="40">
+      <c r="A150" s="41">
         <f>A149+1</f>
         <v/>
       </c>
-      <c r="B150" s="40">
+      <c r="B150" s="41">
         <f>ROUNDUP(A150/12,0)</f>
         <v/>
       </c>
@@ -15813,11 +15816,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="40">
+      <c r="A151" s="41">
         <f>A150+1</f>
         <v/>
       </c>
-      <c r="B151" s="40">
+      <c r="B151" s="41">
         <f>ROUNDUP(A151/12,0)</f>
         <v/>
       </c>
@@ -15843,11 +15846,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="40">
+      <c r="A152" s="41">
         <f>A151+1</f>
         <v/>
       </c>
-      <c r="B152" s="40">
+      <c r="B152" s="41">
         <f>ROUNDUP(A152/12,0)</f>
         <v/>
       </c>
@@ -15873,11 +15876,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="40">
+      <c r="A153" s="41">
         <f>A152+1</f>
         <v/>
       </c>
-      <c r="B153" s="40">
+      <c r="B153" s="41">
         <f>ROUNDUP(A153/12,0)</f>
         <v/>
       </c>
@@ -15903,11 +15906,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="40">
+      <c r="A154" s="41">
         <f>A153+1</f>
         <v/>
       </c>
-      <c r="B154" s="40">
+      <c r="B154" s="41">
         <f>ROUNDUP(A154/12,0)</f>
         <v/>
       </c>
@@ -15933,11 +15936,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="40">
+      <c r="A155" s="41">
         <f>A154+1</f>
         <v/>
       </c>
-      <c r="B155" s="40">
+      <c r="B155" s="41">
         <f>ROUNDUP(A155/12,0)</f>
         <v/>
       </c>
@@ -15963,11 +15966,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="40">
+      <c r="A156" s="41">
         <f>A155+1</f>
         <v/>
       </c>
-      <c r="B156" s="40">
+      <c r="B156" s="41">
         <f>ROUNDUP(A156/12,0)</f>
         <v/>
       </c>
@@ -15993,11 +15996,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="40">
+      <c r="A157" s="41">
         <f>A156+1</f>
         <v/>
       </c>
-      <c r="B157" s="40">
+      <c r="B157" s="41">
         <f>ROUNDUP(A157/12,0)</f>
         <v/>
       </c>
@@ -16023,11 +16026,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="40">
+      <c r="A158" s="41">
         <f>A157+1</f>
         <v/>
       </c>
-      <c r="B158" s="40">
+      <c r="B158" s="41">
         <f>ROUNDUP(A158/12,0)</f>
         <v/>
       </c>
@@ -16053,11 +16056,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="40">
+      <c r="A159" s="41">
         <f>A158+1</f>
         <v/>
       </c>
-      <c r="B159" s="40">
+      <c r="B159" s="41">
         <f>ROUNDUP(A159/12,0)</f>
         <v/>
       </c>
@@ -16083,11 +16086,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="40">
+      <c r="A160" s="41">
         <f>A159+1</f>
         <v/>
       </c>
-      <c r="B160" s="40">
+      <c r="B160" s="41">
         <f>ROUNDUP(A160/12,0)</f>
         <v/>
       </c>
@@ -16113,11 +16116,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="40">
+      <c r="A161" s="41">
         <f>A160+1</f>
         <v/>
       </c>
-      <c r="B161" s="40">
+      <c r="B161" s="41">
         <f>ROUNDUP(A161/12,0)</f>
         <v/>
       </c>
@@ -16143,11 +16146,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="40">
+      <c r="A162" s="41">
         <f>A161+1</f>
         <v/>
       </c>
-      <c r="B162" s="40">
+      <c r="B162" s="41">
         <f>ROUNDUP(A162/12,0)</f>
         <v/>
       </c>
@@ -16173,11 +16176,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="40">
+      <c r="A163" s="41">
         <f>A162+1</f>
         <v/>
       </c>
-      <c r="B163" s="40">
+      <c r="B163" s="41">
         <f>ROUNDUP(A163/12,0)</f>
         <v/>
       </c>
@@ -16203,11 +16206,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="40">
+      <c r="A164" s="41">
         <f>A163+1</f>
         <v/>
       </c>
-      <c r="B164" s="40">
+      <c r="B164" s="41">
         <f>ROUNDUP(A164/12,0)</f>
         <v/>
       </c>
@@ -16233,11 +16236,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="40">
+      <c r="A165" s="41">
         <f>A164+1</f>
         <v/>
       </c>
-      <c r="B165" s="40">
+      <c r="B165" s="41">
         <f>ROUNDUP(A165/12,0)</f>
         <v/>
       </c>
@@ -16263,11 +16266,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="40">
+      <c r="A166" s="41">
         <f>A165+1</f>
         <v/>
       </c>
-      <c r="B166" s="40">
+      <c r="B166" s="41">
         <f>ROUNDUP(A166/12,0)</f>
         <v/>
       </c>
@@ -16293,11 +16296,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="40">
+      <c r="A167" s="41">
         <f>A166+1</f>
         <v/>
       </c>
-      <c r="B167" s="40">
+      <c r="B167" s="41">
         <f>ROUNDUP(A167/12,0)</f>
         <v/>
       </c>
@@ -16323,11 +16326,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="40">
+      <c r="A168" s="41">
         <f>A167+1</f>
         <v/>
       </c>
-      <c r="B168" s="40">
+      <c r="B168" s="41">
         <f>ROUNDUP(A168/12,0)</f>
         <v/>
       </c>
@@ -16353,11 +16356,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="40">
+      <c r="A169" s="41">
         <f>A168+1</f>
         <v/>
       </c>
-      <c r="B169" s="40">
+      <c r="B169" s="41">
         <f>ROUNDUP(A169/12,0)</f>
         <v/>
       </c>
@@ -16383,11 +16386,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="40">
+      <c r="A170" s="41">
         <f>A169+1</f>
         <v/>
       </c>
-      <c r="B170" s="40">
+      <c r="B170" s="41">
         <f>ROUNDUP(A170/12,0)</f>
         <v/>
       </c>
@@ -16413,11 +16416,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="40">
+      <c r="A171" s="41">
         <f>A170+1</f>
         <v/>
       </c>
-      <c r="B171" s="40">
+      <c r="B171" s="41">
         <f>ROUNDUP(A171/12,0)</f>
         <v/>
       </c>
@@ -16443,11 +16446,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="40">
+      <c r="A172" s="41">
         <f>A171+1</f>
         <v/>
       </c>
-      <c r="B172" s="40">
+      <c r="B172" s="41">
         <f>ROUNDUP(A172/12,0)</f>
         <v/>
       </c>
@@ -16473,11 +16476,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="40">
+      <c r="A173" s="41">
         <f>A172+1</f>
         <v/>
       </c>
-      <c r="B173" s="40">
+      <c r="B173" s="41">
         <f>ROUNDUP(A173/12,0)</f>
         <v/>
       </c>
@@ -16503,11 +16506,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="40">
+      <c r="A174" s="41">
         <f>A173+1</f>
         <v/>
       </c>
-      <c r="B174" s="40">
+      <c r="B174" s="41">
         <f>ROUNDUP(A174/12,0)</f>
         <v/>
       </c>
@@ -16533,11 +16536,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="40">
+      <c r="A175" s="41">
         <f>A174+1</f>
         <v/>
       </c>
-      <c r="B175" s="40">
+      <c r="B175" s="41">
         <f>ROUNDUP(A175/12,0)</f>
         <v/>
       </c>
@@ -16563,11 +16566,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="40">
+      <c r="A176" s="41">
         <f>A175+1</f>
         <v/>
       </c>
-      <c r="B176" s="40">
+      <c r="B176" s="41">
         <f>ROUNDUP(A176/12,0)</f>
         <v/>
       </c>
@@ -16593,11 +16596,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="40">
+      <c r="A177" s="41">
         <f>A176+1</f>
         <v/>
       </c>
-      <c r="B177" s="40">
+      <c r="B177" s="41">
         <f>ROUNDUP(A177/12,0)</f>
         <v/>
       </c>
@@ -16623,11 +16626,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="40">
+      <c r="A178" s="41">
         <f>A177+1</f>
         <v/>
       </c>
-      <c r="B178" s="40">
+      <c r="B178" s="41">
         <f>ROUNDUP(A178/12,0)</f>
         <v/>
       </c>
@@ -16653,11 +16656,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="40">
+      <c r="A179" s="41">
         <f>A178+1</f>
         <v/>
       </c>
-      <c r="B179" s="40">
+      <c r="B179" s="41">
         <f>ROUNDUP(A179/12,0)</f>
         <v/>
       </c>
@@ -16683,11 +16686,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="40">
+      <c r="A180" s="41">
         <f>A179+1</f>
         <v/>
       </c>
-      <c r="B180" s="40">
+      <c r="B180" s="41">
         <f>ROUNDUP(A180/12,0)</f>
         <v/>
       </c>
@@ -16713,11 +16716,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="40">
+      <c r="A181" s="41">
         <f>A180+1</f>
         <v/>
       </c>
-      <c r="B181" s="40">
+      <c r="B181" s="41">
         <f>ROUNDUP(A181/12,0)</f>
         <v/>
       </c>
@@ -16743,11 +16746,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="40">
+      <c r="A182" s="41">
         <f>A181+1</f>
         <v/>
       </c>
-      <c r="B182" s="40">
+      <c r="B182" s="41">
         <f>ROUNDUP(A182/12,0)</f>
         <v/>
       </c>
@@ -16773,11 +16776,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="40">
+      <c r="A183" s="41">
         <f>A182+1</f>
         <v/>
       </c>
-      <c r="B183" s="40">
+      <c r="B183" s="41">
         <f>ROUNDUP(A183/12,0)</f>
         <v/>
       </c>
@@ -16803,11 +16806,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="40">
+      <c r="A184" s="41">
         <f>A183+1</f>
         <v/>
       </c>
-      <c r="B184" s="40">
+      <c r="B184" s="41">
         <f>ROUNDUP(A184/12,0)</f>
         <v/>
       </c>
@@ -16833,11 +16836,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="40">
+      <c r="A185" s="41">
         <f>A184+1</f>
         <v/>
       </c>
-      <c r="B185" s="40">
+      <c r="B185" s="41">
         <f>ROUNDUP(A185/12,0)</f>
         <v/>
       </c>
@@ -16863,11 +16866,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="40">
+      <c r="A186" s="41">
         <f>A185+1</f>
         <v/>
       </c>
-      <c r="B186" s="40">
+      <c r="B186" s="41">
         <f>ROUNDUP(A186/12,0)</f>
         <v/>
       </c>
@@ -16893,11 +16896,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="40">
+      <c r="A187" s="41">
         <f>A186+1</f>
         <v/>
       </c>
-      <c r="B187" s="40">
+      <c r="B187" s="41">
         <f>ROUNDUP(A187/12,0)</f>
         <v/>
       </c>
@@ -16923,11 +16926,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="40">
+      <c r="A188" s="41">
         <f>A187+1</f>
         <v/>
       </c>
-      <c r="B188" s="40">
+      <c r="B188" s="41">
         <f>ROUNDUP(A188/12,0)</f>
         <v/>
       </c>
@@ -16953,11 +16956,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="40">
+      <c r="A189" s="41">
         <f>A188+1</f>
         <v/>
       </c>
-      <c r="B189" s="40">
+      <c r="B189" s="41">
         <f>ROUNDUP(A189/12,0)</f>
         <v/>
       </c>
@@ -16983,11 +16986,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="40">
+      <c r="A190" s="41">
         <f>A189+1</f>
         <v/>
       </c>
-      <c r="B190" s="40">
+      <c r="B190" s="41">
         <f>ROUNDUP(A190/12,0)</f>
         <v/>
       </c>
@@ -17013,11 +17016,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="40">
+      <c r="A191" s="41">
         <f>A190+1</f>
         <v/>
       </c>
-      <c r="B191" s="40">
+      <c r="B191" s="41">
         <f>ROUNDUP(A191/12,0)</f>
         <v/>
       </c>
@@ -17043,11 +17046,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="40">
+      <c r="A192" s="41">
         <f>A191+1</f>
         <v/>
       </c>
-      <c r="B192" s="40">
+      <c r="B192" s="41">
         <f>ROUNDUP(A192/12,0)</f>
         <v/>
       </c>
@@ -17073,11 +17076,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="40">
+      <c r="A193" s="41">
         <f>A192+1</f>
         <v/>
       </c>
-      <c r="B193" s="40">
+      <c r="B193" s="41">
         <f>ROUNDUP(A193/12,0)</f>
         <v/>
       </c>
@@ -17103,11 +17106,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="40">
+      <c r="A194" s="41">
         <f>A193+1</f>
         <v/>
       </c>
-      <c r="B194" s="40">
+      <c r="B194" s="41">
         <f>ROUNDUP(A194/12,0)</f>
         <v/>
       </c>
@@ -17133,11 +17136,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="40">
+      <c r="A195" s="41">
         <f>A194+1</f>
         <v/>
       </c>
-      <c r="B195" s="40">
+      <c r="B195" s="41">
         <f>ROUNDUP(A195/12,0)</f>
         <v/>
       </c>
@@ -17163,11 +17166,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="40">
+      <c r="A196" s="41">
         <f>A195+1</f>
         <v/>
       </c>
-      <c r="B196" s="40">
+      <c r="B196" s="41">
         <f>ROUNDUP(A196/12,0)</f>
         <v/>
       </c>
@@ -17193,11 +17196,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="40">
+      <c r="A197" s="41">
         <f>A196+1</f>
         <v/>
       </c>
-      <c r="B197" s="40">
+      <c r="B197" s="41">
         <f>ROUNDUP(A197/12,0)</f>
         <v/>
       </c>
@@ -17223,11 +17226,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="40">
+      <c r="A198" s="41">
         <f>A197+1</f>
         <v/>
       </c>
-      <c r="B198" s="40">
+      <c r="B198" s="41">
         <f>ROUNDUP(A198/12,0)</f>
         <v/>
       </c>
@@ -17253,11 +17256,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="40">
+      <c r="A199" s="41">
         <f>A198+1</f>
         <v/>
       </c>
-      <c r="B199" s="40">
+      <c r="B199" s="41">
         <f>ROUNDUP(A199/12,0)</f>
         <v/>
       </c>
@@ -17283,11 +17286,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="40">
+      <c r="A200" s="41">
         <f>A199+1</f>
         <v/>
       </c>
-      <c r="B200" s="40">
+      <c r="B200" s="41">
         <f>ROUNDUP(A200/12,0)</f>
         <v/>
       </c>
@@ -17313,11 +17316,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="40">
+      <c r="A201" s="41">
         <f>A200+1</f>
         <v/>
       </c>
-      <c r="B201" s="40">
+      <c r="B201" s="41">
         <f>ROUNDUP(A201/12,0)</f>
         <v/>
       </c>
@@ -17343,11 +17346,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="40">
+      <c r="A202" s="41">
         <f>A201+1</f>
         <v/>
       </c>
-      <c r="B202" s="40">
+      <c r="B202" s="41">
         <f>ROUNDUP(A202/12,0)</f>
         <v/>
       </c>
@@ -17373,11 +17376,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="40">
+      <c r="A203" s="41">
         <f>A202+1</f>
         <v/>
       </c>
-      <c r="B203" s="40">
+      <c r="B203" s="41">
         <f>ROUNDUP(A203/12,0)</f>
         <v/>
       </c>
@@ -17403,11 +17406,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="40">
+      <c r="A204" s="41">
         <f>A203+1</f>
         <v/>
       </c>
-      <c r="B204" s="40">
+      <c r="B204" s="41">
         <f>ROUNDUP(A204/12,0)</f>
         <v/>
       </c>
@@ -17433,11 +17436,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="40">
+      <c r="A205" s="41">
         <f>A204+1</f>
         <v/>
       </c>
-      <c r="B205" s="40">
+      <c r="B205" s="41">
         <f>ROUNDUP(A205/12,0)</f>
         <v/>
       </c>
@@ -17463,11 +17466,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="40">
+      <c r="A206" s="41">
         <f>A205+1</f>
         <v/>
       </c>
-      <c r="B206" s="40">
+      <c r="B206" s="41">
         <f>ROUNDUP(A206/12,0)</f>
         <v/>
       </c>
@@ -17493,11 +17496,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="40">
+      <c r="A207" s="41">
         <f>A206+1</f>
         <v/>
       </c>
-      <c r="B207" s="40">
+      <c r="B207" s="41">
         <f>ROUNDUP(A207/12,0)</f>
         <v/>
       </c>
@@ -17523,11 +17526,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="40">
+      <c r="A208" s="41">
         <f>A207+1</f>
         <v/>
       </c>
-      <c r="B208" s="40">
+      <c r="B208" s="41">
         <f>ROUNDUP(A208/12,0)</f>
         <v/>
       </c>
@@ -17553,11 +17556,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="40">
+      <c r="A209" s="41">
         <f>A208+1</f>
         <v/>
       </c>
-      <c r="B209" s="40">
+      <c r="B209" s="41">
         <f>ROUNDUP(A209/12,0)</f>
         <v/>
       </c>
@@ -17583,11 +17586,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="40">
+      <c r="A210" s="41">
         <f>A209+1</f>
         <v/>
       </c>
-      <c r="B210" s="40">
+      <c r="B210" s="41">
         <f>ROUNDUP(A210/12,0)</f>
         <v/>
       </c>
@@ -17613,11 +17616,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="40">
+      <c r="A211" s="41">
         <f>A210+1</f>
         <v/>
       </c>
-      <c r="B211" s="40">
+      <c r="B211" s="41">
         <f>ROUNDUP(A211/12,0)</f>
         <v/>
       </c>
@@ -17643,11 +17646,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="40">
+      <c r="A212" s="41">
         <f>A211+1</f>
         <v/>
       </c>
-      <c r="B212" s="40">
+      <c r="B212" s="41">
         <f>ROUNDUP(A212/12,0)</f>
         <v/>
       </c>
@@ -17673,11 +17676,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="40">
+      <c r="A213" s="41">
         <f>A212+1</f>
         <v/>
       </c>
-      <c r="B213" s="40">
+      <c r="B213" s="41">
         <f>ROUNDUP(A213/12,0)</f>
         <v/>
       </c>
@@ -17703,11 +17706,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="40">
+      <c r="A214" s="41">
         <f>A213+1</f>
         <v/>
       </c>
-      <c r="B214" s="40">
+      <c r="B214" s="41">
         <f>ROUNDUP(A214/12,0)</f>
         <v/>
       </c>
@@ -17733,11 +17736,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="40">
+      <c r="A215" s="41">
         <f>A214+1</f>
         <v/>
       </c>
-      <c r="B215" s="40">
+      <c r="B215" s="41">
         <f>ROUNDUP(A215/12,0)</f>
         <v/>
       </c>
@@ -17763,11 +17766,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="40">
+      <c r="A216" s="41">
         <f>A215+1</f>
         <v/>
       </c>
-      <c r="B216" s="40">
+      <c r="B216" s="41">
         <f>ROUNDUP(A216/12,0)</f>
         <v/>
       </c>
@@ -17793,11 +17796,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="40">
+      <c r="A217" s="41">
         <f>A216+1</f>
         <v/>
       </c>
-      <c r="B217" s="40">
+      <c r="B217" s="41">
         <f>ROUNDUP(A217/12,0)</f>
         <v/>
       </c>
@@ -17823,11 +17826,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="40">
+      <c r="A218" s="41">
         <f>A217+1</f>
         <v/>
       </c>
-      <c r="B218" s="40">
+      <c r="B218" s="41">
         <f>ROUNDUP(A218/12,0)</f>
         <v/>
       </c>
@@ -17853,11 +17856,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="40">
+      <c r="A219" s="41">
         <f>A218+1</f>
         <v/>
       </c>
-      <c r="B219" s="40">
+      <c r="B219" s="41">
         <f>ROUNDUP(A219/12,0)</f>
         <v/>
       </c>
@@ -17883,11 +17886,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="40">
+      <c r="A220" s="41">
         <f>A219+1</f>
         <v/>
       </c>
-      <c r="B220" s="40">
+      <c r="B220" s="41">
         <f>ROUNDUP(A220/12,0)</f>
         <v/>
       </c>
@@ -17913,11 +17916,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="40">
+      <c r="A221" s="41">
         <f>A220+1</f>
         <v/>
       </c>
-      <c r="B221" s="40">
+      <c r="B221" s="41">
         <f>ROUNDUP(A221/12,0)</f>
         <v/>
       </c>
@@ -17943,11 +17946,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="40">
+      <c r="A222" s="41">
         <f>A221+1</f>
         <v/>
       </c>
-      <c r="B222" s="40">
+      <c r="B222" s="41">
         <f>ROUNDUP(A222/12,0)</f>
         <v/>
       </c>
@@ -17973,11 +17976,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="40">
+      <c r="A223" s="41">
         <f>A222+1</f>
         <v/>
       </c>
-      <c r="B223" s="40">
+      <c r="B223" s="41">
         <f>ROUNDUP(A223/12,0)</f>
         <v/>
       </c>
@@ -18003,11 +18006,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="40">
+      <c r="A224" s="41">
         <f>A223+1</f>
         <v/>
       </c>
-      <c r="B224" s="40">
+      <c r="B224" s="41">
         <f>ROUNDUP(A224/12,0)</f>
         <v/>
       </c>
@@ -18033,11 +18036,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="40">
+      <c r="A225" s="41">
         <f>A224+1</f>
         <v/>
       </c>
-      <c r="B225" s="40">
+      <c r="B225" s="41">
         <f>ROUNDUP(A225/12,0)</f>
         <v/>
       </c>
@@ -18063,11 +18066,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="40">
+      <c r="A226" s="41">
         <f>A225+1</f>
         <v/>
       </c>
-      <c r="B226" s="40">
+      <c r="B226" s="41">
         <f>ROUNDUP(A226/12,0)</f>
         <v/>
       </c>
@@ -18093,11 +18096,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="40">
+      <c r="A227" s="41">
         <f>A226+1</f>
         <v/>
       </c>
-      <c r="B227" s="40">
+      <c r="B227" s="41">
         <f>ROUNDUP(A227/12,0)</f>
         <v/>
       </c>
@@ -18123,11 +18126,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="40">
+      <c r="A228" s="41">
         <f>A227+1</f>
         <v/>
       </c>
-      <c r="B228" s="40">
+      <c r="B228" s="41">
         <f>ROUNDUP(A228/12,0)</f>
         <v/>
       </c>
@@ -18153,11 +18156,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="40">
+      <c r="A229" s="41">
         <f>A228+1</f>
         <v/>
       </c>
-      <c r="B229" s="40">
+      <c r="B229" s="41">
         <f>ROUNDUP(A229/12,0)</f>
         <v/>
       </c>
@@ -18183,11 +18186,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="40">
+      <c r="A230" s="41">
         <f>A229+1</f>
         <v/>
       </c>
-      <c r="B230" s="40">
+      <c r="B230" s="41">
         <f>ROUNDUP(A230/12,0)</f>
         <v/>
       </c>
@@ -18213,11 +18216,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="40">
+      <c r="A231" s="41">
         <f>A230+1</f>
         <v/>
       </c>
-      <c r="B231" s="40">
+      <c r="B231" s="41">
         <f>ROUNDUP(A231/12,0)</f>
         <v/>
       </c>
@@ -18243,11 +18246,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="40">
+      <c r="A232" s="41">
         <f>A231+1</f>
         <v/>
       </c>
-      <c r="B232" s="40">
+      <c r="B232" s="41">
         <f>ROUNDUP(A232/12,0)</f>
         <v/>
       </c>
@@ -18273,11 +18276,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="40">
+      <c r="A233" s="41">
         <f>A232+1</f>
         <v/>
       </c>
-      <c r="B233" s="40">
+      <c r="B233" s="41">
         <f>ROUNDUP(A233/12,0)</f>
         <v/>
       </c>
@@ -18303,11 +18306,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="40">
+      <c r="A234" s="41">
         <f>A233+1</f>
         <v/>
       </c>
-      <c r="B234" s="40">
+      <c r="B234" s="41">
         <f>ROUNDUP(A234/12,0)</f>
         <v/>
       </c>
@@ -18333,11 +18336,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="40">
+      <c r="A235" s="41">
         <f>A234+1</f>
         <v/>
       </c>
-      <c r="B235" s="40">
+      <c r="B235" s="41">
         <f>ROUNDUP(A235/12,0)</f>
         <v/>
       </c>
@@ -18363,11 +18366,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="40">
+      <c r="A236" s="41">
         <f>A235+1</f>
         <v/>
       </c>
-      <c r="B236" s="40">
+      <c r="B236" s="41">
         <f>ROUNDUP(A236/12,0)</f>
         <v/>
       </c>
@@ -18393,11 +18396,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="40">
+      <c r="A237" s="41">
         <f>A236+1</f>
         <v/>
       </c>
-      <c r="B237" s="40">
+      <c r="B237" s="41">
         <f>ROUNDUP(A237/12,0)</f>
         <v/>
       </c>
@@ -18423,11 +18426,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="40">
+      <c r="A238" s="41">
         <f>A237+1</f>
         <v/>
       </c>
-      <c r="B238" s="40">
+      <c r="B238" s="41">
         <f>ROUNDUP(A238/12,0)</f>
         <v/>
       </c>
@@ -18453,11 +18456,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="40">
+      <c r="A239" s="41">
         <f>A238+1</f>
         <v/>
       </c>
-      <c r="B239" s="40">
+      <c r="B239" s="41">
         <f>ROUNDUP(A239/12,0)</f>
         <v/>
       </c>
@@ -18483,11 +18486,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="40">
+      <c r="A240" s="41">
         <f>A239+1</f>
         <v/>
       </c>
-      <c r="B240" s="40">
+      <c r="B240" s="41">
         <f>ROUNDUP(A240/12,0)</f>
         <v/>
       </c>
@@ -18513,11 +18516,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="40">
+      <c r="A241" s="41">
         <f>A240+1</f>
         <v/>
       </c>
-      <c r="B241" s="40">
+      <c r="B241" s="41">
         <f>ROUNDUP(A241/12,0)</f>
         <v/>
       </c>
@@ -18543,11 +18546,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="40">
+      <c r="A242" s="41">
         <f>A241+1</f>
         <v/>
       </c>
-      <c r="B242" s="40">
+      <c r="B242" s="41">
         <f>ROUNDUP(A242/12,0)</f>
         <v/>
       </c>
@@ -18573,11 +18576,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="40">
+      <c r="A243" s="41">
         <f>A242+1</f>
         <v/>
       </c>
-      <c r="B243" s="40">
+      <c r="B243" s="41">
         <f>ROUNDUP(A243/12,0)</f>
         <v/>
       </c>
@@ -18603,11 +18606,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="40">
+      <c r="A244" s="41">
         <f>A243+1</f>
         <v/>
       </c>
-      <c r="B244" s="40">
+      <c r="B244" s="41">
         <f>ROUNDUP(A244/12,0)</f>
         <v/>
       </c>
@@ -18633,11 +18636,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="40">
+      <c r="A245" s="41">
         <f>A244+1</f>
         <v/>
       </c>
-      <c r="B245" s="40">
+      <c r="B245" s="41">
         <f>ROUNDUP(A245/12,0)</f>
         <v/>
       </c>
@@ -18663,11 +18666,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="40">
+      <c r="A246" s="41">
         <f>A245+1</f>
         <v/>
       </c>
-      <c r="B246" s="40">
+      <c r="B246" s="41">
         <f>ROUNDUP(A246/12,0)</f>
         <v/>
       </c>
@@ -18693,11 +18696,11 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="40">
+      <c r="A247" s="41">
         <f>A246+1</f>
         <v/>
       </c>
-      <c r="B247" s="40">
+      <c r="B247" s="41">
         <f>ROUNDUP(A247/12,0)</f>
         <v/>
       </c>
@@ -18723,11 +18726,11 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="40">
+      <c r="A248" s="41">
         <f>A247+1</f>
         <v/>
       </c>
-      <c r="B248" s="40">
+      <c r="B248" s="41">
         <f>ROUNDUP(A248/12,0)</f>
         <v/>
       </c>
@@ -18753,11 +18756,11 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="40">
+      <c r="A249" s="41">
         <f>A248+1</f>
         <v/>
       </c>
-      <c r="B249" s="40">
+      <c r="B249" s="41">
         <f>ROUNDUP(A249/12,0)</f>
         <v/>
       </c>
@@ -18783,11 +18786,11 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="40">
+      <c r="A250" s="41">
         <f>A249+1</f>
         <v/>
       </c>
-      <c r="B250" s="40">
+      <c r="B250" s="41">
         <f>ROUNDUP(A250/12,0)</f>
         <v/>
       </c>
@@ -18813,11 +18816,11 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="40">
+      <c r="A251" s="41">
         <f>A250+1</f>
         <v/>
       </c>
-      <c r="B251" s="40">
+      <c r="B251" s="41">
         <f>ROUNDUP(A251/12,0)</f>
         <v/>
       </c>
@@ -18843,11 +18846,11 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="40">
+      <c r="A252" s="41">
         <f>A251+1</f>
         <v/>
       </c>
-      <c r="B252" s="40">
+      <c r="B252" s="41">
         <f>ROUNDUP(A252/12,0)</f>
         <v/>
       </c>
@@ -18873,11 +18876,11 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="40">
+      <c r="A253" s="41">
         <f>A252+1</f>
         <v/>
       </c>
-      <c r="B253" s="40">
+      <c r="B253" s="41">
         <f>ROUNDUP(A253/12,0)</f>
         <v/>
       </c>
@@ -18903,11 +18906,11 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="40">
+      <c r="A254" s="41">
         <f>A253+1</f>
         <v/>
       </c>
-      <c r="B254" s="40">
+      <c r="B254" s="41">
         <f>ROUNDUP(A254/12,0)</f>
         <v/>
       </c>
@@ -18933,11 +18936,11 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="40">
+      <c r="A255" s="41">
         <f>A254+1</f>
         <v/>
       </c>
-      <c r="B255" s="40">
+      <c r="B255" s="41">
         <f>ROUNDUP(A255/12,0)</f>
         <v/>
       </c>
@@ -18963,11 +18966,11 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="40">
+      <c r="A256" s="41">
         <f>A255+1</f>
         <v/>
       </c>
-      <c r="B256" s="40">
+      <c r="B256" s="41">
         <f>ROUNDUP(A256/12,0)</f>
         <v/>
       </c>
@@ -18993,11 +18996,11 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="40">
+      <c r="A257" s="41">
         <f>A256+1</f>
         <v/>
       </c>
-      <c r="B257" s="40">
+      <c r="B257" s="41">
         <f>ROUNDUP(A257/12,0)</f>
         <v/>
       </c>
@@ -19023,11 +19026,11 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="40">
+      <c r="A258" s="41">
         <f>A257+1</f>
         <v/>
       </c>
-      <c r="B258" s="40">
+      <c r="B258" s="41">
         <f>ROUNDUP(A258/12,0)</f>
         <v/>
       </c>
@@ -19053,11 +19056,11 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="40">
+      <c r="A259" s="41">
         <f>A258+1</f>
         <v/>
       </c>
-      <c r="B259" s="40">
+      <c r="B259" s="41">
         <f>ROUNDUP(A259/12,0)</f>
         <v/>
       </c>
@@ -19083,11 +19086,11 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="40">
+      <c r="A260" s="41">
         <f>A259+1</f>
         <v/>
       </c>
-      <c r="B260" s="40">
+      <c r="B260" s="41">
         <f>ROUNDUP(A260/12,0)</f>
         <v/>
       </c>
@@ -19113,11 +19116,11 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="40">
+      <c r="A261" s="41">
         <f>A260+1</f>
         <v/>
       </c>
-      <c r="B261" s="40">
+      <c r="B261" s="41">
         <f>ROUNDUP(A261/12,0)</f>
         <v/>
       </c>
@@ -19143,11 +19146,11 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="40">
+      <c r="A262" s="41">
         <f>A261+1</f>
         <v/>
       </c>
-      <c r="B262" s="40">
+      <c r="B262" s="41">
         <f>ROUNDUP(A262/12,0)</f>
         <v/>
       </c>
@@ -19173,11 +19176,11 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="40">
+      <c r="A263" s="41">
         <f>A262+1</f>
         <v/>
       </c>
-      <c r="B263" s="40">
+      <c r="B263" s="41">
         <f>ROUNDUP(A263/12,0)</f>
         <v/>
       </c>
@@ -19203,11 +19206,11 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="40">
+      <c r="A264" s="41">
         <f>A263+1</f>
         <v/>
       </c>
-      <c r="B264" s="40">
+      <c r="B264" s="41">
         <f>ROUNDUP(A264/12,0)</f>
         <v/>
       </c>
@@ -19264,37 +19267,37 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Conservador (Y1)</t>
         </is>
       </c>
-      <c r="C3" s="35" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>Conservador (Y3)</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="36" t="inlineStr">
         <is>
           <t>Caso Base (Y1)</t>
         </is>
       </c>
-      <c r="E3" s="35" t="inlineStr">
+      <c r="E3" s="36" t="inlineStr">
         <is>
           <t>Caso Base (Y3)</t>
         </is>
       </c>
-      <c r="F3" s="35" t="inlineStr">
+      <c r="F3" s="36" t="inlineStr">
         <is>
           <t>Optimista (Y1)</t>
         </is>
       </c>
-      <c r="G3" s="35" t="inlineStr">
+      <c r="G3" s="36" t="inlineStr">
         <is>
           <t>Optimista (Y3)</t>
         </is>
@@ -19549,12 +19552,12 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>Simulation Parameter</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Result Value</t>
         </is>
